--- a/MC2020_E25.xlsx
+++ b/MC2020_E25.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thuvaragan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5320BE30-E9D6-4201-8617-D8506C4F67DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="409">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1251,14 +1252,20 @@
   </si>
   <si>
     <t>PETERSON N.S.</t>
+  </si>
+  <si>
+    <t>2024/E/183</t>
+  </si>
+  <si>
+    <t>2021/E/184</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1450,25 +1457,25 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1502,7 +1509,7 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1546,20 +1553,32 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
-    <cellStyle name="60% - Accent1 2" xfId="1"/>
-    <cellStyle name="60% - Accent2 2" xfId="2"/>
-    <cellStyle name="60% - Accent3 2" xfId="3"/>
-    <cellStyle name="60% - Accent4 2" xfId="4"/>
-    <cellStyle name="60% - Accent5 2" xfId="5"/>
-    <cellStyle name="60% - Accent6 2" xfId="6"/>
+    <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Comma" xfId="10" builtinId="3"/>
-    <cellStyle name="Neutral 2" xfId="7"/>
+    <cellStyle name="Neutral 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8"/>
-    <cellStyle name="Normal 3" xfId="11"/>
-    <cellStyle name="Title 2" xfId="9"/>
+    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Title 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1831,8 +1850,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H238"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H239"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -1883,7 +1902,9 @@
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
-      <c r="G2" s="10"/>
+      <c r="G2" s="10">
+        <v>35</v>
+      </c>
       <c r="H2" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -1903,7 +1924,9 @@
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
-      <c r="G3" s="10"/>
+      <c r="G3" s="10">
+        <v>51</v>
+      </c>
       <c r="H3" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -1923,7 +1946,9 @@
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="10"/>
+      <c r="G4" s="10">
+        <v>53</v>
+      </c>
       <c r="H4" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -1943,7 +1968,9 @@
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="10">
+        <v>63</v>
+      </c>
       <c r="H5" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -1963,7 +1990,9 @@
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="10"/>
+      <c r="G6" s="10">
+        <v>46</v>
+      </c>
       <c r="H6" s="8">
         <v>28.571428599999997</v>
       </c>
@@ -1983,7 +2012,9 @@
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="10"/>
+      <c r="G7" s="10">
+        <v>60</v>
+      </c>
       <c r="H7" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -2003,7 +2034,9 @@
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="10"/>
+      <c r="G8" s="10">
+        <v>59</v>
+      </c>
       <c r="H8" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2023,7 +2056,9 @@
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="10"/>
+      <c r="G9" s="10">
+        <v>64</v>
+      </c>
       <c r="H9" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2043,7 +2078,9 @@
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="10"/>
+      <c r="G10" s="10">
+        <v>42</v>
+      </c>
       <c r="H10" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2063,7 +2100,9 @@
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="10"/>
+      <c r="G11" s="10">
+        <v>49</v>
+      </c>
       <c r="H11" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2083,7 +2122,9 @@
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="10"/>
+      <c r="G12" s="10">
+        <v>57</v>
+      </c>
       <c r="H12" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2103,7 +2144,9 @@
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="10"/>
+      <c r="G13" s="10">
+        <v>42</v>
+      </c>
       <c r="H13" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -2123,7 +2166,9 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="10"/>
+      <c r="G14" s="10">
+        <v>46</v>
+      </c>
       <c r="H14" s="8">
         <v>100</v>
       </c>
@@ -2143,7 +2188,9 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="10"/>
+      <c r="G15" s="10">
+        <v>55</v>
+      </c>
       <c r="H15" s="8">
         <v>100</v>
       </c>
@@ -2163,7 +2210,9 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="10"/>
+      <c r="G16" s="10">
+        <v>62</v>
+      </c>
       <c r="H16" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2183,7 +2232,9 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="10"/>
+      <c r="G17" s="10">
+        <v>70</v>
+      </c>
       <c r="H17" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2203,7 +2254,9 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="10"/>
+      <c r="G18" s="10">
+        <v>57</v>
+      </c>
       <c r="H18" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2223,7 +2276,9 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="10"/>
+      <c r="G19" s="10">
+        <v>77</v>
+      </c>
       <c r="H19" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2243,7 +2298,9 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="10"/>
+      <c r="G20" s="10">
+        <v>53</v>
+      </c>
       <c r="H20" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2263,7 +2320,9 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="10"/>
+      <c r="G21" s="10">
+        <v>58</v>
+      </c>
       <c r="H21" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2283,7 +2342,9 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="10"/>
+      <c r="G22" s="10">
+        <v>51</v>
+      </c>
       <c r="H22" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2303,7 +2364,9 @@
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="10"/>
+      <c r="G23" s="10">
+        <v>40</v>
+      </c>
       <c r="H23" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2323,7 +2386,9 @@
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
-      <c r="G24" s="10"/>
+      <c r="G24" s="10">
+        <v>64</v>
+      </c>
       <c r="H24" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2343,7 +2408,9 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="10"/>
+      <c r="G25" s="10">
+        <v>41</v>
+      </c>
       <c r="H25" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -2363,7 +2430,9 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="10"/>
+      <c r="G26" s="10">
+        <v>42</v>
+      </c>
       <c r="H26" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2383,7 +2452,9 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="10"/>
+      <c r="G27" s="10">
+        <v>61</v>
+      </c>
       <c r="H27" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -2403,7 +2474,9 @@
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="10"/>
+      <c r="G28" s="10">
+        <v>51</v>
+      </c>
       <c r="H28" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2423,7 +2496,9 @@
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="10"/>
+      <c r="G29" s="10">
+        <v>51</v>
+      </c>
       <c r="H29" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2443,7 +2518,9 @@
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="10"/>
+      <c r="G30" s="10">
+        <v>41</v>
+      </c>
       <c r="H30" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2463,7 +2540,9 @@
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="10"/>
+      <c r="G31" s="10">
+        <v>68</v>
+      </c>
       <c r="H31" s="8">
         <v>100</v>
       </c>
@@ -2483,7 +2562,9 @@
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="10"/>
+      <c r="G32" s="10">
+        <v>61</v>
+      </c>
       <c r="H32" s="8">
         <v>100</v>
       </c>
@@ -2503,7 +2584,9 @@
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="10"/>
+      <c r="G33" s="10">
+        <v>62</v>
+      </c>
       <c r="H33" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -2523,7 +2606,9 @@
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
-      <c r="G34" s="10"/>
+      <c r="G34" s="10">
+        <v>55</v>
+      </c>
       <c r="H34" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -2543,7 +2628,9 @@
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
-      <c r="G35" s="10"/>
+      <c r="G35" s="10">
+        <v>45</v>
+      </c>
       <c r="H35" s="8">
         <v>100</v>
       </c>
@@ -2563,7 +2650,9 @@
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
-      <c r="G36" s="10"/>
+      <c r="G36" s="10">
+        <v>42</v>
+      </c>
       <c r="H36" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2583,7 +2672,9 @@
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="10"/>
+      <c r="G37" s="10">
+        <v>52</v>
+      </c>
       <c r="H37" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -2603,7 +2694,9 @@
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="10"/>
+      <c r="G38" s="10">
+        <v>42</v>
+      </c>
       <c r="H38" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2623,7 +2716,9 @@
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
-      <c r="G39" s="10"/>
+      <c r="G39" s="10">
+        <v>67</v>
+      </c>
       <c r="H39" s="8">
         <v>100</v>
       </c>
@@ -2643,7 +2738,9 @@
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
-      <c r="G40" s="10"/>
+      <c r="G40" s="10">
+        <v>69</v>
+      </c>
       <c r="H40" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2663,7 +2760,9 @@
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
-      <c r="G41" s="10"/>
+      <c r="G41" s="10">
+        <v>64</v>
+      </c>
       <c r="H41" s="8">
         <v>100</v>
       </c>
@@ -2683,7 +2782,9 @@
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
-      <c r="G42" s="10"/>
+      <c r="G42" s="10">
+        <v>67</v>
+      </c>
       <c r="H42" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2703,7 +2804,9 @@
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
-      <c r="G43" s="10"/>
+      <c r="G43" s="10">
+        <v>54</v>
+      </c>
       <c r="H43" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2723,7 +2826,9 @@
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="10"/>
+      <c r="G44" s="10">
+        <v>46</v>
+      </c>
       <c r="H44" s="8">
         <v>100</v>
       </c>
@@ -2743,7 +2848,9 @@
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
-      <c r="G45" s="10"/>
+      <c r="G45" s="10">
+        <v>44</v>
+      </c>
       <c r="H45" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2763,7 +2870,9 @@
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
-      <c r="G46" s="10"/>
+      <c r="G46" s="10">
+        <v>50</v>
+      </c>
       <c r="H46" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2783,7 +2892,9 @@
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="10"/>
+      <c r="G47" s="10">
+        <v>68</v>
+      </c>
       <c r="H47" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2803,7 +2914,9 @@
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
-      <c r="G48" s="10"/>
+      <c r="G48" s="10">
+        <v>55</v>
+      </c>
       <c r="H48" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2823,7 +2936,9 @@
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
-      <c r="G49" s="10"/>
+      <c r="G49" s="10">
+        <v>54</v>
+      </c>
       <c r="H49" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2843,7 +2958,9 @@
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
-      <c r="G50" s="10"/>
+      <c r="G50" s="10">
+        <v>68</v>
+      </c>
       <c r="H50" s="8">
         <v>100</v>
       </c>
@@ -2863,7 +2980,9 @@
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="10"/>
+      <c r="G51" s="10">
+        <v>52</v>
+      </c>
       <c r="H51" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -2883,7 +3002,9 @@
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
-      <c r="G52" s="10"/>
+      <c r="G52" s="10">
+        <v>46</v>
+      </c>
       <c r="H52" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -2903,7 +3024,9 @@
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
-      <c r="G53" s="10"/>
+      <c r="G53" s="10">
+        <v>48</v>
+      </c>
       <c r="H53" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -2923,7 +3046,9 @@
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
-      <c r="G54" s="10"/>
+      <c r="G54" s="10">
+        <v>51</v>
+      </c>
       <c r="H54" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -2943,7 +3068,9 @@
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
-      <c r="G55" s="10"/>
+      <c r="G55" s="10">
+        <v>46</v>
+      </c>
       <c r="H55" s="8">
         <v>100</v>
       </c>
@@ -2963,7 +3090,9 @@
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
-      <c r="G56" s="10"/>
+      <c r="G56" s="10">
+        <v>71</v>
+      </c>
       <c r="H56" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -2983,7 +3112,9 @@
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
-      <c r="G57" s="10"/>
+      <c r="G57" s="10">
+        <v>42</v>
+      </c>
       <c r="H57" s="8">
         <v>100</v>
       </c>
@@ -3003,7 +3134,9 @@
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
-      <c r="G58" s="10"/>
+      <c r="G58" s="10">
+        <v>45</v>
+      </c>
       <c r="H58" s="8">
         <v>50</v>
       </c>
@@ -3023,7 +3156,9 @@
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
-      <c r="G59" s="10"/>
+      <c r="G59" s="10">
+        <v>64</v>
+      </c>
       <c r="H59" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3043,7 +3178,9 @@
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
-      <c r="G60" s="10"/>
+      <c r="G60" s="10">
+        <v>53</v>
+      </c>
       <c r="H60" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3063,7 +3200,9 @@
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
-      <c r="G61" s="10"/>
+      <c r="G61" s="10">
+        <v>48</v>
+      </c>
       <c r="H61" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -3083,7 +3222,9 @@
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
-      <c r="G62" s="10"/>
+      <c r="G62" s="10">
+        <v>54</v>
+      </c>
       <c r="H62" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3103,7 +3244,9 @@
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
-      <c r="G63" s="10"/>
+      <c r="G63" s="10">
+        <v>66</v>
+      </c>
       <c r="H63" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3123,7 +3266,9 @@
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
-      <c r="G64" s="10"/>
+      <c r="G64" s="10">
+        <v>58</v>
+      </c>
       <c r="H64" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3143,7 +3288,9 @@
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
-      <c r="G65" s="10"/>
+      <c r="G65" s="10">
+        <v>51</v>
+      </c>
       <c r="H65" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -3163,7 +3310,9 @@
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
-      <c r="G66" s="10"/>
+      <c r="G66" s="10">
+        <v>51</v>
+      </c>
       <c r="H66" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3183,7 +3332,9 @@
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
-      <c r="G67" s="10"/>
+      <c r="G67" s="10">
+        <v>55</v>
+      </c>
       <c r="H67" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -3203,7 +3354,9 @@
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
-      <c r="G68" s="10"/>
+      <c r="G68" s="10">
+        <v>44</v>
+      </c>
       <c r="H68" s="8">
         <v>53.846153799999996</v>
       </c>
@@ -3223,7 +3376,9 @@
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
-      <c r="G69" s="10"/>
+      <c r="G69" s="10">
+        <v>64</v>
+      </c>
       <c r="H69" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -3243,7 +3398,9 @@
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
-      <c r="G70" s="10"/>
+      <c r="G70" s="10">
+        <v>68</v>
+      </c>
       <c r="H70" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3263,7 +3420,9 @@
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="10"/>
+      <c r="G71" s="10">
+        <v>59</v>
+      </c>
       <c r="H71" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3283,7 +3442,9 @@
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
-      <c r="G72" s="10"/>
+      <c r="G72" s="10">
+        <v>51</v>
+      </c>
       <c r="H72" s="8">
         <v>76.923076899999998</v>
       </c>
@@ -3303,7 +3464,9 @@
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
-      <c r="G73" s="10"/>
+      <c r="G73" s="10">
+        <v>46</v>
+      </c>
       <c r="H73" s="8">
         <v>57.142857100000001</v>
       </c>
@@ -3323,7 +3486,9 @@
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="5"/>
-      <c r="G74" s="10"/>
+      <c r="G74" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="H74" s="8">
         <v>7.1428570999999996</v>
       </c>
@@ -3343,7 +3508,9 @@
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
-      <c r="G75" s="10"/>
+      <c r="G75" s="10">
+        <v>64</v>
+      </c>
       <c r="H75" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -3363,7 +3530,9 @@
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="10"/>
+      <c r="G76" s="10">
+        <v>74</v>
+      </c>
       <c r="H76" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3383,7 +3552,9 @@
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
-      <c r="G77" s="10"/>
+      <c r="G77" s="10">
+        <v>48</v>
+      </c>
       <c r="H77" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -3403,7 +3574,9 @@
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
-      <c r="G78" s="10"/>
+      <c r="G78" s="10">
+        <v>64</v>
+      </c>
       <c r="H78" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -3423,7 +3596,9 @@
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
-      <c r="G79" s="10"/>
+      <c r="G79" s="10">
+        <v>62</v>
+      </c>
       <c r="H79" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -3443,7 +3618,9 @@
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
-      <c r="G80" s="10"/>
+      <c r="G80" s="10">
+        <v>64</v>
+      </c>
       <c r="H80" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -3463,7 +3640,9 @@
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
-      <c r="G81" s="10"/>
+      <c r="G81" s="10">
+        <v>67</v>
+      </c>
       <c r="H81" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -3483,7 +3662,9 @@
       </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
-      <c r="G82" s="10"/>
+      <c r="G82" s="10">
+        <v>46</v>
+      </c>
       <c r="H82" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3503,7 +3684,9 @@
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="10"/>
+      <c r="G83" s="10">
+        <v>61</v>
+      </c>
       <c r="H83" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3523,7 +3706,9 @@
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
-      <c r="G84" s="10"/>
+      <c r="G84" s="10">
+        <v>50</v>
+      </c>
       <c r="H84" s="8">
         <v>100</v>
       </c>
@@ -3543,7 +3728,9 @@
       </c>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
-      <c r="G85" s="10"/>
+      <c r="G85" s="10">
+        <v>71</v>
+      </c>
       <c r="H85" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3563,7 +3750,9 @@
       </c>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
-      <c r="G86" s="10"/>
+      <c r="G86" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="H86" s="8">
         <v>0</v>
       </c>
@@ -3583,7 +3772,9 @@
       </c>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
-      <c r="G87" s="10"/>
+      <c r="G87" s="10">
+        <v>46</v>
+      </c>
       <c r="H87" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3603,7 +3794,9 @@
       </c>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
-      <c r="G88" s="10"/>
+      <c r="G88" s="10">
+        <v>58</v>
+      </c>
       <c r="H88" s="8">
         <v>35.714285699999998</v>
       </c>
@@ -3623,7 +3816,9 @@
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
-      <c r="G89" s="10"/>
+      <c r="G89" s="10">
+        <v>51</v>
+      </c>
       <c r="H89" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3643,7 +3838,9 @@
       </c>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="10"/>
+      <c r="G90" s="10">
+        <v>52</v>
+      </c>
       <c r="H90" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3663,7 +3860,9 @@
       </c>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
-      <c r="G91" s="10"/>
+      <c r="G91" s="10">
+        <v>62</v>
+      </c>
       <c r="H91" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -3683,7 +3882,9 @@
       </c>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
-      <c r="G92" s="10"/>
+      <c r="G92" s="10">
+        <v>56</v>
+      </c>
       <c r="H92" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3703,7 +3904,9 @@
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
-      <c r="G93" s="10"/>
+      <c r="G93" s="10">
+        <v>48</v>
+      </c>
       <c r="H93" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -3723,7 +3926,9 @@
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
-      <c r="G94" s="10"/>
+      <c r="G94" s="10">
+        <v>49</v>
+      </c>
       <c r="H94" s="8">
         <v>50</v>
       </c>
@@ -3743,7 +3948,9 @@
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="10"/>
+      <c r="G95" s="10">
+        <v>55</v>
+      </c>
       <c r="H95" s="8">
         <v>35.714285699999998</v>
       </c>
@@ -3763,7 +3970,9 @@
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
-      <c r="G96" s="10"/>
+      <c r="G96" s="10">
+        <v>46</v>
+      </c>
       <c r="H96" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -3783,7 +3992,9 @@
       </c>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
-      <c r="G97" s="10"/>
+      <c r="G97" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="H97" s="8">
         <v>0</v>
       </c>
@@ -3803,7 +4014,9 @@
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
-      <c r="G98" s="10"/>
+      <c r="G98" s="10">
+        <v>65</v>
+      </c>
       <c r="H98" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -3823,7 +4036,9 @@
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
-      <c r="G99" s="10"/>
+      <c r="G99" s="10">
+        <v>61</v>
+      </c>
       <c r="H99" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3843,7 +4058,9 @@
       </c>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
-      <c r="G100" s="10"/>
+      <c r="G100" s="10">
+        <v>36</v>
+      </c>
       <c r="H100" s="8">
         <v>100</v>
       </c>
@@ -3863,7 +4080,9 @@
       </c>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
-      <c r="G101" s="10"/>
+      <c r="G101" s="10">
+        <v>64</v>
+      </c>
       <c r="H101" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3883,7 +4102,9 @@
       </c>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
-      <c r="G102" s="10"/>
+      <c r="G102" s="10">
+        <v>45</v>
+      </c>
       <c r="H102" s="8">
         <v>42.857142899999999</v>
       </c>
@@ -3903,7 +4124,9 @@
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="5"/>
-      <c r="G103" s="10"/>
+      <c r="G103" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="H103" s="8">
         <v>0</v>
       </c>
@@ -3923,7 +4146,9 @@
       </c>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
-      <c r="G104" s="10"/>
+      <c r="G104" s="10">
+        <v>69</v>
+      </c>
       <c r="H104" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3943,7 +4168,9 @@
       </c>
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
-      <c r="G105" s="10"/>
+      <c r="G105" s="10">
+        <v>35</v>
+      </c>
       <c r="H105" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -3963,7 +4190,9 @@
       </c>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
-      <c r="G106" s="10"/>
+      <c r="G106" s="10">
+        <v>57</v>
+      </c>
       <c r="H106" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -3983,7 +4212,9 @@
       </c>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
-      <c r="G107" s="10"/>
+      <c r="G107" s="10">
+        <v>55</v>
+      </c>
       <c r="H107" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4003,7 +4234,9 @@
       </c>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
-      <c r="G108" s="10"/>
+      <c r="G108" s="10">
+        <v>63</v>
+      </c>
       <c r="H108" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4023,7 +4256,9 @@
       </c>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
-      <c r="G109" s="10"/>
+      <c r="G109" s="10">
+        <v>47</v>
+      </c>
       <c r="H109" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4043,7 +4278,9 @@
       </c>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
-      <c r="G110" s="10"/>
+      <c r="G110" s="10">
+        <v>70</v>
+      </c>
       <c r="H110" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4063,7 +4300,9 @@
       </c>
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
-      <c r="G111" s="10"/>
+      <c r="G111" s="10">
+        <v>44</v>
+      </c>
       <c r="H111" s="8">
         <v>57.142857100000001</v>
       </c>
@@ -4083,7 +4322,9 @@
       </c>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
-      <c r="G112" s="10"/>
+      <c r="G112" s="10">
+        <v>49</v>
+      </c>
       <c r="H112" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -4103,7 +4344,9 @@
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
-      <c r="G113" s="10"/>
+      <c r="G113" s="10">
+        <v>58</v>
+      </c>
       <c r="H113" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4123,7 +4366,9 @@
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
-      <c r="G114" s="10"/>
+      <c r="G114" s="10">
+        <v>60</v>
+      </c>
       <c r="H114" s="8">
         <v>100</v>
       </c>
@@ -4143,7 +4388,9 @@
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
-      <c r="G115" s="10"/>
+      <c r="G115" s="10">
+        <v>58</v>
+      </c>
       <c r="H115" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4163,7 +4410,9 @@
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
-      <c r="G116" s="10"/>
+      <c r="G116" s="10">
+        <v>51</v>
+      </c>
       <c r="H116" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4183,7 +4432,9 @@
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
-      <c r="G117" s="10"/>
+      <c r="G117" s="10">
+        <v>58</v>
+      </c>
       <c r="H117" s="8">
         <v>100</v>
       </c>
@@ -4203,7 +4454,9 @@
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
-      <c r="G118" s="10"/>
+      <c r="G118" s="10">
+        <v>58</v>
+      </c>
       <c r="H118" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4223,7 +4476,9 @@
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
-      <c r="G119" s="10"/>
+      <c r="G119" s="10">
+        <v>38</v>
+      </c>
       <c r="H119" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4243,7 +4498,9 @@
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
-      <c r="G120" s="10"/>
+      <c r="G120" s="10">
+        <v>60</v>
+      </c>
       <c r="H120" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4263,7 +4520,9 @@
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
-      <c r="G121" s="10"/>
+      <c r="G121" s="10">
+        <v>43</v>
+      </c>
       <c r="H121" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4283,7 +4542,9 @@
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
-      <c r="G122" s="10"/>
+      <c r="G122" s="10">
+        <v>44</v>
+      </c>
       <c r="H122" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4303,7 +4564,9 @@
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
-      <c r="G123" s="10"/>
+      <c r="G123" s="10">
+        <v>61</v>
+      </c>
       <c r="H123" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4323,7 +4586,9 @@
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
-      <c r="G124" s="10"/>
+      <c r="G124" s="10">
+        <v>43</v>
+      </c>
       <c r="H124" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -4343,7 +4608,9 @@
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
-      <c r="G125" s="10"/>
+      <c r="G125" s="10">
+        <v>42</v>
+      </c>
       <c r="H125" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4363,7 +4630,9 @@
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
-      <c r="G126" s="10"/>
+      <c r="G126" s="10">
+        <v>47</v>
+      </c>
       <c r="H126" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4383,7 +4652,9 @@
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
-      <c r="G127" s="10"/>
+      <c r="G127" s="10">
+        <v>57</v>
+      </c>
       <c r="H127" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4403,7 +4674,9 @@
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
-      <c r="G128" s="10"/>
+      <c r="G128" s="10">
+        <v>63</v>
+      </c>
       <c r="H128" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4423,7 +4696,9 @@
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
-      <c r="G129" s="10"/>
+      <c r="G129" s="10">
+        <v>35</v>
+      </c>
       <c r="H129" s="8">
         <v>100</v>
       </c>
@@ -4443,7 +4718,9 @@
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
-      <c r="G130" s="10"/>
+      <c r="G130" s="10">
+        <v>38</v>
+      </c>
       <c r="H130" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4463,7 +4740,9 @@
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
-      <c r="G131" s="10"/>
+      <c r="G131" s="10">
+        <v>58</v>
+      </c>
       <c r="H131" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4483,7 +4762,9 @@
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
-      <c r="G132" s="10"/>
+      <c r="G132" s="10">
+        <v>60</v>
+      </c>
       <c r="H132" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -4503,7 +4784,9 @@
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
-      <c r="G133" s="10"/>
+      <c r="G133" s="10">
+        <v>61</v>
+      </c>
       <c r="H133" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4523,7 +4806,9 @@
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
-      <c r="G134" s="10"/>
+      <c r="G134" s="10">
+        <v>58</v>
+      </c>
       <c r="H134" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4543,7 +4828,9 @@
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
-      <c r="G135" s="10"/>
+      <c r="G135" s="10">
+        <v>62</v>
+      </c>
       <c r="H135" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -4563,7 +4850,9 @@
       </c>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
-      <c r="G136" s="10"/>
+      <c r="G136" s="10">
+        <v>53</v>
+      </c>
       <c r="H136" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4583,7 +4872,9 @@
       </c>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
-      <c r="G137" s="10"/>
+      <c r="G137" s="10">
+        <v>30</v>
+      </c>
       <c r="H137" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4603,7 +4894,9 @@
       </c>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
-      <c r="G138" s="10"/>
+      <c r="G138" s="10">
+        <v>59</v>
+      </c>
       <c r="H138" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4623,7 +4916,9 @@
       </c>
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
-      <c r="G139" s="10"/>
+      <c r="G139" s="10">
+        <v>51</v>
+      </c>
       <c r="H139" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -4643,7 +4938,9 @@
       </c>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
-      <c r="G140" s="10"/>
+      <c r="G140" s="10">
+        <v>61</v>
+      </c>
       <c r="H140" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4663,7 +4960,9 @@
       </c>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
-      <c r="G141" s="10"/>
+      <c r="G141" s="10">
+        <v>54</v>
+      </c>
       <c r="H141" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -4683,7 +4982,9 @@
       </c>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
-      <c r="G142" s="10"/>
+      <c r="G142" s="10">
+        <v>45</v>
+      </c>
       <c r="H142" s="8">
         <v>100</v>
       </c>
@@ -4703,7 +5004,9 @@
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
-      <c r="G143" s="10"/>
+      <c r="G143" s="10">
+        <v>47</v>
+      </c>
       <c r="H143" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4723,7 +5026,9 @@
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
-      <c r="G144" s="10"/>
+      <c r="G144" s="10">
+        <v>61</v>
+      </c>
       <c r="H144" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4743,7 +5048,9 @@
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
-      <c r="G145" s="10"/>
+      <c r="G145" s="10">
+        <v>73</v>
+      </c>
       <c r="H145" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4763,7 +5070,9 @@
       </c>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
-      <c r="G146" s="10"/>
+      <c r="G146" s="10">
+        <v>53</v>
+      </c>
       <c r="H146" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4783,7 +5092,9 @@
       </c>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
-      <c r="G147" s="10"/>
+      <c r="G147" s="10">
+        <v>54</v>
+      </c>
       <c r="H147" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -4803,7 +5114,9 @@
       </c>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
-      <c r="G148" s="10"/>
+      <c r="G148" s="10">
+        <v>51</v>
+      </c>
       <c r="H148" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4823,7 +5136,9 @@
       </c>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
-      <c r="G149" s="10"/>
+      <c r="G149" s="10">
+        <v>56</v>
+      </c>
       <c r="H149" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4843,7 +5158,9 @@
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
-      <c r="G150" s="10"/>
+      <c r="G150" s="10">
+        <v>51</v>
+      </c>
       <c r="H150" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4863,7 +5180,9 @@
       </c>
       <c r="E151" s="5"/>
       <c r="F151" s="5"/>
-      <c r="G151" s="10"/>
+      <c r="G151" s="10">
+        <v>67</v>
+      </c>
       <c r="H151" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -4883,7 +5202,9 @@
       </c>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
-      <c r="G152" s="10"/>
+      <c r="G152" s="10">
+        <v>45</v>
+      </c>
       <c r="H152" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -4903,7 +5224,9 @@
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
-      <c r="G153" s="10"/>
+      <c r="G153" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="H153" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -4923,7 +5246,9 @@
       </c>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
-      <c r="G154" s="10"/>
+      <c r="G154" s="10">
+        <v>73</v>
+      </c>
       <c r="H154" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -4943,7 +5268,9 @@
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
-      <c r="G155" s="10"/>
+      <c r="G155" s="10">
+        <v>62</v>
+      </c>
       <c r="H155" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -4963,7 +5290,9 @@
       </c>
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
-      <c r="G156" s="10"/>
+      <c r="G156" s="10">
+        <v>49</v>
+      </c>
       <c r="H156" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -4983,7 +5312,9 @@
       </c>
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
-      <c r="G157" s="10"/>
+      <c r="G157" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="H157" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5003,7 +5334,9 @@
       </c>
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
-      <c r="G158" s="10"/>
+      <c r="G158" s="10">
+        <v>50</v>
+      </c>
       <c r="H158" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -5023,7 +5356,9 @@
       </c>
       <c r="E159" s="5"/>
       <c r="F159" s="5"/>
-      <c r="G159" s="10"/>
+      <c r="G159" s="10">
+        <v>62</v>
+      </c>
       <c r="H159" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5043,7 +5378,9 @@
       </c>
       <c r="E160" s="5"/>
       <c r="F160" s="5"/>
-      <c r="G160" s="10"/>
+      <c r="G160" s="10">
+        <v>51</v>
+      </c>
       <c r="H160" s="8">
         <v>100</v>
       </c>
@@ -5063,7 +5400,9 @@
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
-      <c r="G161" s="10"/>
+      <c r="G161" s="10">
+        <v>47</v>
+      </c>
       <c r="H161" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5083,7 +5422,9 @@
       </c>
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
-      <c r="G162" s="10"/>
+      <c r="G162" s="10">
+        <v>50</v>
+      </c>
       <c r="H162" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -5103,7 +5444,9 @@
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
-      <c r="G163" s="10"/>
+      <c r="G163" s="10">
+        <v>45</v>
+      </c>
       <c r="H163" s="8">
         <v>100</v>
       </c>
@@ -5123,7 +5466,9 @@
       </c>
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
-      <c r="G164" s="10"/>
+      <c r="G164" s="10">
+        <v>49</v>
+      </c>
       <c r="H164" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5143,7 +5488,9 @@
       </c>
       <c r="E165" s="5"/>
       <c r="F165" s="5"/>
-      <c r="G165" s="10"/>
+      <c r="G165" s="10">
+        <v>51</v>
+      </c>
       <c r="H165" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -5163,7 +5510,9 @@
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5"/>
-      <c r="G166" s="10"/>
+      <c r="G166" s="10">
+        <v>56</v>
+      </c>
       <c r="H166" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5183,7 +5532,9 @@
       </c>
       <c r="E167" s="5"/>
       <c r="F167" s="5"/>
-      <c r="G167" s="10"/>
+      <c r="G167" s="10">
+        <v>61</v>
+      </c>
       <c r="H167" s="8">
         <v>100</v>
       </c>
@@ -5203,7 +5554,9 @@
       </c>
       <c r="E168" s="5"/>
       <c r="F168" s="5"/>
-      <c r="G168" s="10"/>
+      <c r="G168" s="10">
+        <v>58</v>
+      </c>
       <c r="H168" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5223,7 +5576,9 @@
       </c>
       <c r="E169" s="5"/>
       <c r="F169" s="5"/>
-      <c r="G169" s="10"/>
+      <c r="G169" s="10">
+        <v>43</v>
+      </c>
       <c r="H169" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5243,7 +5598,9 @@
       </c>
       <c r="E170" s="5"/>
       <c r="F170" s="5"/>
-      <c r="G170" s="10"/>
+      <c r="G170" s="10">
+        <v>57</v>
+      </c>
       <c r="H170" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5263,7 +5620,9 @@
       </c>
       <c r="E171" s="5"/>
       <c r="F171" s="5"/>
-      <c r="G171" s="10"/>
+      <c r="G171" s="10">
+        <v>77</v>
+      </c>
       <c r="H171" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5283,7 +5642,9 @@
       </c>
       <c r="E172" s="5"/>
       <c r="F172" s="5"/>
-      <c r="G172" s="10"/>
+      <c r="G172" s="10">
+        <v>45</v>
+      </c>
       <c r="H172" s="8">
         <v>100</v>
       </c>
@@ -5303,7 +5664,9 @@
       </c>
       <c r="E173" s="5"/>
       <c r="F173" s="5"/>
-      <c r="G173" s="10"/>
+      <c r="G173" s="10">
+        <v>62</v>
+      </c>
       <c r="H173" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -5323,7 +5686,9 @@
       </c>
       <c r="E174" s="5"/>
       <c r="F174" s="5"/>
-      <c r="G174" s="10"/>
+      <c r="G174" s="10">
+        <v>53</v>
+      </c>
       <c r="H174" s="8">
         <v>76.923076899999998</v>
       </c>
@@ -5343,7 +5708,9 @@
       </c>
       <c r="E175" s="5"/>
       <c r="F175" s="5"/>
-      <c r="G175" s="10"/>
+      <c r="G175" s="10">
+        <v>43</v>
+      </c>
       <c r="H175" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5363,7 +5730,9 @@
       </c>
       <c r="E176" s="5"/>
       <c r="F176" s="5"/>
-      <c r="G176" s="10"/>
+      <c r="G176" s="10">
+        <v>52</v>
+      </c>
       <c r="H176" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5383,7 +5752,9 @@
       </c>
       <c r="E177" s="5"/>
       <c r="F177" s="5"/>
-      <c r="G177" s="10"/>
+      <c r="G177" s="10">
+        <v>50</v>
+      </c>
       <c r="H177" s="8">
         <v>71.428571399999996</v>
       </c>
@@ -5403,7 +5774,9 @@
       </c>
       <c r="E178" s="5"/>
       <c r="F178" s="5"/>
-      <c r="G178" s="10"/>
+      <c r="G178" s="10">
+        <v>55</v>
+      </c>
       <c r="H178" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5423,7 +5796,9 @@
       </c>
       <c r="E179" s="5"/>
       <c r="F179" s="5"/>
-      <c r="G179" s="10"/>
+      <c r="G179" s="10">
+        <v>53</v>
+      </c>
       <c r="H179" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5443,7 +5818,9 @@
       </c>
       <c r="E180" s="5"/>
       <c r="F180" s="5"/>
-      <c r="G180" s="10"/>
+      <c r="G180" s="10">
+        <v>61</v>
+      </c>
       <c r="H180" s="8">
         <v>78.571428600000004</v>
       </c>
@@ -5463,7 +5840,9 @@
       </c>
       <c r="E181" s="5"/>
       <c r="F181" s="5"/>
-      <c r="G181" s="10"/>
+      <c r="G181" s="10">
+        <v>48</v>
+      </c>
       <c r="H181" s="8">
         <v>100</v>
       </c>
@@ -5483,7 +5862,9 @@
       </c>
       <c r="E182" s="5"/>
       <c r="F182" s="5"/>
-      <c r="G182" s="10"/>
+      <c r="G182" s="10">
+        <v>37</v>
+      </c>
       <c r="H182" s="8">
         <v>64.285714299999995</v>
       </c>
@@ -5503,7 +5884,9 @@
       </c>
       <c r="E183" s="5"/>
       <c r="F183" s="5"/>
-      <c r="G183" s="10"/>
+      <c r="G183" s="10">
+        <v>44</v>
+      </c>
       <c r="H183" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5523,7 +5906,9 @@
       </c>
       <c r="E184" s="5"/>
       <c r="F184" s="5"/>
-      <c r="G184" s="10"/>
+      <c r="G184" s="10">
+        <v>53</v>
+      </c>
       <c r="H184" s="8">
         <v>100</v>
       </c>
@@ -5543,7 +5928,9 @@
       </c>
       <c r="E185" s="5"/>
       <c r="F185" s="5"/>
-      <c r="G185" s="10"/>
+      <c r="G185" s="10">
+        <v>74</v>
+      </c>
       <c r="H185" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5563,7 +5950,9 @@
       </c>
       <c r="E186" s="5"/>
       <c r="F186" s="5"/>
-      <c r="G186" s="10"/>
+      <c r="G186" s="10">
+        <v>62</v>
+      </c>
       <c r="H186" s="8">
         <v>100</v>
       </c>
@@ -5583,7 +5972,9 @@
       </c>
       <c r="E187" s="5"/>
       <c r="F187" s="5"/>
-      <c r="G187" s="10"/>
+      <c r="G187" s="10">
+        <v>47</v>
+      </c>
       <c r="H187" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5603,7 +5994,9 @@
       </c>
       <c r="E188" s="5"/>
       <c r="F188" s="5"/>
-      <c r="G188" s="10"/>
+      <c r="G188" s="10">
+        <v>37</v>
+      </c>
       <c r="H188" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5623,7 +6016,9 @@
       </c>
       <c r="E189" s="5"/>
       <c r="F189" s="5"/>
-      <c r="G189" s="10"/>
+      <c r="G189" s="10">
+        <v>42</v>
+      </c>
       <c r="H189" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5643,7 +6038,9 @@
       </c>
       <c r="E190" s="5"/>
       <c r="F190" s="5"/>
-      <c r="G190" s="10"/>
+      <c r="G190" s="10">
+        <v>57</v>
+      </c>
       <c r="H190" s="8">
         <v>85.714285700000005</v>
       </c>
@@ -5663,7 +6060,9 @@
       </c>
       <c r="E191" s="5"/>
       <c r="F191" s="5"/>
-      <c r="G191" s="10"/>
+      <c r="G191" s="10">
+        <v>62</v>
+      </c>
       <c r="H191" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5683,7 +6082,9 @@
       </c>
       <c r="E192" s="5"/>
       <c r="F192" s="5"/>
-      <c r="G192" s="10"/>
+      <c r="G192" s="10">
+        <v>45</v>
+      </c>
       <c r="H192" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5703,7 +6104,9 @@
       </c>
       <c r="E193" s="5"/>
       <c r="F193" s="5"/>
-      <c r="G193" s="10"/>
+      <c r="G193" s="10">
+        <v>39</v>
+      </c>
       <c r="H193" s="8">
         <v>92.857142899999999</v>
       </c>
@@ -5723,7 +6126,9 @@
       </c>
       <c r="E194" s="5"/>
       <c r="F194" s="5"/>
-      <c r="G194" s="10"/>
+      <c r="G194" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="H194" s="6"/>
     </row>
     <row r="195" spans="1:8">
@@ -5741,7 +6146,9 @@
       </c>
       <c r="E195" s="5"/>
       <c r="F195" s="5"/>
-      <c r="G195" s="10"/>
+      <c r="G195" s="10">
+        <v>50</v>
+      </c>
       <c r="H195" s="6"/>
     </row>
     <row r="196" spans="1:8">
@@ -5757,7 +6164,9 @@
       </c>
       <c r="E196" s="5"/>
       <c r="F196" s="5"/>
-      <c r="G196" s="10"/>
+      <c r="G196" s="39">
+        <v>53</v>
+      </c>
       <c r="H196" s="6"/>
     </row>
     <row r="197" spans="1:8">
@@ -5775,7 +6184,9 @@
       </c>
       <c r="E197" s="5"/>
       <c r="F197" s="5"/>
-      <c r="G197" s="10"/>
+      <c r="G197" s="10">
+        <v>40</v>
+      </c>
       <c r="H197" s="6"/>
     </row>
     <row r="198" spans="1:8">
@@ -5793,80 +6204,104 @@
       </c>
       <c r="E198" s="5"/>
       <c r="F198" s="5"/>
-      <c r="G198" s="10"/>
+      <c r="G198" s="10">
+        <v>71</v>
+      </c>
       <c r="H198" s="6"/>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="35" t="s">
-        <v>402</v>
-      </c>
-      <c r="B199" s="29" t="s">
-        <v>403</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="B199" s="29"/>
       <c r="C199" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="D199" s="9">
-        <v>86.5</v>
+      <c r="D199" s="9" t="s">
+        <v>383</v>
       </c>
       <c r="E199" s="5"/>
       <c r="F199" s="5"/>
-      <c r="G199" s="10"/>
+      <c r="G199" s="10">
+        <v>49</v>
+      </c>
       <c r="H199" s="6"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="B200" s="31"/>
-      <c r="C200" s="10">
-        <v>36</v>
+      <c r="A200" s="35" t="s">
+        <v>402</v>
+      </c>
+      <c r="B200" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>383</v>
       </c>
       <c r="D200" s="9">
-        <v>92.5</v>
+        <v>86.5</v>
       </c>
       <c r="E200" s="5"/>
       <c r="F200" s="5"/>
-      <c r="G200" s="10"/>
+      <c r="G200" s="10">
+        <v>54</v>
+      </c>
       <c r="H200" s="6"/>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="B201" s="31" t="s">
-        <v>406</v>
-      </c>
-      <c r="C201" s="10" t="s">
-        <v>383</v>
+        <v>404</v>
+      </c>
+      <c r="B201" s="31"/>
+      <c r="C201" s="10">
+        <v>36</v>
       </c>
       <c r="D201" s="9">
-        <v>86.5</v>
+        <v>92.5</v>
       </c>
       <c r="E201" s="5"/>
       <c r="F201" s="5"/>
-      <c r="G201" s="10"/>
+      <c r="G201" s="10">
+        <v>54</v>
+      </c>
       <c r="H201" s="6"/>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" s="14"/>
-      <c r="B202" s="15"/>
-      <c r="C202" s="16"/>
-      <c r="D202" s="17"/>
-      <c r="E202" s="18"/>
-      <c r="F202" s="18"/>
-      <c r="G202" s="19"/>
-      <c r="H202" s="20"/>
+      <c r="A202" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="B202" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D202" s="9">
+        <v>86.5</v>
+      </c>
+      <c r="E202" s="5"/>
+      <c r="F202" s="5"/>
+      <c r="G202" s="10">
+        <v>45</v>
+      </c>
+      <c r="H202" s="6"/>
     </row>
     <row r="203" spans="1:8">
-      <c r="A203" s="14"/>
-      <c r="B203" s="15"/>
-      <c r="C203" s="16"/>
-      <c r="D203" s="17"/>
-      <c r="E203" s="18"/>
-      <c r="F203" s="18"/>
-      <c r="G203" s="19"/>
-      <c r="H203" s="20"/>
+      <c r="A203" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="B203" s="37"/>
+      <c r="C203" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="10">
+        <v>29</v>
+      </c>
+      <c r="H203" s="6"/>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="14"/>
@@ -5904,7 +6339,7 @@
       <c r="C207" s="16"/>
       <c r="D207" s="17"/>
       <c r="E207" s="18"/>
-      <c r="F207" s="21"/>
+      <c r="F207" s="18"/>
       <c r="G207" s="19"/>
       <c r="H207" s="20"/>
     </row>
@@ -5914,7 +6349,7 @@
       <c r="C208" s="16"/>
       <c r="D208" s="17"/>
       <c r="E208" s="18"/>
-      <c r="F208" s="18"/>
+      <c r="F208" s="21"/>
       <c r="G208" s="19"/>
       <c r="H208" s="20"/>
     </row>
@@ -6003,7 +6438,7 @@
       <c r="B217" s="15"/>
       <c r="C217" s="16"/>
       <c r="D217" s="17"/>
-      <c r="E217" s="22"/>
+      <c r="E217" s="18"/>
       <c r="F217" s="18"/>
       <c r="G217" s="19"/>
       <c r="H217" s="20"/>
@@ -6013,7 +6448,7 @@
       <c r="B218" s="15"/>
       <c r="C218" s="16"/>
       <c r="D218" s="17"/>
-      <c r="E218" s="18"/>
+      <c r="E218" s="22"/>
       <c r="F218" s="18"/>
       <c r="G218" s="19"/>
       <c r="H218" s="20"/>
@@ -6163,17 +6598,17 @@
       <c r="B233" s="15"/>
       <c r="C233" s="16"/>
       <c r="D233" s="17"/>
-      <c r="E233" s="22"/>
+      <c r="E233" s="18"/>
       <c r="F233" s="18"/>
       <c r="G233" s="19"/>
       <c r="H233" s="20"/>
     </row>
     <row r="234" spans="1:8">
-      <c r="A234" s="23"/>
-      <c r="B234" s="24"/>
+      <c r="A234" s="14"/>
+      <c r="B234" s="15"/>
       <c r="C234" s="16"/>
       <c r="D234" s="17"/>
-      <c r="E234" s="18"/>
+      <c r="E234" s="22"/>
       <c r="F234" s="18"/>
       <c r="G234" s="19"/>
       <c r="H234" s="20"/>
@@ -6203,20 +6638,30 @@
       <c r="B237" s="24"/>
       <c r="C237" s="16"/>
       <c r="D237" s="17"/>
-      <c r="E237" s="16"/>
+      <c r="E237" s="18"/>
       <c r="F237" s="18"/>
       <c r="G237" s="19"/>
       <c r="H237" s="20"/>
     </row>
     <row r="238" spans="1:8">
-      <c r="A238" s="25"/>
-      <c r="B238" s="26"/>
+      <c r="A238" s="23"/>
+      <c r="B238" s="24"/>
       <c r="C238" s="16"/>
       <c r="D238" s="17"/>
       <c r="E238" s="16"/>
       <c r="F238" s="18"/>
       <c r="G238" s="19"/>
       <c r="H238" s="20"/>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="25"/>
+      <c r="B239" s="26"/>
+      <c r="C239" s="16"/>
+      <c r="D239" s="17"/>
+      <c r="E239" s="16"/>
+      <c r="F239" s="18"/>
+      <c r="G239" s="19"/>
+      <c r="H239" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6369,18 +6814,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6390,12 +6835,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6409,4 +6848,10 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
--- a/MC2020_E25.xlsx
+++ b/MC2020_E25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5320BE30-E9D6-4201-8617-D8506C4F67DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7997429F-F3ED-4E28-B3BB-BE164E4E8F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="410">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1258,6 +1258,9 @@
   </si>
   <si>
     <t>2021/E/184</t>
+  </si>
+  <si>
+    <t>2023/E/090</t>
   </si>
 </sst>
 </file>
@@ -1460,7 +1463,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1472,9 +1475,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1562,7 +1562,14 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1851,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:M240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -1861,7 +1868,7 @@
     <col min="8" max="8" width="15.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1886,4782 +1893,5616 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="11" t="s">
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="33" t="s">
         <v>383</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>82</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="5">
+        <v>72</v>
+      </c>
       <c r="F2" s="5"/>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <v>35</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="11" t="s">
+      <c r="L2" s="39"/>
+      <c r="M2" s="38"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>70</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>82</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5">
+        <v>72</v>
+      </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>51</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="11" t="s">
+      <c r="L3" s="39"/>
+      <c r="M3" s="38"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>60</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>75</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5">
+        <v>59</v>
+      </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>53</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="11" t="s">
+      <c r="L4" s="39"/>
+      <c r="M4" s="38"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>42</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>86</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5">
+        <v>65</v>
+      </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>63</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="12" t="s">
+      <c r="L5" s="39"/>
+      <c r="M5" s="38"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>36</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>99</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5">
+        <v>64</v>
+      </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>46</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>28.571428599999997</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="12" t="s">
+      <c r="L6" s="39"/>
+      <c r="M6" s="38"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>70</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>68.5</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5">
+        <v>64</v>
+      </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>60</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="12" t="s">
+      <c r="L7" s="39"/>
+      <c r="M7" s="38"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>70</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>53</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5">
+        <v>80</v>
+      </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>59</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="12" t="s">
+      <c r="L8" s="39"/>
+      <c r="M8" s="38"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>54</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>82.5</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5">
+        <v>71</v>
+      </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>64</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="12" t="s">
+      <c r="L9" s="39"/>
+      <c r="M9" s="38"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>54</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>82.5</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5">
+        <v>68</v>
+      </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>42</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="12" t="s">
+      <c r="L10" s="39"/>
+      <c r="M10" s="38"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>66</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>91</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5">
+        <v>82</v>
+      </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>49</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="12" t="s">
+      <c r="L11" s="39"/>
+      <c r="M11" s="38"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>52</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>95</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5">
+        <v>71</v>
+      </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>57</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="12" t="s">
+      <c r="L12" s="39"/>
+      <c r="M12" s="38"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>12</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>71</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5">
+        <v>64</v>
+      </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>42</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="12" t="s">
+      <c r="L13" s="39"/>
+      <c r="M13" s="38"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>52</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>95</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5">
+        <v>64</v>
+      </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>46</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="12" t="s">
+      <c r="L14" s="39"/>
+      <c r="M14" s="38"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>54</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>91</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5">
+        <v>88</v>
+      </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>55</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="12" t="s">
+      <c r="L15" s="39"/>
+      <c r="M15" s="38"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>58</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>80.5</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5">
+        <v>97</v>
+      </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>62</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="12" t="s">
+      <c r="L16" s="39"/>
+      <c r="M16" s="38"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>50</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>76</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5">
+        <v>73</v>
+      </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>70</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="12" t="s">
+      <c r="L17" s="39"/>
+      <c r="M17" s="38"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>64</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>92.5</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5">
+        <v>75</v>
+      </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>57</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="12" t="s">
+      <c r="L18" s="39"/>
+      <c r="M18" s="38"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>54</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>91</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5">
+        <v>73</v>
+      </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>77</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="12" t="s">
+      <c r="L19" s="39"/>
+      <c r="M19" s="38"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>66</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>91</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5">
+        <v>83</v>
+      </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>53</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="12" t="s">
+      <c r="L20" s="39"/>
+      <c r="M20" s="38"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>54</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>79</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5">
+        <v>73</v>
+      </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>58</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="12" t="s">
+      <c r="L21" s="39"/>
+      <c r="M21" s="38"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>30</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>92</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5">
+        <v>62</v>
+      </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <v>51</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="12" t="s">
+      <c r="L22" s="39"/>
+      <c r="M22" s="38"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>32</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>89</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5">
+        <v>68</v>
+      </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <v>40</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="12" t="s">
+      <c r="L23" s="39"/>
+      <c r="M23" s="38"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>26</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>84</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5">
+        <v>90</v>
+      </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="10">
+      <c r="G24" s="9">
         <v>64</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="12" t="s">
+      <c r="L24" s="39"/>
+      <c r="M24" s="38"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>26</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <v>84</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5">
+        <v>67</v>
+      </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <v>41</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="12" t="s">
+      <c r="L25" s="39"/>
+      <c r="M25" s="38"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <v>50</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>76</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5">
+        <v>55</v>
+      </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="10">
+      <c r="G26" s="9">
         <v>42</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="12" t="s">
+      <c r="L26" s="39"/>
+      <c r="M26" s="38"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>44</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>85</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5">
+        <v>96</v>
+      </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>61</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="12" t="s">
+      <c r="L27" s="39"/>
+      <c r="M27" s="38"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <v>26</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>84</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="5">
+        <v>71</v>
+      </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <v>51</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="12" t="s">
+      <c r="L28" s="39"/>
+      <c r="M28" s="38"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <v>50</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>79</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5">
+        <v>78</v>
+      </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>51</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="12" t="s">
+      <c r="L29" s="39"/>
+      <c r="M29" s="38"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <v>52</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>95</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="5">
+        <v>69</v>
+      </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <v>41</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="12" t="s">
+      <c r="L30" s="39"/>
+      <c r="M30" s="38"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <v>18</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <v>98</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5">
+        <v>76</v>
+      </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>68</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="12" t="s">
+      <c r="L31" s="39"/>
+      <c r="M31" s="38"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <v>52</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>80</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="5">
+        <v>72</v>
+      </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <v>61</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="12" t="s">
+      <c r="L32" s="39"/>
+      <c r="M32" s="38"/>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <v>50</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <v>79</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5">
+        <v>70</v>
+      </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>62</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="12" t="s">
+      <c r="L33" s="39"/>
+      <c r="M33" s="38"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <v>30</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <v>82</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="5">
+        <v>64</v>
+      </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="10">
+      <c r="G34" s="9">
         <v>55</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="12" t="s">
+      <c r="L34" s="39"/>
+      <c r="M34" s="38"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="9">
         <v>30</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="8">
         <v>82</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5">
+        <v>57</v>
+      </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="10">
+      <c r="G35" s="9">
         <v>45</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="12" t="s">
+      <c r="L35" s="39"/>
+      <c r="M35" s="38"/>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="9">
         <v>70</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>75</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="5">
+        <v>57</v>
+      </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="10">
+      <c r="G36" s="9">
         <v>42</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="12" t="s">
+      <c r="L36" s="39"/>
+      <c r="M36" s="38"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="9">
         <v>36</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>99</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5">
+        <v>70</v>
+      </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="10">
+      <c r="G37" s="9">
         <v>52</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="12" t="s">
+      <c r="L37" s="39"/>
+      <c r="M37" s="38"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="9">
         <v>70</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>75</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="5">
+        <v>62</v>
+      </c>
       <c r="F38" s="5"/>
-      <c r="G38" s="10">
+      <c r="G38" s="9">
         <v>42</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="12" t="s">
+      <c r="L38" s="39"/>
+      <c r="M38" s="38"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="9">
         <v>42</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>86</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5">
+        <v>62</v>
+      </c>
       <c r="F39" s="5"/>
-      <c r="G39" s="10">
+      <c r="G39" s="9">
         <v>67</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="12" t="s">
+      <c r="L39" s="39"/>
+      <c r="M39" s="38"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="9">
         <v>44</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>92</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5">
+        <v>91</v>
+      </c>
       <c r="F40" s="5"/>
-      <c r="G40" s="10">
+      <c r="G40" s="9">
         <v>69</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="12" t="s">
+      <c r="L40" s="39"/>
+      <c r="M40" s="38"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="9">
         <v>64</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>89</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5">
+        <v>91</v>
+      </c>
       <c r="F41" s="5"/>
-      <c r="G41" s="10">
+      <c r="G41" s="9">
         <v>64</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="12" t="s">
+      <c r="L41" s="39"/>
+      <c r="M41" s="38"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="9">
         <v>40</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>75.5</v>
       </c>
-      <c r="E42" s="5"/>
+      <c r="E42" s="5">
+        <v>80</v>
+      </c>
       <c r="F42" s="5"/>
-      <c r="G42" s="10">
+      <c r="G42" s="9">
         <v>67</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="12" t="s">
+      <c r="L42" s="39"/>
+      <c r="M42" s="38"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="9">
         <v>64</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="8">
         <v>88</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="5">
+        <v>47</v>
+      </c>
       <c r="F43" s="5"/>
-      <c r="G43" s="10">
+      <c r="G43" s="9">
         <v>54</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="12" t="s">
+      <c r="L43" s="39"/>
+      <c r="M43" s="38"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="9">
         <v>46</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="8">
         <v>86</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="5">
+        <v>73</v>
+      </c>
       <c r="F44" s="5"/>
-      <c r="G44" s="10">
+      <c r="G44" s="9">
         <v>46</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="12" t="s">
+      <c r="L44" s="39"/>
+      <c r="M44" s="38"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="9">
         <v>34</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="8">
         <v>90</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5">
+        <v>70</v>
+      </c>
       <c r="F45" s="5"/>
-      <c r="G45" s="10">
+      <c r="G45" s="9">
         <v>44</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="12" t="s">
+      <c r="L45" s="39"/>
+      <c r="M45" s="38"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="9">
         <v>40</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>75.5</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="5">
+        <v>74</v>
+      </c>
       <c r="F46" s="5"/>
-      <c r="G46" s="10">
+      <c r="G46" s="9">
         <v>50</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="12" t="s">
+      <c r="L46" s="39"/>
+      <c r="M46" s="38"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="9">
         <v>46</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="8">
         <v>86</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="5">
+        <v>65</v>
+      </c>
       <c r="F47" s="5"/>
-      <c r="G47" s="10">
+      <c r="G47" s="9">
         <v>68</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="12" t="s">
+      <c r="L47" s="39"/>
+      <c r="M47" s="38"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="9">
         <v>18</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>98</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="5">
+        <v>74</v>
+      </c>
       <c r="F48" s="5"/>
-      <c r="G48" s="10">
+      <c r="G48" s="9">
         <v>55</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="12" t="s">
+      <c r="L48" s="39"/>
+      <c r="M48" s="38"/>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="9">
         <v>52</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="8">
         <v>80</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="5">
+        <v>67</v>
+      </c>
       <c r="F49" s="5"/>
-      <c r="G49" s="10">
+      <c r="G49" s="9">
         <v>54</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="12" t="s">
+      <c r="L49" s="39"/>
+      <c r="M49" s="38"/>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="9">
         <v>40</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="8">
         <v>86.5</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="5">
+        <v>63</v>
+      </c>
       <c r="F50" s="5"/>
-      <c r="G50" s="10">
+      <c r="G50" s="9">
         <v>68</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="12" t="s">
+      <c r="L50" s="39"/>
+      <c r="M50" s="38"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="9">
         <v>52</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="8">
         <v>99</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="5">
+        <v>61</v>
+      </c>
       <c r="F51" s="5"/>
-      <c r="G51" s="10">
+      <c r="G51" s="9">
         <v>52</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="12" t="s">
+      <c r="L51" s="39"/>
+      <c r="M51" s="38"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="28" t="s">
+      <c r="B52" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="9">
         <v>52</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>80</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="5">
+        <v>72</v>
+      </c>
       <c r="F52" s="5"/>
-      <c r="G52" s="10">
+      <c r="G52" s="9">
         <v>46</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="12" t="s">
+      <c r="L52" s="39"/>
+      <c r="M52" s="38"/>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="9">
         <v>26</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="8">
         <v>79</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="5">
+        <v>72</v>
+      </c>
       <c r="F53" s="5"/>
-      <c r="G53" s="10">
+      <c r="G53" s="9">
         <v>48</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="12" t="s">
+      <c r="L53" s="39"/>
+      <c r="M53" s="38"/>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="9">
         <v>64</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="8">
         <v>89</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="5">
+        <v>57</v>
+      </c>
       <c r="F54" s="5"/>
-      <c r="G54" s="10">
+      <c r="G54" s="9">
         <v>51</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="12" t="s">
+      <c r="L54" s="39"/>
+      <c r="M54" s="38"/>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="9">
         <v>44</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="8">
         <v>92</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5">
+        <v>78</v>
+      </c>
       <c r="F55" s="5"/>
-      <c r="G55" s="10">
+      <c r="G55" s="9">
         <v>46</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="12" t="s">
+      <c r="L55" s="39"/>
+      <c r="M55" s="38"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="9">
         <v>60</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="8">
         <v>75</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5">
+        <v>51</v>
+      </c>
       <c r="F56" s="5"/>
-      <c r="G56" s="10">
+      <c r="G56" s="9">
         <v>71</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="12" t="s">
+      <c r="L56" s="39"/>
+      <c r="M56" s="38"/>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B57" s="28" t="s">
+      <c r="B57" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="9">
         <v>32</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="8">
         <v>94</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5">
+        <v>68</v>
+      </c>
       <c r="F57" s="5"/>
-      <c r="G57" s="10">
+      <c r="G57" s="9">
         <v>42</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="12" t="s">
+      <c r="L57" s="39"/>
+      <c r="M57" s="38"/>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="28" t="s">
+      <c r="B58" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="9">
         <v>66</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="8">
         <v>68.5</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F58" s="5"/>
-      <c r="G58" s="10">
+      <c r="G58" s="9">
         <v>45</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="7">
         <v>50</v>
       </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="12" t="s">
+      <c r="L58" s="39"/>
+      <c r="M58" s="38"/>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="9">
         <v>54</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="8">
         <v>91</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5">
+        <v>78</v>
+      </c>
       <c r="F59" s="5"/>
-      <c r="G59" s="10">
+      <c r="G59" s="9">
         <v>64</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="12" t="s">
+      <c r="L59" s="39"/>
+      <c r="M59" s="38"/>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="9">
         <v>48</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="8">
         <v>91.5</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5">
+        <v>83</v>
+      </c>
       <c r="F60" s="5"/>
-      <c r="G60" s="10">
+      <c r="G60" s="9">
         <v>53</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="12" t="s">
+      <c r="L60" s="39"/>
+      <c r="M60" s="38"/>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="9">
         <v>48</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="8">
         <v>84.5</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>69</v>
+      </c>
       <c r="F61" s="5"/>
-      <c r="G61" s="10">
+      <c r="G61" s="9">
         <v>48</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="12" t="s">
+      <c r="L61" s="39"/>
+      <c r="M61" s="38"/>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="9">
         <v>54</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="8">
         <v>82.5</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="5">
+        <v>82</v>
+      </c>
       <c r="F62" s="5"/>
-      <c r="G62" s="10">
+      <c r="G62" s="9">
         <v>54</v>
       </c>
-      <c r="H62" s="8">
+      <c r="H62" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="12" t="s">
+      <c r="L62" s="39"/>
+      <c r="M62" s="38"/>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="28" t="s">
+      <c r="B63" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="9">
         <v>60</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="8">
         <v>90</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="5">
+        <v>78</v>
+      </c>
       <c r="F63" s="5"/>
-      <c r="G63" s="10">
+      <c r="G63" s="9">
         <v>66</v>
       </c>
-      <c r="H63" s="8">
+      <c r="H63" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="12" t="s">
+      <c r="L63" s="39"/>
+      <c r="M63" s="38"/>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="28" t="s">
+      <c r="B64" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="9">
         <v>32</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="8">
         <v>89</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="5">
+        <v>65</v>
+      </c>
       <c r="F64" s="5"/>
-      <c r="G64" s="10">
+      <c r="G64" s="9">
         <v>58</v>
       </c>
-      <c r="H64" s="8">
+      <c r="H64" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="12" t="s">
+      <c r="L64" s="39"/>
+      <c r="M64" s="38"/>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="9">
         <v>56</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="8">
         <v>89</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="5">
+        <v>77</v>
+      </c>
       <c r="F65" s="5"/>
-      <c r="G65" s="10">
+      <c r="G65" s="9">
         <v>51</v>
       </c>
-      <c r="H65" s="8">
+      <c r="H65" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="12" t="s">
+      <c r="L65" s="39"/>
+      <c r="M65" s="38"/>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="B66" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="10">
+      <c r="C66" s="9">
         <v>48</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="8">
         <v>57</v>
       </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="5">
+        <v>74</v>
+      </c>
       <c r="F66" s="5"/>
-      <c r="G66" s="10">
+      <c r="G66" s="9">
         <v>51</v>
       </c>
-      <c r="H66" s="8">
+      <c r="H66" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="12" t="s">
+      <c r="L66" s="39"/>
+      <c r="M66" s="38"/>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="28" t="s">
+      <c r="B67" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C67" s="9">
         <v>56</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="8">
         <v>92</v>
       </c>
-      <c r="E67" s="5"/>
+      <c r="E67" s="5">
+        <v>79</v>
+      </c>
       <c r="F67" s="5"/>
-      <c r="G67" s="10">
+      <c r="G67" s="9">
         <v>55</v>
       </c>
-      <c r="H67" s="8">
+      <c r="H67" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="12" t="s">
+      <c r="L67" s="39"/>
+      <c r="M67" s="38"/>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="28" t="s">
+      <c r="B68" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="C68" s="10">
+      <c r="C68" s="9">
         <v>70</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>75</v>
       </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="5">
+        <v>39</v>
+      </c>
       <c r="F68" s="5"/>
-      <c r="G68" s="10">
+      <c r="G68" s="9">
         <v>44</v>
       </c>
-      <c r="H68" s="8">
+      <c r="H68" s="7">
         <v>53.846153799999996</v>
       </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="12" t="s">
+      <c r="L68" s="39"/>
+      <c r="M68" s="38"/>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="A69" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="9">
         <v>44</v>
       </c>
-      <c r="D69" s="9">
+      <c r="D69" s="8">
         <v>91</v>
       </c>
-      <c r="E69" s="5"/>
+      <c r="E69" s="5">
+        <v>58</v>
+      </c>
       <c r="F69" s="5"/>
-      <c r="G69" s="10">
+      <c r="G69" s="9">
         <v>64</v>
       </c>
-      <c r="H69" s="8">
+      <c r="H69" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="12" t="s">
+      <c r="L69" s="39"/>
+      <c r="M69" s="38"/>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="A70" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="28" t="s">
+      <c r="B70" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="9">
         <v>48</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>89.5</v>
       </c>
-      <c r="E70" s="5"/>
+      <c r="E70" s="5">
+        <v>76</v>
+      </c>
       <c r="F70" s="5"/>
-      <c r="G70" s="10">
+      <c r="G70" s="9">
         <v>68</v>
       </c>
-      <c r="H70" s="8">
+      <c r="H70" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="12" t="s">
+      <c r="L70" s="39"/>
+      <c r="M70" s="38"/>
+    </row>
+    <row r="71" spans="1:13">
+      <c r="A71" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="C71" s="10">
+      <c r="C71" s="9">
         <v>34</v>
       </c>
-      <c r="D71" s="9">
+      <c r="D71" s="8">
         <v>90</v>
       </c>
-      <c r="E71" s="5"/>
+      <c r="E71" s="5">
+        <v>80</v>
+      </c>
       <c r="F71" s="5"/>
-      <c r="G71" s="10">
+      <c r="G71" s="9">
         <v>59</v>
       </c>
-      <c r="H71" s="8">
+      <c r="H71" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="12" t="s">
+      <c r="L71" s="39"/>
+      <c r="M71" s="38"/>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B72" s="28" t="s">
+      <c r="B72" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="C72" s="10">
+      <c r="C72" s="9">
         <v>44</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>91.5</v>
       </c>
-      <c r="E72" s="5"/>
+      <c r="E72" s="5">
+        <v>78</v>
+      </c>
       <c r="F72" s="5"/>
-      <c r="G72" s="10">
+      <c r="G72" s="9">
         <v>51</v>
       </c>
-      <c r="H72" s="8">
+      <c r="H72" s="7">
         <v>76.923076899999998</v>
       </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="12" t="s">
+      <c r="L72" s="39"/>
+      <c r="M72" s="38"/>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="C73" s="10">
+      <c r="C73" s="9">
         <v>70</v>
       </c>
-      <c r="D73" s="9">
+      <c r="D73" s="8">
         <v>75</v>
       </c>
-      <c r="E73" s="5"/>
+      <c r="E73" s="5">
+        <v>72</v>
+      </c>
       <c r="F73" s="5"/>
-      <c r="G73" s="10">
+      <c r="G73" s="9">
         <v>46</v>
       </c>
-      <c r="H73" s="8">
+      <c r="H73" s="7">
         <v>57.142857100000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="12" t="s">
+      <c r="L73" s="39"/>
+      <c r="M73" s="38"/>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B74" s="28" t="s">
+      <c r="B74" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C74" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D74" s="9" t="s">
+      <c r="D74" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E74" s="7"/>
+      <c r="E74" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F74" s="5"/>
-      <c r="G74" s="10" t="s">
+      <c r="G74" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="H74" s="8">
+      <c r="H74" s="7">
         <v>7.1428570999999996</v>
       </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="12" t="s">
+      <c r="L74" s="39"/>
+      <c r="M74" s="38"/>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C75" s="10">
+      <c r="C75" s="9">
         <v>52</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="D75" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E75" s="5"/>
+      <c r="E75" s="5">
+        <v>73</v>
+      </c>
       <c r="F75" s="5"/>
-      <c r="G75" s="10">
+      <c r="G75" s="9">
         <v>64</v>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="12" t="s">
+      <c r="L75" s="39"/>
+      <c r="M75" s="38"/>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B76" s="28" t="s">
+      <c r="B76" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="C76" s="10">
+      <c r="C76" s="9">
         <v>48</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="8">
         <v>89.5</v>
       </c>
-      <c r="E76" s="5"/>
+      <c r="E76" s="5">
+        <v>80</v>
+      </c>
       <c r="F76" s="5"/>
-      <c r="G76" s="10">
+      <c r="G76" s="9">
         <v>74</v>
       </c>
-      <c r="H76" s="8">
+      <c r="H76" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="12" t="s">
+      <c r="L76" s="39"/>
+      <c r="M76" s="38"/>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B77" s="28" t="s">
+      <c r="B77" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="9">
         <v>58</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="8">
         <v>68.5</v>
       </c>
-      <c r="E77" s="5"/>
+      <c r="E77" s="5">
+        <v>85</v>
+      </c>
       <c r="F77" s="5"/>
-      <c r="G77" s="10">
+      <c r="G77" s="9">
         <v>48</v>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="12" t="s">
+      <c r="L77" s="39"/>
+      <c r="M77" s="38"/>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B78" s="28" t="s">
+      <c r="B78" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="C78" s="10">
+      <c r="C78" s="9">
         <v>52</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="8">
         <v>99</v>
       </c>
-      <c r="E78" s="5"/>
+      <c r="E78" s="5">
+        <v>52</v>
+      </c>
       <c r="F78" s="5"/>
-      <c r="G78" s="10">
+      <c r="G78" s="9">
         <v>64</v>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="12" t="s">
+      <c r="L78" s="39"/>
+      <c r="M78" s="38"/>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B79" s="28" t="s">
+      <c r="B79" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="C79" s="10">
+      <c r="C79" s="9">
         <v>52</v>
       </c>
-      <c r="D79" s="9">
+      <c r="D79" s="8">
         <v>68</v>
       </c>
-      <c r="E79" s="5"/>
+      <c r="E79" s="5">
+        <v>86</v>
+      </c>
       <c r="F79" s="5"/>
-      <c r="G79" s="10">
+      <c r="G79" s="9">
         <v>62</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="12" t="s">
+      <c r="L79" s="39"/>
+      <c r="M79" s="38"/>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B80" s="28" t="s">
+      <c r="B80" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="C80" s="10">
+      <c r="C80" s="9">
         <v>26</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <v>91</v>
       </c>
-      <c r="E80" s="5"/>
+      <c r="E80" s="5">
+        <v>75</v>
+      </c>
       <c r="F80" s="5"/>
-      <c r="G80" s="10">
+      <c r="G80" s="9">
         <v>64</v>
       </c>
-      <c r="H80" s="8">
+      <c r="H80" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="12" t="s">
+      <c r="L80" s="39"/>
+      <c r="M80" s="38"/>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="9">
         <v>56</v>
       </c>
-      <c r="D81" s="9">
+      <c r="D81" s="8">
         <v>92</v>
       </c>
-      <c r="E81" s="5"/>
+      <c r="E81" s="5">
+        <v>85</v>
+      </c>
       <c r="F81" s="5"/>
-      <c r="G81" s="10">
+      <c r="G81" s="9">
         <v>67</v>
       </c>
-      <c r="H81" s="8">
+      <c r="H81" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="12" t="s">
+      <c r="L81" s="39"/>
+      <c r="M81" s="38"/>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B82" s="28" t="s">
+      <c r="B82" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="C82" s="10">
+      <c r="C82" s="9">
         <v>34</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="8">
         <v>90</v>
       </c>
-      <c r="E82" s="5"/>
+      <c r="E82" s="5">
+        <v>60</v>
+      </c>
       <c r="F82" s="5"/>
-      <c r="G82" s="10">
+      <c r="G82" s="9">
         <v>46</v>
       </c>
-      <c r="H82" s="8">
+      <c r="H82" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="12" t="s">
+      <c r="L82" s="39"/>
+      <c r="M82" s="38"/>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B83" s="28" t="s">
+      <c r="B83" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="9">
         <v>44</v>
       </c>
-      <c r="D83" s="9">
+      <c r="D83" s="8">
         <v>91</v>
       </c>
-      <c r="E83" s="5"/>
+      <c r="E83" s="5">
+        <v>62</v>
+      </c>
       <c r="F83" s="5"/>
-      <c r="G83" s="10">
+      <c r="G83" s="9">
         <v>61</v>
       </c>
-      <c r="H83" s="8">
+      <c r="H83" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="12" t="s">
+      <c r="L83" s="39"/>
+      <c r="M83" s="38"/>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B84" s="28" t="s">
+      <c r="B84" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="C84" s="10">
+      <c r="C84" s="9">
         <v>34</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="8">
         <v>90</v>
       </c>
-      <c r="E84" s="5"/>
+      <c r="E84" s="5">
+        <v>79</v>
+      </c>
       <c r="F84" s="5"/>
-      <c r="G84" s="10">
+      <c r="G84" s="9">
         <v>50</v>
       </c>
-      <c r="H84" s="8">
+      <c r="H84" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="12" t="s">
+      <c r="L84" s="39"/>
+      <c r="M84" s="38"/>
+    </row>
+    <row r="85" spans="1:13">
+      <c r="A85" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B85" s="28" t="s">
+      <c r="B85" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="9">
         <v>48</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="8">
         <v>89.5</v>
       </c>
-      <c r="E85" s="5"/>
+      <c r="E85" s="5">
+        <v>85</v>
+      </c>
       <c r="F85" s="5"/>
-      <c r="G85" s="10">
+      <c r="G85" s="9">
         <v>71</v>
       </c>
-      <c r="H85" s="8">
+      <c r="H85" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="12" t="s">
+      <c r="L85" s="39"/>
+      <c r="M85" s="38"/>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="A86" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B86" s="28" t="s">
+      <c r="B86" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="D86" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E86" s="5"/>
+      <c r="E86" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F86" s="5"/>
-      <c r="G86" s="10" t="s">
+      <c r="G86" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="H86" s="8">
+      <c r="H86" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="12" t="s">
+      <c r="L86" s="39"/>
+      <c r="M86" s="38"/>
+    </row>
+    <row r="87" spans="1:13">
+      <c r="A87" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B87" s="28" t="s">
+      <c r="B87" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="9">
         <v>40</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="8">
         <v>75.5</v>
       </c>
-      <c r="E87" s="5"/>
+      <c r="E87" s="5">
+        <v>71</v>
+      </c>
       <c r="F87" s="5"/>
-      <c r="G87" s="10">
+      <c r="G87" s="9">
         <v>46</v>
       </c>
-      <c r="H87" s="8">
+      <c r="H87" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="12" t="s">
+      <c r="L87" s="39"/>
+      <c r="M87" s="38"/>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B88" s="28" t="s">
+      <c r="B88" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="C88" s="10">
+      <c r="C88" s="9">
         <v>52</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="8">
         <v>88</v>
       </c>
-      <c r="E88" s="5"/>
+      <c r="E88" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F88" s="5"/>
-      <c r="G88" s="10">
+      <c r="G88" s="9">
         <v>58</v>
       </c>
-      <c r="H88" s="8">
+      <c r="H88" s="7">
         <v>35.714285699999998</v>
       </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="12" t="s">
+      <c r="L88" s="39"/>
+      <c r="M88" s="38"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B89" s="28" t="s">
+      <c r="B89" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="9">
         <v>58</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="8">
         <v>80.5</v>
       </c>
-      <c r="E89" s="5"/>
+      <c r="E89" s="5">
+        <v>55</v>
+      </c>
       <c r="F89" s="5"/>
-      <c r="G89" s="10">
+      <c r="G89" s="9">
         <v>51</v>
       </c>
-      <c r="H89" s="8">
+      <c r="H89" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="12" t="s">
+      <c r="L89" s="39"/>
+      <c r="M89" s="38"/>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="B90" s="28" t="s">
+      <c r="B90" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C90" s="9">
         <v>46</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="8">
         <v>86</v>
       </c>
-      <c r="E90" s="5"/>
+      <c r="E90" s="5">
+        <v>59</v>
+      </c>
       <c r="F90" s="5"/>
-      <c r="G90" s="10">
+      <c r="G90" s="9">
         <v>52</v>
       </c>
-      <c r="H90" s="8">
+      <c r="H90" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="12" t="s">
+      <c r="L90" s="39"/>
+      <c r="M90" s="38"/>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="B91" s="28" t="s">
+      <c r="B91" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="C91" s="10">
+      <c r="C91" s="9">
         <v>44</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="8">
         <v>82</v>
       </c>
-      <c r="E91" s="5"/>
+      <c r="E91" s="5">
+        <v>67</v>
+      </c>
       <c r="F91" s="5"/>
-      <c r="G91" s="10">
+      <c r="G91" s="9">
         <v>62</v>
       </c>
-      <c r="H91" s="8">
+      <c r="H91" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="12" t="s">
+      <c r="L91" s="39"/>
+      <c r="M91" s="38"/>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B92" s="28" t="s">
+      <c r="B92" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="C92" s="10">
+      <c r="C92" s="9">
         <v>38</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="8">
         <v>90</v>
       </c>
-      <c r="E92" s="5"/>
+      <c r="E92" s="5">
+        <v>85</v>
+      </c>
       <c r="F92" s="5"/>
-      <c r="G92" s="10">
+      <c r="G92" s="9">
         <v>56</v>
       </c>
-      <c r="H92" s="8">
+      <c r="H92" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="12" t="s">
+      <c r="L92" s="39"/>
+      <c r="M92" s="38"/>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="A93" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="C93" s="10">
+      <c r="C93" s="9">
         <v>44</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="8">
         <v>53</v>
       </c>
-      <c r="E93" s="5"/>
+      <c r="E93" s="5">
+        <v>69</v>
+      </c>
       <c r="F93" s="5"/>
-      <c r="G93" s="10">
+      <c r="G93" s="9">
         <v>48</v>
       </c>
-      <c r="H93" s="8">
+      <c r="H93" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="12" t="s">
+      <c r="L93" s="39"/>
+      <c r="M93" s="38"/>
+    </row>
+    <row r="94" spans="1:13">
+      <c r="A94" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="B94" s="28" t="s">
+      <c r="B94" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="C94" s="10">
+      <c r="C94" s="9">
         <v>44</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="8">
         <v>53</v>
       </c>
-      <c r="E94" s="5"/>
+      <c r="E94" s="5">
+        <v>80</v>
+      </c>
       <c r="F94" s="5"/>
-      <c r="G94" s="10">
+      <c r="G94" s="9">
         <v>49</v>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="7">
         <v>50</v>
       </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="12" t="s">
+      <c r="L94" s="39"/>
+      <c r="M94" s="38"/>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="C95" s="10">
+      <c r="C95" s="9">
         <v>70</v>
       </c>
-      <c r="D95" s="9">
+      <c r="D95" s="8">
         <v>82</v>
       </c>
-      <c r="E95" s="5"/>
+      <c r="E95" s="5">
+        <v>67</v>
+      </c>
       <c r="F95" s="5"/>
-      <c r="G95" s="10">
+      <c r="G95" s="9">
         <v>55</v>
       </c>
-      <c r="H95" s="8">
+      <c r="H95" s="7">
         <v>35.714285699999998</v>
       </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="12" t="s">
+      <c r="L95" s="39"/>
+      <c r="M95" s="38"/>
+    </row>
+    <row r="96" spans="1:13">
+      <c r="A96" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B96" s="28" t="s">
+      <c r="B96" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="C96" s="10">
+      <c r="C96" s="9">
         <v>60</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="8">
         <v>75</v>
       </c>
-      <c r="E96" s="5"/>
+      <c r="E96" s="5">
+        <v>68</v>
+      </c>
       <c r="F96" s="5"/>
-      <c r="G96" s="10">
+      <c r="G96" s="9">
         <v>46</v>
       </c>
-      <c r="H96" s="8">
+      <c r="H96" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="12" t="s">
+      <c r="L96" s="39"/>
+      <c r="M96" s="38"/>
+    </row>
+    <row r="97" spans="1:13">
+      <c r="A97" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B97" s="28" t="s">
+      <c r="B97" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C97" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D97" s="9" t="s">
+      <c r="D97" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E97" s="5"/>
+      <c r="E97" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F97" s="5"/>
-      <c r="G97" s="10" t="s">
+      <c r="G97" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="H97" s="8">
+      <c r="H97" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="12" t="s">
+      <c r="L97" s="39"/>
+      <c r="M97" s="38"/>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="A98" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B98" s="28" t="s">
+      <c r="B98" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="C98" s="10">
+      <c r="C98" s="9">
         <v>60</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="8">
         <v>75</v>
       </c>
-      <c r="E98" s="5"/>
+      <c r="E98" s="5">
+        <v>75</v>
+      </c>
       <c r="F98" s="5"/>
-      <c r="G98" s="10">
+      <c r="G98" s="9">
         <v>65</v>
       </c>
-      <c r="H98" s="8">
+      <c r="H98" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="12" t="s">
+      <c r="L98" s="39"/>
+      <c r="M98" s="38"/>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="C99" s="10">
+      <c r="C99" s="9">
         <v>38</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="8">
         <v>90</v>
       </c>
-      <c r="E99" s="5"/>
+      <c r="E99" s="5">
+        <v>64</v>
+      </c>
       <c r="F99" s="5"/>
-      <c r="G99" s="10">
+      <c r="G99" s="9">
         <v>61</v>
       </c>
-      <c r="H99" s="8">
+      <c r="H99" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="11" t="s">
+      <c r="L99" s="39"/>
+      <c r="M99" s="38"/>
+    </row>
+    <row r="100" spans="1:13">
+      <c r="A100" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B100" s="27" t="s">
+      <c r="B100" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="C100" s="10">
+      <c r="C100" s="9">
         <v>60</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="8">
         <v>82</v>
       </c>
-      <c r="E100" s="5"/>
+      <c r="E100" s="5">
+        <v>74</v>
+      </c>
       <c r="F100" s="5"/>
-      <c r="G100" s="10">
+      <c r="G100" s="9">
         <v>36</v>
       </c>
-      <c r="H100" s="8">
+      <c r="H100" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="11" t="s">
+      <c r="L100" s="39"/>
+      <c r="M100" s="38"/>
+    </row>
+    <row r="101" spans="1:13">
+      <c r="A101" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B101" s="27" t="s">
+      <c r="B101" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C101" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="8">
         <v>80.5</v>
       </c>
-      <c r="E101" s="5"/>
+      <c r="E101" s="5">
+        <v>58</v>
+      </c>
       <c r="F101" s="5"/>
-      <c r="G101" s="10">
+      <c r="G101" s="9">
         <v>64</v>
       </c>
-      <c r="H101" s="8">
+      <c r="H101" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="11" t="s">
+      <c r="L101" s="39"/>
+      <c r="M101" s="38"/>
+    </row>
+    <row r="102" spans="1:13">
+      <c r="A102" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B102" s="27" t="s">
+      <c r="B102" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="C102" s="10">
+      <c r="C102" s="9">
         <v>42</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <v>86</v>
       </c>
-      <c r="E102" s="5"/>
+      <c r="E102" s="5">
+        <v>53</v>
+      </c>
       <c r="F102" s="5"/>
-      <c r="G102" s="10">
+      <c r="G102" s="9">
         <v>45</v>
       </c>
-      <c r="H102" s="8">
+      <c r="H102" s="7">
         <v>42.857142899999999</v>
       </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="11" t="s">
+      <c r="L102" s="39"/>
+      <c r="M102" s="38"/>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="A103" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B103" s="27" t="s">
+      <c r="B103" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="C103" s="10" t="s">
+      <c r="C103" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D103" s="9" t="s">
+      <c r="D103" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E103" s="7"/>
+      <c r="E103" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F103" s="5"/>
-      <c r="G103" s="10" t="s">
+      <c r="G103" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="H103" s="8">
+      <c r="H103" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="11" t="s">
+      <c r="L103" s="39"/>
+      <c r="M103" s="38"/>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="C104" s="10">
+      <c r="C104" s="9">
         <v>64</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="8">
         <v>88</v>
       </c>
-      <c r="E104" s="5"/>
+      <c r="E104" s="5">
+        <v>91</v>
+      </c>
       <c r="F104" s="5"/>
-      <c r="G104" s="10">
+      <c r="G104" s="9">
         <v>69</v>
       </c>
-      <c r="H104" s="8">
+      <c r="H104" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="11" t="s">
+      <c r="L104" s="39"/>
+      <c r="M104" s="38"/>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B105" s="27" t="s">
+      <c r="B105" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="C105" s="10">
+      <c r="C105" s="9">
         <v>28</v>
       </c>
-      <c r="D105" s="9">
+      <c r="D105" s="8">
         <v>88</v>
       </c>
-      <c r="E105" s="5"/>
+      <c r="E105" s="5">
+        <v>83</v>
+      </c>
       <c r="F105" s="5"/>
-      <c r="G105" s="10">
+      <c r="G105" s="9">
         <v>35</v>
       </c>
-      <c r="H105" s="8">
+      <c r="H105" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="11" t="s">
+      <c r="L105" s="39"/>
+      <c r="M105" s="38"/>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B106" s="27" t="s">
+      <c r="B106" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="C106" s="10">
+      <c r="C106" s="9">
         <v>46</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="8">
         <v>86</v>
       </c>
-      <c r="E106" s="5"/>
+      <c r="E106" s="5">
+        <v>48</v>
+      </c>
       <c r="F106" s="5"/>
-      <c r="G106" s="10">
+      <c r="G106" s="9">
         <v>57</v>
       </c>
-      <c r="H106" s="8">
+      <c r="H106" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="11" t="s">
+      <c r="L106" s="39"/>
+      <c r="M106" s="38"/>
+    </row>
+    <row r="107" spans="1:13">
+      <c r="A107" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B107" s="27" t="s">
+      <c r="B107" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C107" s="10">
+      <c r="C107" s="9">
         <v>46</v>
       </c>
-      <c r="D107" s="9">
+      <c r="D107" s="8">
         <v>91.5</v>
       </c>
-      <c r="E107" s="5"/>
+      <c r="E107" s="5">
+        <v>71</v>
+      </c>
       <c r="F107" s="5"/>
-      <c r="G107" s="10">
+      <c r="G107" s="9">
         <v>55</v>
       </c>
-      <c r="H107" s="8">
+      <c r="H107" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="11" t="s">
+      <c r="L107" s="39"/>
+      <c r="M107" s="38"/>
+    </row>
+    <row r="108" spans="1:13">
+      <c r="A108" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="C108" s="10">
+      <c r="C108" s="9">
         <v>18</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="8">
         <v>98</v>
       </c>
-      <c r="E108" s="5"/>
+      <c r="E108" s="5">
+        <v>86</v>
+      </c>
       <c r="F108" s="5"/>
-      <c r="G108" s="10">
+      <c r="G108" s="9">
         <v>63</v>
       </c>
-      <c r="H108" s="8">
+      <c r="H108" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="11" t="s">
+      <c r="L108" s="39"/>
+      <c r="M108" s="38"/>
+    </row>
+    <row r="109" spans="1:13">
+      <c r="A109" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="C109" s="10">
+      <c r="C109" s="9">
         <v>12</v>
       </c>
-      <c r="D109" s="9">
+      <c r="D109" s="8">
         <v>71</v>
       </c>
-      <c r="E109" s="5"/>
+      <c r="E109" s="5">
+        <v>69</v>
+      </c>
       <c r="F109" s="5"/>
-      <c r="G109" s="10">
+      <c r="G109" s="9">
         <v>47</v>
       </c>
-      <c r="H109" s="8">
+      <c r="H109" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="11" t="s">
+      <c r="L109" s="39"/>
+      <c r="M109" s="38"/>
+    </row>
+    <row r="110" spans="1:13">
+      <c r="A110" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B110" s="27" t="s">
+      <c r="B110" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C110" s="10">
+      <c r="C110" s="9">
         <v>56</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="8">
         <v>92</v>
       </c>
-      <c r="E110" s="5"/>
+      <c r="E110" s="5">
+        <v>81</v>
+      </c>
       <c r="F110" s="5"/>
-      <c r="G110" s="10">
+      <c r="G110" s="9">
         <v>70</v>
       </c>
-      <c r="H110" s="8">
+      <c r="H110" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="11" t="s">
+      <c r="L110" s="39"/>
+      <c r="M110" s="38"/>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="A111" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="10">
+      <c r="C111" s="9">
         <v>52</v>
       </c>
-      <c r="D111" s="9">
+      <c r="D111" s="8">
         <v>99</v>
       </c>
-      <c r="E111" s="5"/>
+      <c r="E111" s="5">
+        <v>52</v>
+      </c>
       <c r="F111" s="5"/>
-      <c r="G111" s="10">
+      <c r="G111" s="9">
         <v>44</v>
       </c>
-      <c r="H111" s="8">
+      <c r="H111" s="7">
         <v>57.142857100000001</v>
       </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="11" t="s">
+      <c r="L111" s="39"/>
+      <c r="M111" s="38"/>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="C112" s="10">
+      <c r="C112" s="9">
         <v>50</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="8">
         <v>79</v>
       </c>
-      <c r="E112" s="5"/>
+      <c r="E112" s="5">
+        <v>72</v>
+      </c>
       <c r="F112" s="5"/>
-      <c r="G112" s="10">
+      <c r="G112" s="9">
         <v>49</v>
       </c>
-      <c r="H112" s="8">
+      <c r="H112" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="11" t="s">
+      <c r="L112" s="39"/>
+      <c r="M112" s="38"/>
+    </row>
+    <row r="113" spans="1:13">
+      <c r="A113" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B113" s="27" t="s">
+      <c r="B113" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C113" s="10">
+      <c r="C113" s="9">
         <v>34</v>
       </c>
-      <c r="D113" s="9">
+      <c r="D113" s="8">
         <v>68</v>
       </c>
-      <c r="E113" s="5"/>
+      <c r="E113" s="5">
+        <v>62</v>
+      </c>
       <c r="F113" s="5"/>
-      <c r="G113" s="10">
+      <c r="G113" s="9">
         <v>58</v>
       </c>
-      <c r="H113" s="8">
+      <c r="H113" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="11" t="s">
+      <c r="L113" s="39"/>
+      <c r="M113" s="38"/>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="A114" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="10">
+      <c r="C114" s="9">
         <v>48</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="8">
         <v>96</v>
       </c>
-      <c r="E114" s="5"/>
+      <c r="E114" s="5">
+        <v>79</v>
+      </c>
       <c r="F114" s="5"/>
-      <c r="G114" s="10">
+      <c r="G114" s="9">
         <v>60</v>
       </c>
-      <c r="H114" s="8">
+      <c r="H114" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="11" t="s">
+      <c r="L114" s="39"/>
+      <c r="M114" s="38"/>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B115" s="27" t="s">
+      <c r="B115" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="C115" s="10">
+      <c r="C115" s="9">
         <v>40</v>
       </c>
-      <c r="D115" s="9">
+      <c r="D115" s="8">
         <v>86.5</v>
       </c>
-      <c r="E115" s="5"/>
+      <c r="E115" s="5">
+        <v>64</v>
+      </c>
       <c r="F115" s="5"/>
-      <c r="G115" s="10">
+      <c r="G115" s="9">
         <v>58</v>
       </c>
-      <c r="H115" s="8">
+      <c r="H115" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="11" t="s">
+      <c r="L115" s="39"/>
+      <c r="M115" s="38"/>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="10">
+      <c r="C116" s="9">
         <v>48</v>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="8">
         <v>96</v>
       </c>
-      <c r="E116" s="5"/>
+      <c r="E116" s="5">
+        <v>62</v>
+      </c>
       <c r="F116" s="5"/>
-      <c r="G116" s="10">
+      <c r="G116" s="9">
         <v>51</v>
       </c>
-      <c r="H116" s="8">
+      <c r="H116" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="11" t="s">
+      <c r="L116" s="39"/>
+      <c r="M116" s="38"/>
+    </row>
+    <row r="117" spans="1:13">
+      <c r="A117" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B117" s="27" t="s">
+      <c r="B117" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C117" s="10">
+      <c r="C117" s="9">
         <v>32</v>
       </c>
-      <c r="D117" s="9">
+      <c r="D117" s="8">
         <v>94</v>
       </c>
-      <c r="E117" s="5"/>
+      <c r="E117" s="5">
+        <v>86</v>
+      </c>
       <c r="F117" s="5"/>
-      <c r="G117" s="10">
+      <c r="G117" s="9">
         <v>58</v>
       </c>
-      <c r="H117" s="8">
+      <c r="H117" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="11" t="s">
+      <c r="L117" s="39"/>
+      <c r="M117" s="38"/>
+    </row>
+    <row r="118" spans="1:13">
+      <c r="A118" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B118" s="27" t="s">
+      <c r="B118" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="10">
+      <c r="C118" s="9">
         <v>38</v>
       </c>
-      <c r="D118" s="9">
+      <c r="D118" s="8">
         <v>90</v>
       </c>
-      <c r="E118" s="5"/>
+      <c r="E118" s="5">
+        <v>64</v>
+      </c>
       <c r="F118" s="5"/>
-      <c r="G118" s="10">
+      <c r="G118" s="9">
         <v>58</v>
       </c>
-      <c r="H118" s="8">
+      <c r="H118" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="11" t="s">
+      <c r="L118" s="39"/>
+      <c r="M118" s="38"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B119" s="27" t="s">
+      <c r="B119" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="C119" s="10">
+      <c r="C119" s="9">
         <v>28</v>
       </c>
-      <c r="D119" s="9">
+      <c r="D119" s="8">
         <v>88</v>
       </c>
-      <c r="E119" s="5"/>
+      <c r="E119" s="5">
+        <v>75</v>
+      </c>
       <c r="F119" s="5"/>
-      <c r="G119" s="10">
+      <c r="G119" s="9">
         <v>38</v>
       </c>
-      <c r="H119" s="8">
+      <c r="H119" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="11" t="s">
+      <c r="L119" s="39"/>
+      <c r="M119" s="38"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B120" s="27" t="s">
+      <c r="B120" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C120" s="10">
+      <c r="C120" s="9">
         <v>48</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="8">
         <v>96</v>
       </c>
-      <c r="E120" s="5"/>
+      <c r="E120" s="5">
+        <v>69</v>
+      </c>
       <c r="F120" s="5"/>
-      <c r="G120" s="10">
+      <c r="G120" s="9">
         <v>60</v>
       </c>
-      <c r="H120" s="8">
+      <c r="H120" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="11" t="s">
+      <c r="L120" s="39"/>
+      <c r="M120" s="38"/>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B121" s="27" t="s">
+      <c r="B121" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C121" s="10">
+      <c r="C121" s="9">
         <v>50</v>
       </c>
-      <c r="D121" s="9">
+      <c r="D121" s="8">
         <v>76</v>
       </c>
-      <c r="E121" s="5"/>
+      <c r="E121" s="5">
+        <v>66</v>
+      </c>
       <c r="F121" s="5"/>
-      <c r="G121" s="10">
+      <c r="G121" s="9">
         <v>43</v>
       </c>
-      <c r="H121" s="8">
+      <c r="H121" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="11" t="s">
+      <c r="L121" s="39"/>
+      <c r="M121" s="38"/>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B122" s="27" t="s">
+      <c r="B122" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="C122" s="10">
+      <c r="C122" s="9">
         <v>58</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="8">
         <v>80.5</v>
       </c>
-      <c r="E122" s="5"/>
+      <c r="E122" s="5">
+        <v>54</v>
+      </c>
       <c r="F122" s="5"/>
-      <c r="G122" s="10">
+      <c r="G122" s="9">
         <v>44</v>
       </c>
-      <c r="H122" s="8">
+      <c r="H122" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="11" t="s">
+      <c r="L122" s="39"/>
+      <c r="M122" s="38"/>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B123" s="27" t="s">
+      <c r="B123" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C123" s="10">
+      <c r="C123" s="9">
         <v>40</v>
       </c>
-      <c r="D123" s="9">
+      <c r="D123" s="8">
         <v>86.5</v>
       </c>
-      <c r="E123" s="5"/>
+      <c r="E123" s="5">
+        <v>65</v>
+      </c>
       <c r="F123" s="5"/>
-      <c r="G123" s="10">
+      <c r="G123" s="9">
         <v>61</v>
       </c>
-      <c r="H123" s="8">
+      <c r="H123" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="11" t="s">
+      <c r="L123" s="39"/>
+      <c r="M123" s="38"/>
+    </row>
+    <row r="124" spans="1:13">
+      <c r="A124" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B124" s="27" t="s">
+      <c r="B124" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="C124" s="10">
+      <c r="C124" s="9">
         <v>40</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="8">
         <v>89</v>
       </c>
-      <c r="E124" s="5"/>
+      <c r="E124" s="5">
+        <v>60</v>
+      </c>
       <c r="F124" s="5"/>
-      <c r="G124" s="10">
+      <c r="G124" s="9">
         <v>43</v>
       </c>
-      <c r="H124" s="8">
+      <c r="H124" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="11" t="s">
+      <c r="L124" s="39"/>
+      <c r="M124" s="38"/>
+    </row>
+    <row r="125" spans="1:13">
+      <c r="A125" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B125" s="27" t="s">
+      <c r="B125" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="C125" s="10">
+      <c r="C125" s="9">
         <v>46</v>
       </c>
-      <c r="D125" s="9">
+      <c r="D125" s="8">
         <v>86</v>
       </c>
-      <c r="E125" s="5"/>
+      <c r="E125" s="5">
+        <v>88</v>
+      </c>
       <c r="F125" s="5"/>
-      <c r="G125" s="10">
+      <c r="G125" s="9">
         <v>42</v>
       </c>
-      <c r="H125" s="8">
+      <c r="H125" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="11" t="s">
+      <c r="L125" s="39"/>
+      <c r="M125" s="38"/>
+    </row>
+    <row r="126" spans="1:13">
+      <c r="A126" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B126" s="27" t="s">
+      <c r="B126" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="C126" s="10">
+      <c r="C126" s="9">
         <v>54</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="8">
         <v>91</v>
       </c>
-      <c r="E126" s="5"/>
+      <c r="E126" s="5">
+        <v>67</v>
+      </c>
       <c r="F126" s="5"/>
-      <c r="G126" s="10">
+      <c r="G126" s="9">
         <v>47</v>
       </c>
-      <c r="H126" s="8">
+      <c r="H126" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="11" t="s">
+      <c r="L126" s="39"/>
+      <c r="M126" s="38"/>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B127" s="27" t="s">
+      <c r="B127" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="10">
+      <c r="C127" s="9">
         <v>38</v>
       </c>
-      <c r="D127" s="9">
+      <c r="D127" s="8">
         <v>90</v>
       </c>
-      <c r="E127" s="5"/>
+      <c r="E127" s="5">
+        <v>90</v>
+      </c>
       <c r="F127" s="5"/>
-      <c r="G127" s="10">
+      <c r="G127" s="9">
         <v>57</v>
       </c>
-      <c r="H127" s="8">
+      <c r="H127" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="11" t="s">
+      <c r="L127" s="39"/>
+      <c r="M127" s="38"/>
+    </row>
+    <row r="128" spans="1:13">
+      <c r="A128" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B128" s="27" t="s">
+      <c r="B128" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="C128" s="10">
+      <c r="C128" s="9">
         <v>70</v>
       </c>
-      <c r="D128" s="9">
+      <c r="D128" s="8">
         <v>86</v>
       </c>
-      <c r="E128" s="5"/>
+      <c r="E128" s="5">
+        <v>69</v>
+      </c>
       <c r="F128" s="5"/>
-      <c r="G128" s="10">
+      <c r="G128" s="9">
         <v>63</v>
       </c>
-      <c r="H128" s="8">
+      <c r="H128" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="129" spans="1:8">
-      <c r="A129" s="11" t="s">
+      <c r="L128" s="39"/>
+      <c r="M128" s="38"/>
+    </row>
+    <row r="129" spans="1:13">
+      <c r="A129" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="B129" s="27" t="s">
+      <c r="B129" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="C129" s="10">
+      <c r="C129" s="9">
         <v>30</v>
       </c>
-      <c r="D129" s="9">
+      <c r="D129" s="8">
         <v>94</v>
       </c>
-      <c r="E129" s="5"/>
+      <c r="E129" s="5">
+        <v>78</v>
+      </c>
       <c r="F129" s="5"/>
-      <c r="G129" s="10">
+      <c r="G129" s="9">
         <v>35</v>
       </c>
-      <c r="H129" s="8">
+      <c r="H129" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="130" spans="1:8">
-      <c r="A130" s="11" t="s">
+      <c r="L129" s="39"/>
+      <c r="M129" s="38"/>
+    </row>
+    <row r="130" spans="1:13">
+      <c r="A130" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="C130" s="10">
+      <c r="C130" s="9">
         <v>50</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="8">
         <v>94</v>
       </c>
-      <c r="E130" s="5"/>
+      <c r="E130" s="5">
+        <v>67</v>
+      </c>
       <c r="F130" s="5"/>
-      <c r="G130" s="10">
+      <c r="G130" s="9">
         <v>38</v>
       </c>
-      <c r="H130" s="8">
+      <c r="H130" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="131" spans="1:8">
-      <c r="A131" s="11" t="s">
+      <c r="L130" s="39"/>
+      <c r="M130" s="38"/>
+    </row>
+    <row r="131" spans="1:13">
+      <c r="A131" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="B131" s="27" t="s">
+      <c r="B131" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="C131" s="10">
+      <c r="C131" s="9">
         <v>42</v>
       </c>
-      <c r="D131" s="9">
+      <c r="D131" s="8">
         <v>86</v>
       </c>
-      <c r="E131" s="5"/>
+      <c r="E131" s="5">
+        <v>58</v>
+      </c>
       <c r="F131" s="5"/>
-      <c r="G131" s="10">
+      <c r="G131" s="9">
         <v>58</v>
       </c>
-      <c r="H131" s="8">
+      <c r="H131" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="132" spans="1:8">
-      <c r="A132" s="11" t="s">
+      <c r="L131" s="39"/>
+      <c r="M131" s="38"/>
+    </row>
+    <row r="132" spans="1:13">
+      <c r="A132" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="B132" s="27" t="s">
+      <c r="B132" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="C132" s="10">
+      <c r="C132" s="9">
         <v>70</v>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="8">
         <v>86</v>
       </c>
-      <c r="E132" s="5"/>
+      <c r="E132" s="5">
+        <v>71</v>
+      </c>
       <c r="F132" s="5"/>
-      <c r="G132" s="10">
+      <c r="G132" s="9">
         <v>60</v>
       </c>
-      <c r="H132" s="8">
+      <c r="H132" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="11" t="s">
+      <c r="L132" s="39"/>
+      <c r="M132" s="38"/>
+    </row>
+    <row r="133" spans="1:13">
+      <c r="A133" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B133" s="27" t="s">
+      <c r="B133" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="C133" s="10">
+      <c r="C133" s="9">
         <v>48</v>
       </c>
-      <c r="D133" s="9">
+      <c r="D133" s="8">
         <v>57</v>
       </c>
-      <c r="E133" s="5"/>
+      <c r="E133" s="5">
+        <v>80</v>
+      </c>
       <c r="F133" s="5"/>
-      <c r="G133" s="10">
+      <c r="G133" s="9">
         <v>61</v>
       </c>
-      <c r="H133" s="8">
+      <c r="H133" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" s="11" t="s">
+      <c r="L133" s="39"/>
+      <c r="M133" s="38"/>
+    </row>
+    <row r="134" spans="1:13">
+      <c r="A134" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B134" s="27" t="s">
+      <c r="B134" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="C134" s="10">
+      <c r="C134" s="9">
         <v>44</v>
       </c>
-      <c r="D134" s="9">
+      <c r="D134" s="8">
         <v>85</v>
       </c>
-      <c r="E134" s="5"/>
+      <c r="E134" s="5">
+        <v>54</v>
+      </c>
       <c r="F134" s="5"/>
-      <c r="G134" s="10">
+      <c r="G134" s="9">
         <v>58</v>
       </c>
-      <c r="H134" s="8">
+      <c r="H134" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="135" spans="1:8">
-      <c r="A135" s="11" t="s">
+      <c r="L134" s="39"/>
+      <c r="M134" s="38"/>
+    </row>
+    <row r="135" spans="1:13">
+      <c r="A135" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B135" s="27" t="s">
+      <c r="B135" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="C135" s="10">
+      <c r="C135" s="9">
         <v>48</v>
       </c>
-      <c r="D135" s="9">
+      <c r="D135" s="8">
         <v>84.5</v>
       </c>
-      <c r="E135" s="5"/>
+      <c r="E135" s="5">
+        <v>86</v>
+      </c>
       <c r="F135" s="5"/>
-      <c r="G135" s="10">
+      <c r="G135" s="9">
         <v>62</v>
       </c>
-      <c r="H135" s="8">
+      <c r="H135" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" s="11" t="s">
+      <c r="L135" s="39"/>
+      <c r="M135" s="38"/>
+    </row>
+    <row r="136" spans="1:13">
+      <c r="A136" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B136" s="27" t="s">
+      <c r="B136" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="C136" s="10">
+      <c r="C136" s="9">
         <v>40</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="8">
         <v>66.5</v>
       </c>
-      <c r="E136" s="5"/>
+      <c r="E136" s="5">
+        <v>78</v>
+      </c>
       <c r="F136" s="5"/>
-      <c r="G136" s="10">
+      <c r="G136" s="9">
         <v>53</v>
       </c>
-      <c r="H136" s="8">
+      <c r="H136" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="137" spans="1:8">
-      <c r="A137" s="11" t="s">
+      <c r="L136" s="39"/>
+      <c r="M136" s="38"/>
+    </row>
+    <row r="137" spans="1:13">
+      <c r="A137" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B137" s="27" t="s">
+      <c r="B137" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="C137" s="10">
+      <c r="C137" s="9">
         <v>66</v>
       </c>
-      <c r="D137" s="9">
+      <c r="D137" s="8">
         <v>91</v>
       </c>
-      <c r="E137" s="5"/>
+      <c r="E137" s="5">
+        <v>89</v>
+      </c>
       <c r="F137" s="5"/>
-      <c r="G137" s="10">
+      <c r="G137" s="9">
         <v>30</v>
       </c>
-      <c r="H137" s="8">
+      <c r="H137" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="138" spans="1:8">
-      <c r="A138" s="11" t="s">
+      <c r="L137" s="39"/>
+      <c r="M137" s="38"/>
+    </row>
+    <row r="138" spans="1:13">
+      <c r="A138" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B138" s="27" t="s">
+      <c r="B138" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="C138" s="10">
+      <c r="C138" s="9">
         <v>44</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="8">
         <v>92</v>
       </c>
-      <c r="E138" s="5"/>
+      <c r="E138" s="5">
+        <v>87</v>
+      </c>
       <c r="F138" s="5"/>
-      <c r="G138" s="10">
+      <c r="G138" s="9">
         <v>59</v>
       </c>
-      <c r="H138" s="8">
+      <c r="H138" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="139" spans="1:8">
-      <c r="A139" s="11" t="s">
+      <c r="L138" s="39"/>
+      <c r="M138" s="38"/>
+    </row>
+    <row r="139" spans="1:13">
+      <c r="A139" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B139" s="27" t="s">
+      <c r="B139" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="C139" s="10">
+      <c r="C139" s="9">
         <v>40</v>
       </c>
-      <c r="D139" s="9">
+      <c r="D139" s="8">
         <v>66.5</v>
       </c>
-      <c r="E139" s="5"/>
+      <c r="E139" s="5">
+        <v>76</v>
+      </c>
       <c r="F139" s="5"/>
-      <c r="G139" s="10">
+      <c r="G139" s="9">
         <v>51</v>
       </c>
-      <c r="H139" s="8">
+      <c r="H139" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="140" spans="1:8">
-      <c r="A140" s="11" t="s">
+      <c r="L139" s="39"/>
+      <c r="M139" s="38"/>
+    </row>
+    <row r="140" spans="1:13">
+      <c r="A140" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B140" s="27" t="s">
+      <c r="B140" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="C140" s="10">
+      <c r="C140" s="9">
         <v>18</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="8">
         <v>98</v>
       </c>
-      <c r="E140" s="5"/>
+      <c r="E140" s="5">
+        <v>89</v>
+      </c>
       <c r="F140" s="5"/>
-      <c r="G140" s="10">
+      <c r="G140" s="9">
         <v>61</v>
       </c>
-      <c r="H140" s="8">
+      <c r="H140" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="11" t="s">
+      <c r="L140" s="39"/>
+      <c r="M140" s="38"/>
+    </row>
+    <row r="141" spans="1:13">
+      <c r="A141" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B141" s="27" t="s">
+      <c r="B141" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="C141" s="10">
+      <c r="C141" s="9">
         <v>46</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D141" s="8">
         <v>86</v>
       </c>
-      <c r="E141" s="5"/>
+      <c r="E141" s="5">
+        <v>66</v>
+      </c>
       <c r="F141" s="5"/>
-      <c r="G141" s="10">
+      <c r="G141" s="9">
         <v>54</v>
       </c>
-      <c r="H141" s="8">
+      <c r="H141" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="142" spans="1:8">
-      <c r="A142" s="11" t="s">
+      <c r="L141" s="39"/>
+      <c r="M141" s="38"/>
+    </row>
+    <row r="142" spans="1:13">
+      <c r="A142" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B142" s="27" t="s">
+      <c r="B142" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="C142" s="10">
+      <c r="C142" s="9">
         <v>46</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="8">
         <v>86</v>
       </c>
-      <c r="E142" s="5"/>
+      <c r="E142" s="5">
+        <v>62</v>
+      </c>
       <c r="F142" s="5"/>
-      <c r="G142" s="10">
+      <c r="G142" s="9">
         <v>45</v>
       </c>
-      <c r="H142" s="8">
+      <c r="H142" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="143" spans="1:8">
-      <c r="A143" s="11" t="s">
+      <c r="L142" s="39"/>
+      <c r="M142" s="38"/>
+    </row>
+    <row r="143" spans="1:13">
+      <c r="A143" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B143" s="27" t="s">
+      <c r="B143" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="C143" s="10">
+      <c r="C143" s="9">
         <v>44</v>
       </c>
-      <c r="D143" s="9">
+      <c r="D143" s="8">
         <v>91</v>
       </c>
-      <c r="E143" s="5"/>
+      <c r="E143" s="5">
+        <v>85</v>
+      </c>
       <c r="F143" s="5"/>
-      <c r="G143" s="10">
+      <c r="G143" s="9">
         <v>47</v>
       </c>
-      <c r="H143" s="8">
+      <c r="H143" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="11" t="s">
+      <c r="L143" s="39"/>
+      <c r="M143" s="38"/>
+    </row>
+    <row r="144" spans="1:13">
+      <c r="A144" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="B144" s="27" t="s">
+      <c r="B144" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="10">
+      <c r="C144" s="9">
         <v>44</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="8">
         <v>91</v>
       </c>
-      <c r="E144" s="5"/>
+      <c r="E144" s="5">
+        <v>72</v>
+      </c>
       <c r="F144" s="5"/>
-      <c r="G144" s="10">
+      <c r="G144" s="9">
         <v>61</v>
       </c>
-      <c r="H144" s="8">
+      <c r="H144" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="11" t="s">
+      <c r="L144" s="39"/>
+      <c r="M144" s="38"/>
+    </row>
+    <row r="145" spans="1:13">
+      <c r="A145" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B145" s="27" t="s">
+      <c r="B145" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="C145" s="10">
+      <c r="C145" s="9">
         <v>34</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D145" s="8">
         <v>68</v>
       </c>
-      <c r="E145" s="5"/>
+      <c r="E145" s="5">
+        <v>69</v>
+      </c>
       <c r="F145" s="5"/>
-      <c r="G145" s="10">
+      <c r="G145" s="9">
         <v>73</v>
       </c>
-      <c r="H145" s="8">
+      <c r="H145" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="146" spans="1:8">
-      <c r="A146" s="11" t="s">
+      <c r="L145" s="39"/>
+      <c r="M145" s="38"/>
+    </row>
+    <row r="146" spans="1:13">
+      <c r="A146" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B146" s="27" t="s">
+      <c r="B146" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="C146" s="10">
+      <c r="C146" s="9">
         <v>72</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="8">
         <v>82</v>
       </c>
-      <c r="E146" s="5"/>
+      <c r="E146" s="5">
+        <v>73</v>
+      </c>
       <c r="F146" s="5"/>
-      <c r="G146" s="10">
+      <c r="G146" s="9">
         <v>53</v>
       </c>
-      <c r="H146" s="8">
+      <c r="H146" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="147" spans="1:8">
-      <c r="A147" s="11" t="s">
+      <c r="L146" s="39"/>
+      <c r="M146" s="38"/>
+    </row>
+    <row r="147" spans="1:13">
+      <c r="A147" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B147" s="27" t="s">
+      <c r="B147" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="C147" s="10">
+      <c r="C147" s="9">
         <v>48</v>
       </c>
-      <c r="D147" s="9">
+      <c r="D147" s="8">
         <v>99</v>
       </c>
-      <c r="E147" s="5"/>
+      <c r="E147" s="5">
+        <v>81</v>
+      </c>
       <c r="F147" s="5"/>
-      <c r="G147" s="10">
+      <c r="G147" s="9">
         <v>54</v>
       </c>
-      <c r="H147" s="8">
+      <c r="H147" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" s="11" t="s">
+      <c r="L147" s="39"/>
+      <c r="M147" s="38"/>
+    </row>
+    <row r="148" spans="1:13">
+      <c r="A148" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B148" s="27" t="s">
+      <c r="B148" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="C148" s="10">
+      <c r="C148" s="9">
         <v>48</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D148" s="8">
         <v>96</v>
       </c>
-      <c r="E148" s="5"/>
+      <c r="E148" s="5">
+        <v>74</v>
+      </c>
       <c r="F148" s="5"/>
-      <c r="G148" s="10">
+      <c r="G148" s="9">
         <v>51</v>
       </c>
-      <c r="H148" s="8">
+      <c r="H148" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="149" spans="1:8">
-      <c r="A149" s="11" t="s">
+      <c r="L148" s="39"/>
+      <c r="M148" s="38"/>
+    </row>
+    <row r="149" spans="1:13">
+      <c r="A149" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B149" s="27" t="s">
+      <c r="B149" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="C149" s="10">
+      <c r="C149" s="9">
         <v>28</v>
       </c>
-      <c r="D149" s="9">
+      <c r="D149" s="8">
         <v>88</v>
       </c>
-      <c r="E149" s="5"/>
+      <c r="E149" s="5">
+        <v>76</v>
+      </c>
       <c r="F149" s="5"/>
-      <c r="G149" s="10">
+      <c r="G149" s="9">
         <v>56</v>
       </c>
-      <c r="H149" s="8">
+      <c r="H149" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="11" t="s">
+      <c r="L149" s="39"/>
+      <c r="M149" s="38"/>
+    </row>
+    <row r="150" spans="1:13">
+      <c r="A150" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B150" s="27" t="s">
+      <c r="B150" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="C150" s="10">
+      <c r="C150" s="9">
         <v>52</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="8">
         <v>80</v>
       </c>
-      <c r="E150" s="5"/>
+      <c r="E150" s="5">
+        <v>56</v>
+      </c>
       <c r="F150" s="5"/>
-      <c r="G150" s="10">
+      <c r="G150" s="9">
         <v>51</v>
       </c>
-      <c r="H150" s="8">
+      <c r="H150" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="151" spans="1:8">
-      <c r="A151" s="11" t="s">
+      <c r="L150" s="39"/>
+      <c r="M150" s="38"/>
+    </row>
+    <row r="151" spans="1:13">
+      <c r="A151" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="C151" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D151" s="9">
+      <c r="D151" s="8">
         <v>68.5</v>
       </c>
-      <c r="E151" s="5"/>
+      <c r="E151" s="5">
+        <v>82</v>
+      </c>
       <c r="F151" s="5"/>
-      <c r="G151" s="10">
+      <c r="G151" s="9">
         <v>67</v>
       </c>
-      <c r="H151" s="8">
+      <c r="H151" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="11" t="s">
+      <c r="L151" s="39"/>
+      <c r="M151" s="38"/>
+    </row>
+    <row r="152" spans="1:13">
+      <c r="A152" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="B152" s="27" t="s">
+      <c r="B152" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="C152" s="10">
+      <c r="C152" s="9">
         <v>40</v>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="8">
         <v>66.5</v>
       </c>
-      <c r="E152" s="5"/>
+      <c r="E152" s="5">
+        <v>59</v>
+      </c>
       <c r="F152" s="5"/>
-      <c r="G152" s="10">
+      <c r="G152" s="9">
         <v>45</v>
       </c>
-      <c r="H152" s="8">
+      <c r="H152" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="153" spans="1:8">
-      <c r="A153" s="11" t="s">
+      <c r="L152" s="39"/>
+      <c r="M152" s="38"/>
+    </row>
+    <row r="153" spans="1:13">
+      <c r="A153" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B153" s="27" t="s">
+      <c r="B153" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="C153" s="10">
+      <c r="C153" s="9">
         <v>46</v>
       </c>
-      <c r="D153" s="9" t="s">
+      <c r="D153" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E153" s="5"/>
+      <c r="E153" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F153" s="5"/>
-      <c r="G153" s="10" t="s">
+      <c r="G153" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="H153" s="8">
+      <c r="H153" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="154" spans="1:8">
-      <c r="A154" s="11" t="s">
+      <c r="L153" s="39"/>
+      <c r="M153" s="38"/>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="A154" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B154" s="27" t="s">
+      <c r="B154" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="C154" s="10">
+      <c r="C154" s="9">
         <v>28</v>
       </c>
-      <c r="D154" s="9">
+      <c r="D154" s="8">
         <v>88</v>
       </c>
-      <c r="E154" s="5"/>
+      <c r="E154" s="5">
+        <v>73</v>
+      </c>
       <c r="F154" s="5"/>
-      <c r="G154" s="10">
+      <c r="G154" s="9">
         <v>73</v>
       </c>
-      <c r="H154" s="8">
+      <c r="H154" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="155" spans="1:8">
-      <c r="A155" s="11" t="s">
+      <c r="L154" s="39"/>
+      <c r="M154" s="38"/>
+    </row>
+    <row r="155" spans="1:13">
+      <c r="A155" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="B155" s="27" t="s">
+      <c r="B155" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="C155" s="10">
+      <c r="C155" s="9">
         <v>44</v>
       </c>
-      <c r="D155" s="9">
+      <c r="D155" s="8">
         <v>85</v>
       </c>
-      <c r="E155" s="5"/>
+      <c r="E155" s="5">
+        <v>41</v>
+      </c>
       <c r="F155" s="5"/>
-      <c r="G155" s="10">
+      <c r="G155" s="9">
         <v>62</v>
       </c>
-      <c r="H155" s="8">
+      <c r="H155" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="156" spans="1:8">
-      <c r="A156" s="11" t="s">
+      <c r="L155" s="39"/>
+      <c r="M155" s="38"/>
+    </row>
+    <row r="156" spans="1:13">
+      <c r="A156" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B156" s="27" t="s">
+      <c r="B156" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="C156" s="10">
+      <c r="C156" s="9">
         <v>44</v>
       </c>
-      <c r="D156" s="9">
+      <c r="D156" s="8">
         <v>85</v>
       </c>
-      <c r="E156" s="5"/>
+      <c r="E156" s="5">
+        <v>69</v>
+      </c>
       <c r="F156" s="5"/>
-      <c r="G156" s="10">
+      <c r="G156" s="9">
         <v>49</v>
       </c>
-      <c r="H156" s="8">
+      <c r="H156" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="157" spans="1:8">
-      <c r="A157" s="11" t="s">
+      <c r="L156" s="39"/>
+      <c r="M156" s="38"/>
+    </row>
+    <row r="157" spans="1:13">
+      <c r="A157" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B157" s="27" t="s">
+      <c r="B157" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="C157" s="10">
+      <c r="C157" s="9">
         <v>26</v>
       </c>
-      <c r="D157" s="9">
+      <c r="D157" s="8">
         <v>84</v>
       </c>
-      <c r="E157" s="5"/>
+      <c r="E157" s="5">
+        <v>59</v>
+      </c>
       <c r="F157" s="5"/>
-      <c r="G157" s="10" t="s">
+      <c r="G157" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="H157" s="8">
+      <c r="H157" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="158" spans="1:8">
-      <c r="A158" s="11" t="s">
+      <c r="L157" s="39"/>
+      <c r="M157" s="38"/>
+    </row>
+    <row r="158" spans="1:13">
+      <c r="A158" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B158" s="27" t="s">
+      <c r="B158" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="C158" s="10">
+      <c r="C158" s="9">
         <v>48</v>
       </c>
-      <c r="D158" s="9">
+      <c r="D158" s="8">
         <v>89.5</v>
       </c>
-      <c r="E158" s="5"/>
+      <c r="E158" s="5">
+        <v>77</v>
+      </c>
       <c r="F158" s="5"/>
-      <c r="G158" s="10">
+      <c r="G158" s="9">
         <v>50</v>
       </c>
-      <c r="H158" s="8">
+      <c r="H158" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="159" spans="1:8">
-      <c r="A159" s="11" t="s">
+      <c r="L158" s="39"/>
+      <c r="M158" s="38"/>
+    </row>
+    <row r="159" spans="1:13">
+      <c r="A159" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B159" s="27" t="s">
+      <c r="B159" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="C159" s="10">
+      <c r="C159" s="9">
         <v>64</v>
       </c>
-      <c r="D159" s="9">
+      <c r="D159" s="8">
         <v>92.5</v>
       </c>
-      <c r="E159" s="5"/>
+      <c r="E159" s="5">
+        <v>80</v>
+      </c>
       <c r="F159" s="5"/>
-      <c r="G159" s="10">
+      <c r="G159" s="9">
         <v>62</v>
       </c>
-      <c r="H159" s="8">
+      <c r="H159" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="160" spans="1:8">
-      <c r="A160" s="11" t="s">
+      <c r="L159" s="39"/>
+      <c r="M159" s="38"/>
+    </row>
+    <row r="160" spans="1:13">
+      <c r="A160" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B160" s="27" t="s">
+      <c r="B160" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="C160" s="10">
+      <c r="C160" s="9">
         <v>52</v>
       </c>
-      <c r="D160" s="9">
+      <c r="D160" s="8">
         <v>89</v>
       </c>
-      <c r="E160" s="5"/>
+      <c r="E160" s="5">
+        <v>69</v>
+      </c>
       <c r="F160" s="5"/>
-      <c r="G160" s="10">
+      <c r="G160" s="9">
         <v>51</v>
       </c>
-      <c r="H160" s="8">
+      <c r="H160" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="161" spans="1:8">
-      <c r="A161" s="11" t="s">
+      <c r="L160" s="39"/>
+      <c r="M160" s="38"/>
+    </row>
+    <row r="161" spans="1:13">
+      <c r="A161" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B161" s="27" t="s">
+      <c r="B161" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="C161" s="10">
+      <c r="C161" s="9">
         <v>54</v>
       </c>
-      <c r="D161" s="9">
+      <c r="D161" s="8">
         <v>91</v>
       </c>
-      <c r="E161" s="5"/>
+      <c r="E161" s="5">
+        <v>69</v>
+      </c>
       <c r="F161" s="5"/>
-      <c r="G161" s="10">
+      <c r="G161" s="9">
         <v>47</v>
       </c>
-      <c r="H161" s="8">
+      <c r="H161" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="162" spans="1:8">
-      <c r="A162" s="11" t="s">
+      <c r="L161" s="39"/>
+      <c r="M161" s="38"/>
+    </row>
+    <row r="162" spans="1:13">
+      <c r="A162" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B162" s="27" t="s">
+      <c r="B162" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="C162" s="10">
+      <c r="C162" s="9">
         <v>52</v>
       </c>
-      <c r="D162" s="9">
+      <c r="D162" s="8">
         <v>99</v>
       </c>
-      <c r="E162" s="5"/>
+      <c r="E162" s="5">
+        <v>68</v>
+      </c>
       <c r="F162" s="5"/>
-      <c r="G162" s="10">
+      <c r="G162" s="9">
         <v>50</v>
       </c>
-      <c r="H162" s="8">
+      <c r="H162" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="163" spans="1:8">
-      <c r="A163" s="11" t="s">
+      <c r="L162" s="39"/>
+      <c r="M162" s="38"/>
+    </row>
+    <row r="163" spans="1:13">
+      <c r="A163" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B163" s="27" t="s">
+      <c r="B163" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="C163" s="10">
+      <c r="C163" s="9">
         <v>12</v>
       </c>
-      <c r="D163" s="9">
+      <c r="D163" s="8">
         <v>71</v>
       </c>
-      <c r="E163" s="5"/>
+      <c r="E163" s="5">
+        <v>64</v>
+      </c>
       <c r="F163" s="5"/>
-      <c r="G163" s="10">
+      <c r="G163" s="9">
         <v>45</v>
       </c>
-      <c r="H163" s="8">
+      <c r="H163" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="164" spans="1:8">
-      <c r="A164" s="11" t="s">
+      <c r="L163" s="39"/>
+      <c r="M163" s="38"/>
+    </row>
+    <row r="164" spans="1:13">
+      <c r="A164" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B164" s="27" t="s">
+      <c r="B164" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="C164" s="10">
+      <c r="C164" s="9">
         <v>26</v>
       </c>
-      <c r="D164" s="9">
+      <c r="D164" s="8">
         <v>91</v>
       </c>
-      <c r="E164" s="5"/>
+      <c r="E164" s="5">
+        <v>62</v>
+      </c>
       <c r="F164" s="5"/>
-      <c r="G164" s="10">
+      <c r="G164" s="9">
         <v>49</v>
       </c>
-      <c r="H164" s="8">
+      <c r="H164" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="165" spans="1:8">
-      <c r="A165" s="11" t="s">
+      <c r="L164" s="39"/>
+      <c r="M164" s="38"/>
+    </row>
+    <row r="165" spans="1:13">
+      <c r="A165" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B165" s="27" t="s">
+      <c r="B165" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="C165" s="10">
+      <c r="C165" s="9">
         <v>70</v>
       </c>
-      <c r="D165" s="9">
+      <c r="D165" s="8">
         <v>86</v>
       </c>
-      <c r="E165" s="5"/>
+      <c r="E165" s="5">
+        <v>58</v>
+      </c>
       <c r="F165" s="5"/>
-      <c r="G165" s="10">
+      <c r="G165" s="9">
         <v>51</v>
       </c>
-      <c r="H165" s="8">
+      <c r="H165" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="166" spans="1:8">
-      <c r="A166" s="11" t="s">
+      <c r="L165" s="39"/>
+      <c r="M165" s="38"/>
+    </row>
+    <row r="166" spans="1:13">
+      <c r="A166" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B166" s="27" t="s">
+      <c r="B166" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="C166" s="10">
+      <c r="C166" s="9">
         <v>67</v>
       </c>
-      <c r="D166" s="9">
+      <c r="D166" s="8">
         <v>76</v>
       </c>
-      <c r="E166" s="5"/>
+      <c r="E166" s="5">
+        <v>69</v>
+      </c>
       <c r="F166" s="5"/>
-      <c r="G166" s="10">
+      <c r="G166" s="9">
         <v>56</v>
       </c>
-      <c r="H166" s="8">
+      <c r="H166" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="167" spans="1:8">
-      <c r="A167" s="11" t="s">
+      <c r="L166" s="39"/>
+      <c r="M166" s="38"/>
+    </row>
+    <row r="167" spans="1:13">
+      <c r="A167" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="B167" s="27" t="s">
+      <c r="B167" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="C167" s="10">
+      <c r="C167" s="9">
         <v>48</v>
       </c>
-      <c r="D167" s="9">
+      <c r="D167" s="8">
         <v>57</v>
       </c>
-      <c r="E167" s="5"/>
+      <c r="E167" s="5">
+        <v>78</v>
+      </c>
       <c r="F167" s="5"/>
-      <c r="G167" s="10">
+      <c r="G167" s="9">
         <v>61</v>
       </c>
-      <c r="H167" s="8">
+      <c r="H167" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="11" t="s">
+      <c r="L167" s="39"/>
+      <c r="M167" s="38"/>
+    </row>
+    <row r="168" spans="1:13">
+      <c r="A168" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B168" s="27" t="s">
+      <c r="B168" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="C168" s="10">
+      <c r="C168" s="9">
         <v>40</v>
       </c>
-      <c r="D168" s="9">
+      <c r="D168" s="8">
         <v>86.5</v>
       </c>
-      <c r="E168" s="5"/>
+      <c r="E168" s="5">
+        <v>74</v>
+      </c>
       <c r="F168" s="5"/>
-      <c r="G168" s="10">
+      <c r="G168" s="9">
         <v>58</v>
       </c>
-      <c r="H168" s="8">
+      <c r="H168" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="169" spans="1:8">
-      <c r="A169" s="11" t="s">
+      <c r="L168" s="39"/>
+      <c r="M168" s="38"/>
+    </row>
+    <row r="169" spans="1:13">
+      <c r="A169" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="B169" s="27" t="s">
+      <c r="B169" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="C169" s="10">
+      <c r="C169" s="9">
         <v>54</v>
       </c>
-      <c r="D169" s="9">
+      <c r="D169" s="8">
         <v>82.5</v>
       </c>
-      <c r="E169" s="5"/>
+      <c r="E169" s="5">
+        <v>70</v>
+      </c>
       <c r="F169" s="5"/>
-      <c r="G169" s="10">
+      <c r="G169" s="9">
         <v>43</v>
       </c>
-      <c r="H169" s="8">
+      <c r="H169" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="170" spans="1:8">
-      <c r="A170" s="11" t="s">
+      <c r="L169" s="39"/>
+      <c r="M169" s="38"/>
+    </row>
+    <row r="170" spans="1:13">
+      <c r="A170" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="C170" s="10">
+      <c r="C170" s="9">
         <v>44</v>
       </c>
-      <c r="D170" s="9">
+      <c r="D170" s="8">
         <v>92</v>
       </c>
-      <c r="E170" s="5"/>
+      <c r="E170" s="5">
+        <v>56</v>
+      </c>
       <c r="F170" s="5"/>
-      <c r="G170" s="10">
+      <c r="G170" s="9">
         <v>57</v>
       </c>
-      <c r="H170" s="8">
+      <c r="H170" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="171" spans="1:8">
-      <c r="A171" s="11" t="s">
+      <c r="L170" s="39"/>
+      <c r="M170" s="38"/>
+    </row>
+    <row r="171" spans="1:13">
+      <c r="A171" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="B171" s="27" t="s">
+      <c r="B171" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="C171" s="10">
+      <c r="C171" s="9">
         <v>54</v>
       </c>
-      <c r="D171" s="9">
+      <c r="D171" s="8">
         <v>79</v>
       </c>
-      <c r="E171" s="5"/>
+      <c r="E171" s="5">
+        <v>70</v>
+      </c>
       <c r="F171" s="5"/>
-      <c r="G171" s="10">
+      <c r="G171" s="9">
         <v>77</v>
       </c>
-      <c r="H171" s="8">
+      <c r="H171" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="172" spans="1:8">
-      <c r="A172" s="11" t="s">
+      <c r="L171" s="39"/>
+      <c r="M171" s="38"/>
+    </row>
+    <row r="172" spans="1:13">
+      <c r="A172" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B172" s="27" t="s">
+      <c r="B172" s="26" t="s">
         <v>349</v>
       </c>
-      <c r="C172" s="10">
+      <c r="C172" s="9">
         <v>46</v>
       </c>
-      <c r="D172" s="9">
+      <c r="D172" s="8">
         <v>86</v>
       </c>
-      <c r="E172" s="5"/>
+      <c r="E172" s="5">
+        <v>72</v>
+      </c>
       <c r="F172" s="5"/>
-      <c r="G172" s="10">
+      <c r="G172" s="9">
         <v>45</v>
       </c>
-      <c r="H172" s="8">
+      <c r="H172" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="173" spans="1:8">
-      <c r="A173" s="11" t="s">
+      <c r="L172" s="39"/>
+      <c r="M172" s="38"/>
+    </row>
+    <row r="173" spans="1:13">
+      <c r="A173" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="B173" s="27" t="s">
+      <c r="B173" s="26" t="s">
         <v>351</v>
       </c>
-      <c r="C173" s="10">
+      <c r="C173" s="9">
         <v>40</v>
       </c>
-      <c r="D173" s="9">
+      <c r="D173" s="8">
         <v>75.5</v>
       </c>
-      <c r="E173" s="5"/>
+      <c r="E173" s="5">
+        <v>80</v>
+      </c>
       <c r="F173" s="5"/>
-      <c r="G173" s="10">
+      <c r="G173" s="9">
         <v>62</v>
       </c>
-      <c r="H173" s="8">
+      <c r="H173" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="174" spans="1:8">
-      <c r="A174" s="11" t="s">
+      <c r="L173" s="39"/>
+      <c r="M173" s="38"/>
+    </row>
+    <row r="174" spans="1:13">
+      <c r="A174" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="B174" s="27" t="s">
+      <c r="B174" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="C174" s="10">
+      <c r="C174" s="9">
         <v>36</v>
       </c>
-      <c r="D174" s="9">
+      <c r="D174" s="8">
         <v>99</v>
       </c>
-      <c r="E174" s="5"/>
+      <c r="E174" s="5">
+        <v>80</v>
+      </c>
       <c r="F174" s="5"/>
-      <c r="G174" s="10">
+      <c r="G174" s="9">
         <v>53</v>
       </c>
-      <c r="H174" s="8">
+      <c r="H174" s="7">
         <v>76.923076899999998</v>
       </c>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="A175" s="11" t="s">
+      <c r="L174" s="39"/>
+      <c r="M174" s="38"/>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="B175" s="27" t="s">
+      <c r="B175" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="C175" s="10">
+      <c r="C175" s="9">
         <v>48</v>
       </c>
-      <c r="D175" s="9">
+      <c r="D175" s="8">
         <v>57</v>
       </c>
-      <c r="E175" s="5"/>
+      <c r="E175" s="5">
+        <v>80</v>
+      </c>
       <c r="F175" s="5"/>
-      <c r="G175" s="10">
+      <c r="G175" s="9">
         <v>43</v>
       </c>
-      <c r="H175" s="8">
+      <c r="H175" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="176" spans="1:8">
-      <c r="A176" s="11" t="s">
+      <c r="L175" s="39"/>
+      <c r="M175" s="38"/>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="B176" s="27" t="s">
+      <c r="B176" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="C176" s="10">
+      <c r="C176" s="9">
         <v>70</v>
       </c>
-      <c r="D176" s="9">
+      <c r="D176" s="8">
         <v>86</v>
       </c>
-      <c r="E176" s="5"/>
+      <c r="E176" s="5">
+        <v>53</v>
+      </c>
       <c r="F176" s="5"/>
-      <c r="G176" s="10">
+      <c r="G176" s="9">
         <v>52</v>
       </c>
-      <c r="H176" s="8">
+      <c r="H176" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="11" t="s">
+      <c r="L176" s="39"/>
+      <c r="M176" s="38"/>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B177" s="27" t="s">
+      <c r="B177" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="C177" s="10">
+      <c r="C177" s="9">
         <v>52</v>
       </c>
-      <c r="D177" s="9">
+      <c r="D177" s="8">
         <v>95</v>
       </c>
-      <c r="E177" s="5"/>
+      <c r="E177" s="5">
+        <v>63</v>
+      </c>
       <c r="F177" s="5"/>
-      <c r="G177" s="10">
+      <c r="G177" s="9">
         <v>50</v>
       </c>
-      <c r="H177" s="8">
+      <c r="H177" s="7">
         <v>71.428571399999996</v>
       </c>
-    </row>
-    <row r="178" spans="1:8">
-      <c r="A178" s="11" t="s">
+      <c r="L177" s="39"/>
+      <c r="M177" s="38"/>
+    </row>
+    <row r="178" spans="1:13">
+      <c r="A178" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B178" s="27" t="s">
+      <c r="B178" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="C178" s="10">
+      <c r="C178" s="9">
         <v>60</v>
       </c>
-      <c r="D178" s="9">
+      <c r="D178" s="8">
         <v>90</v>
       </c>
-      <c r="E178" s="5"/>
+      <c r="E178" s="5">
+        <v>64</v>
+      </c>
       <c r="F178" s="5"/>
-      <c r="G178" s="10">
+      <c r="G178" s="9">
         <v>55</v>
       </c>
-      <c r="H178" s="8">
+      <c r="H178" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="179" spans="1:8">
-      <c r="A179" s="11" t="s">
+      <c r="L178" s="39"/>
+      <c r="M178" s="38"/>
+    </row>
+    <row r="179" spans="1:13">
+      <c r="A179" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="B179" s="27" t="s">
+      <c r="B179" s="26" t="s">
         <v>363</v>
       </c>
-      <c r="C179" s="10">
+      <c r="C179" s="9">
         <v>26</v>
       </c>
-      <c r="D179" s="9">
+      <c r="D179" s="8">
         <v>100</v>
       </c>
-      <c r="E179" s="5"/>
+      <c r="E179" s="5">
+        <v>61</v>
+      </c>
       <c r="F179" s="5"/>
-      <c r="G179" s="10">
+      <c r="G179" s="9">
         <v>53</v>
       </c>
-      <c r="H179" s="8">
+      <c r="H179" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="180" spans="1:8">
-      <c r="A180" s="11" t="s">
+      <c r="L179" s="39"/>
+      <c r="M179" s="38"/>
+    </row>
+    <row r="180" spans="1:13">
+      <c r="A180" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="C180" s="10">
+      <c r="C180" s="9">
         <v>60</v>
       </c>
-      <c r="D180" s="9">
+      <c r="D180" s="8">
         <v>90</v>
       </c>
-      <c r="E180" s="5"/>
+      <c r="E180" s="5">
+        <v>77</v>
+      </c>
       <c r="F180" s="5"/>
-      <c r="G180" s="10">
+      <c r="G180" s="9">
         <v>61</v>
       </c>
-      <c r="H180" s="8">
+      <c r="H180" s="7">
         <v>78.571428600000004</v>
       </c>
-    </row>
-    <row r="181" spans="1:8">
-      <c r="A181" s="11" t="s">
+      <c r="L180" s="39"/>
+      <c r="M180" s="38"/>
+    </row>
+    <row r="181" spans="1:13">
+      <c r="A181" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="C181" s="10">
+      <c r="C181" s="9">
         <v>64</v>
       </c>
-      <c r="D181" s="9">
+      <c r="D181" s="8">
         <v>92.5</v>
       </c>
-      <c r="E181" s="5"/>
+      <c r="E181" s="5">
+        <v>68</v>
+      </c>
       <c r="F181" s="5"/>
-      <c r="G181" s="10">
+      <c r="G181" s="9">
         <v>48</v>
       </c>
-      <c r="H181" s="8">
+      <c r="H181" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="182" spans="1:8">
-      <c r="A182" s="11" t="s">
+      <c r="L181" s="39"/>
+      <c r="M181" s="38"/>
+    </row>
+    <row r="182" spans="1:13">
+      <c r="A182" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="B182" s="29" t="s">
+      <c r="B182" s="28" t="s">
         <v>384</v>
       </c>
-      <c r="C182" s="10">
+      <c r="C182" s="9">
         <v>46</v>
       </c>
-      <c r="D182" s="9">
+      <c r="D182" s="8">
         <v>84.5</v>
       </c>
-      <c r="E182" s="5"/>
+      <c r="E182" s="5">
+        <v>50</v>
+      </c>
       <c r="F182" s="5"/>
-      <c r="G182" s="10">
+      <c r="G182" s="9">
         <v>37</v>
       </c>
-      <c r="H182" s="8">
+      <c r="H182" s="7">
         <v>64.285714299999995</v>
       </c>
-    </row>
-    <row r="183" spans="1:8">
-      <c r="A183" s="11" t="s">
+      <c r="L182" s="39"/>
+      <c r="M182" s="38"/>
+    </row>
+    <row r="183" spans="1:13">
+      <c r="A183" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B183" s="29" t="s">
+      <c r="B183" s="28" t="s">
         <v>370</v>
       </c>
-      <c r="C183" s="10">
+      <c r="C183" s="9">
         <v>34</v>
       </c>
-      <c r="D183" s="9">
+      <c r="D183" s="8">
         <v>68</v>
       </c>
-      <c r="E183" s="5"/>
+      <c r="E183" s="5">
+        <v>45</v>
+      </c>
       <c r="F183" s="5"/>
-      <c r="G183" s="10">
+      <c r="G183" s="9">
         <v>44</v>
       </c>
-      <c r="H183" s="8">
+      <c r="H183" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="184" spans="1:8">
-      <c r="A184" s="11" t="s">
+      <c r="L183" s="39"/>
+      <c r="M183" s="38"/>
+    </row>
+    <row r="184" spans="1:13">
+      <c r="A184" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="B184" s="30" t="s">
+      <c r="B184" s="29" t="s">
         <v>385</v>
       </c>
-      <c r="C184" s="10">
+      <c r="C184" s="9">
         <v>54</v>
       </c>
-      <c r="D184" s="9">
+      <c r="D184" s="8">
         <v>91</v>
       </c>
-      <c r="E184" s="5"/>
+      <c r="E184" s="5">
+        <v>72</v>
+      </c>
       <c r="F184" s="5"/>
-      <c r="G184" s="10">
+      <c r="G184" s="9">
         <v>53</v>
       </c>
-      <c r="H184" s="8">
+      <c r="H184" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="185" spans="1:8">
-      <c r="A185" s="11" t="s">
+      <c r="L184" s="39"/>
+      <c r="M184" s="38"/>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="A185" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B185" s="31" t="s">
+      <c r="B185" s="30" t="s">
         <v>386</v>
       </c>
-      <c r="C185" s="10">
+      <c r="C185" s="9">
         <v>64</v>
       </c>
-      <c r="D185" s="9">
+      <c r="D185" s="8">
         <v>88</v>
       </c>
-      <c r="E185" s="5"/>
+      <c r="E185" s="5">
+        <v>90</v>
+      </c>
       <c r="F185" s="5"/>
-      <c r="G185" s="10">
+      <c r="G185" s="9">
         <v>74</v>
       </c>
-      <c r="H185" s="8">
+      <c r="H185" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="186" spans="1:8">
-      <c r="A186" s="11" t="s">
+      <c r="L185" s="39"/>
+      <c r="M185" s="38"/>
+    </row>
+    <row r="186" spans="1:13">
+      <c r="A186" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="B186" s="29" t="s">
+      <c r="B186" s="28" t="s">
         <v>387</v>
       </c>
-      <c r="C186" s="10">
+      <c r="C186" s="9">
         <v>72</v>
       </c>
-      <c r="D186" s="9">
+      <c r="D186" s="8">
         <v>100</v>
       </c>
-      <c r="E186" s="5"/>
+      <c r="E186" s="5">
+        <v>52</v>
+      </c>
       <c r="F186" s="5"/>
-      <c r="G186" s="10">
+      <c r="G186" s="9">
         <v>62</v>
       </c>
-      <c r="H186" s="8">
+      <c r="H186" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="187" spans="1:8">
-      <c r="A187" s="11" t="s">
+      <c r="L186" s="39"/>
+      <c r="M186" s="38"/>
+    </row>
+    <row r="187" spans="1:13">
+      <c r="A187" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="B187" s="29" t="s">
+      <c r="B187" s="28" t="s">
         <v>388</v>
       </c>
-      <c r="C187" s="10">
+      <c r="C187" s="9">
         <v>46</v>
       </c>
-      <c r="D187" s="9">
+      <c r="D187" s="8">
         <v>84.5</v>
       </c>
-      <c r="E187" s="5"/>
+      <c r="E187" s="5">
+        <v>69</v>
+      </c>
       <c r="F187" s="5"/>
-      <c r="G187" s="10">
+      <c r="G187" s="9">
         <v>47</v>
       </c>
-      <c r="H187" s="8">
+      <c r="H187" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="188" spans="1:8">
-      <c r="A188" s="11" t="s">
+      <c r="L187" s="39"/>
+      <c r="M187" s="38"/>
+    </row>
+    <row r="188" spans="1:13">
+      <c r="A188" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B188" s="29" t="s">
+      <c r="B188" s="28" t="s">
         <v>389</v>
       </c>
-      <c r="C188" s="10">
+      <c r="C188" s="9">
         <v>54</v>
       </c>
-      <c r="D188" s="9">
+      <c r="D188" s="8">
         <v>87</v>
       </c>
-      <c r="E188" s="5"/>
+      <c r="E188" s="5">
+        <v>75</v>
+      </c>
       <c r="F188" s="5"/>
-      <c r="G188" s="10">
+      <c r="G188" s="9">
         <v>37</v>
       </c>
-      <c r="H188" s="8">
+      <c r="H188" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="189" spans="1:8">
-      <c r="A189" s="11" t="s">
+      <c r="L188" s="39"/>
+      <c r="M188" s="38"/>
+    </row>
+    <row r="189" spans="1:13">
+      <c r="A189" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="B189" s="29" t="s">
+      <c r="B189" s="28" t="s">
         <v>390</v>
       </c>
-      <c r="C189" s="10">
+      <c r="C189" s="9">
         <v>54</v>
       </c>
-      <c r="D189" s="9">
+      <c r="D189" s="8">
         <v>87</v>
       </c>
-      <c r="E189" s="5"/>
+      <c r="E189" s="5">
+        <v>54</v>
+      </c>
       <c r="F189" s="5"/>
-      <c r="G189" s="10">
+      <c r="G189" s="9">
         <v>42</v>
       </c>
-      <c r="H189" s="8">
+      <c r="H189" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="190" spans="1:8">
-      <c r="A190" s="11" t="s">
+      <c r="L189" s="39"/>
+      <c r="M189" s="38"/>
+    </row>
+    <row r="190" spans="1:13">
+      <c r="A190" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="B190" s="32" t="s">
+      <c r="B190" s="31" t="s">
         <v>391</v>
       </c>
-      <c r="C190" s="10">
+      <c r="C190" s="9">
         <v>72</v>
       </c>
-      <c r="D190" s="9">
+      <c r="D190" s="8">
         <v>100</v>
       </c>
-      <c r="E190" s="5"/>
+      <c r="E190" s="5">
+        <v>73</v>
+      </c>
       <c r="F190" s="5"/>
-      <c r="G190" s="10">
+      <c r="G190" s="9">
         <v>57</v>
       </c>
-      <c r="H190" s="8">
+      <c r="H190" s="7">
         <v>85.714285700000005</v>
       </c>
-    </row>
-    <row r="191" spans="1:8">
-      <c r="A191" s="11" t="s">
+      <c r="L190" s="39"/>
+      <c r="M190" s="38"/>
+    </row>
+    <row r="191" spans="1:13">
+      <c r="A191" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="B191" s="29" t="s">
+      <c r="B191" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="C191" s="10">
+      <c r="C191" s="9">
         <v>72</v>
       </c>
-      <c r="D191" s="9">
+      <c r="D191" s="8">
         <v>100</v>
       </c>
-      <c r="E191" s="5"/>
+      <c r="E191" s="5">
+        <v>69</v>
+      </c>
       <c r="F191" s="5"/>
-      <c r="G191" s="10">
+      <c r="G191" s="9">
         <v>62</v>
       </c>
-      <c r="H191" s="8">
+      <c r="H191" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="192" spans="1:8">
-      <c r="A192" s="11" t="s">
+      <c r="L191" s="39"/>
+      <c r="M191" s="38"/>
+    </row>
+    <row r="192" spans="1:13">
+      <c r="A192" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="B192" s="29" t="s">
+      <c r="B192" s="28" t="s">
         <v>393</v>
       </c>
-      <c r="C192" s="10">
+      <c r="C192" s="9">
         <v>54</v>
       </c>
-      <c r="D192" s="9">
+      <c r="D192" s="8">
         <v>87</v>
       </c>
-      <c r="E192" s="5"/>
+      <c r="E192" s="5">
+        <v>78</v>
+      </c>
       <c r="F192" s="5"/>
-      <c r="G192" s="10">
+      <c r="G192" s="9">
         <v>45</v>
       </c>
-      <c r="H192" s="8">
+      <c r="H192" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="193" spans="1:8">
-      <c r="A193" s="11" t="s">
+      <c r="L192" s="39"/>
+      <c r="M192" s="38"/>
+    </row>
+    <row r="193" spans="1:13">
+      <c r="A193" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="B193" s="29" t="s">
+      <c r="B193" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="C193" s="10">
+      <c r="C193" s="9">
         <v>54</v>
       </c>
-      <c r="D193" s="9">
+      <c r="D193" s="8">
         <v>87</v>
       </c>
-      <c r="E193" s="5"/>
+      <c r="E193" s="5">
+        <v>65</v>
+      </c>
       <c r="F193" s="5"/>
-      <c r="G193" s="10">
+      <c r="G193" s="9">
         <v>39</v>
       </c>
-      <c r="H193" s="8">
+      <c r="H193" s="7">
         <v>92.857142899999999</v>
       </c>
-    </row>
-    <row r="194" spans="1:8">
-      <c r="A194" s="13" t="s">
+      <c r="L193" s="39"/>
+      <c r="M193" s="38"/>
+    </row>
+    <row r="194" spans="1:13">
+      <c r="A194" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="B194" s="33" t="s">
+      <c r="B194" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="C194" s="10" t="s">
+      <c r="C194" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D194" s="9" t="s">
+      <c r="D194" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E194" s="5"/>
+      <c r="E194" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F194" s="5"/>
-      <c r="G194" s="10" t="s">
+      <c r="G194" s="9" t="s">
         <v>383</v>
       </c>
       <c r="H194" s="6"/>
-    </row>
-    <row r="195" spans="1:8">
-      <c r="A195" s="35" t="s">
+      <c r="L194" s="40"/>
+      <c r="M194" s="38"/>
+    </row>
+    <row r="195" spans="1:13">
+      <c r="A195" s="34" t="s">
         <v>395</v>
       </c>
-      <c r="B195" s="29" t="s">
+      <c r="B195" s="28" t="s">
         <v>396</v>
       </c>
-      <c r="C195" s="10" t="s">
+      <c r="C195" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D195" s="10">
+      <c r="D195" s="9">
         <v>79</v>
       </c>
-      <c r="E195" s="5"/>
+      <c r="E195" s="5">
+        <v>59</v>
+      </c>
       <c r="F195" s="5"/>
-      <c r="G195" s="10">
+      <c r="G195" s="9">
         <v>50</v>
       </c>
       <c r="H195" s="6"/>
-    </row>
-    <row r="196" spans="1:8">
-      <c r="A196" s="35" t="s">
+      <c r="L195" s="41"/>
+      <c r="M195" s="38"/>
+    </row>
+    <row r="196" spans="1:13">
+      <c r="A196" s="34" t="s">
         <v>397</v>
       </c>
-      <c r="B196" s="29"/>
-      <c r="C196" s="10" t="s">
+      <c r="B196" s="28"/>
+      <c r="C196" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D196" s="9">
+      <c r="D196" s="8">
         <v>86.5</v>
       </c>
-      <c r="E196" s="5"/>
+      <c r="E196" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="F196" s="5"/>
-      <c r="G196" s="39">
+      <c r="G196" s="9">
         <v>53</v>
       </c>
       <c r="H196" s="6"/>
-    </row>
-    <row r="197" spans="1:8">
-      <c r="A197" s="35" t="s">
+      <c r="L196" s="41"/>
+      <c r="M196" s="38"/>
+    </row>
+    <row r="197" spans="1:13">
+      <c r="A197" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="B197" s="29" t="s">
+      <c r="B197" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="C197" s="10" t="s">
+      <c r="C197" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D197" s="10">
+      <c r="D197" s="9">
         <v>91</v>
       </c>
-      <c r="E197" s="5"/>
+      <c r="E197" s="5">
+        <v>54</v>
+      </c>
       <c r="F197" s="5"/>
-      <c r="G197" s="10">
+      <c r="G197" s="9">
         <v>40</v>
       </c>
       <c r="H197" s="6"/>
-    </row>
-    <row r="198" spans="1:8">
-      <c r="A198" s="35" t="s">
+      <c r="L197" s="41"/>
+      <c r="M197" s="38"/>
+    </row>
+    <row r="198" spans="1:13">
+      <c r="A198" s="34" t="s">
         <v>400</v>
       </c>
-      <c r="B198" s="29" t="s">
+      <c r="B198" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="C198" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D198" s="9">
+      <c r="D198" s="8">
         <v>86.5</v>
       </c>
-      <c r="E198" s="5"/>
+      <c r="E198" s="5">
+        <v>59</v>
+      </c>
       <c r="F198" s="5"/>
-      <c r="G198" s="10">
+      <c r="G198" s="9">
         <v>71</v>
       </c>
       <c r="H198" s="6"/>
-    </row>
-    <row r="199" spans="1:8">
-      <c r="A199" s="35" t="s">
+      <c r="L198" s="41"/>
+      <c r="M198" s="38"/>
+    </row>
+    <row r="199" spans="1:13">
+      <c r="A199" s="34" t="s">
         <v>407</v>
       </c>
-      <c r="B199" s="29"/>
-      <c r="C199" s="10" t="s">
+      <c r="B199" s="28"/>
+      <c r="C199" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D199" s="9" t="s">
+      <c r="D199" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E199" s="5"/>
+      <c r="E199" s="5">
+        <v>54</v>
+      </c>
       <c r="F199" s="5"/>
-      <c r="G199" s="10">
+      <c r="G199" s="9">
         <v>49</v>
       </c>
       <c r="H199" s="6"/>
-    </row>
-    <row r="200" spans="1:8">
-      <c r="A200" s="35" t="s">
+      <c r="L199" s="41"/>
+      <c r="M199" s="38"/>
+    </row>
+    <row r="200" spans="1:13">
+      <c r="A200" s="34" t="s">
         <v>402</v>
       </c>
-      <c r="B200" s="29" t="s">
+      <c r="B200" s="28" t="s">
         <v>403</v>
       </c>
-      <c r="C200" s="10" t="s">
+      <c r="C200" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D200" s="9">
+      <c r="D200" s="8">
         <v>86.5</v>
       </c>
-      <c r="E200" s="5"/>
+      <c r="E200" s="5">
+        <v>59</v>
+      </c>
       <c r="F200" s="5"/>
-      <c r="G200" s="10">
+      <c r="G200" s="9">
         <v>54</v>
       </c>
       <c r="H200" s="6"/>
-    </row>
-    <row r="201" spans="1:8">
-      <c r="A201" s="13" t="s">
+      <c r="L200" s="41"/>
+      <c r="M200" s="38"/>
+    </row>
+    <row r="201" spans="1:13">
+      <c r="A201" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="B201" s="31"/>
-      <c r="C201" s="10">
+      <c r="B201" s="30"/>
+      <c r="C201" s="9">
         <v>36</v>
       </c>
-      <c r="D201" s="9">
+      <c r="D201" s="8">
         <v>92.5</v>
       </c>
-      <c r="E201" s="5"/>
+      <c r="E201" s="5">
+        <v>60</v>
+      </c>
       <c r="F201" s="5"/>
-      <c r="G201" s="10">
+      <c r="G201" s="9">
         <v>54</v>
       </c>
       <c r="H201" s="6"/>
-    </row>
-    <row r="202" spans="1:8">
-      <c r="A202" s="13" t="s">
+      <c r="L201" s="41"/>
+      <c r="M201" s="38"/>
+    </row>
+    <row r="202" spans="1:13">
+      <c r="A202" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="B202" s="31" t="s">
+      <c r="B202" s="30" t="s">
         <v>406</v>
       </c>
-      <c r="C202" s="10" t="s">
+      <c r="C202" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="D202" s="9">
+      <c r="D202" s="8">
         <v>86.5</v>
       </c>
-      <c r="E202" s="5"/>
+      <c r="E202" s="5">
+        <v>43</v>
+      </c>
       <c r="F202" s="5"/>
-      <c r="G202" s="10">
+      <c r="G202" s="9">
         <v>45</v>
       </c>
       <c r="H202" s="6"/>
-    </row>
-    <row r="203" spans="1:8">
-      <c r="A203" s="36" t="s">
+      <c r="L202" s="40"/>
+      <c r="M202" s="38"/>
+    </row>
+    <row r="203" spans="1:13">
+      <c r="A203" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="B203" s="30"/>
+      <c r="C203" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D203" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="E203" s="5">
+        <v>43</v>
+      </c>
+      <c r="F203" s="5"/>
+      <c r="G203" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="H203" s="6"/>
+      <c r="L203" s="40"/>
+      <c r="M203" s="38"/>
+    </row>
+    <row r="204" spans="1:13">
+      <c r="A204" s="35" t="s">
         <v>408</v>
       </c>
-      <c r="B203" s="37"/>
-      <c r="C203" s="38" t="s">
+      <c r="B204" s="36"/>
+      <c r="C204" s="37" t="s">
         <v>383</v>
       </c>
-      <c r="D203" s="9" t="s">
+      <c r="D204" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="10">
+      <c r="E204" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F204" s="5"/>
+      <c r="G204" s="9">
         <v>29</v>
       </c>
-      <c r="H203" s="6"/>
-    </row>
-    <row r="204" spans="1:8">
-      <c r="A204" s="14"/>
-      <c r="B204" s="15"/>
-      <c r="C204" s="16"/>
-      <c r="D204" s="17"/>
-      <c r="E204" s="18"/>
-      <c r="F204" s="18"/>
-      <c r="G204" s="19"/>
-      <c r="H204" s="20"/>
-    </row>
-    <row r="205" spans="1:8">
-      <c r="A205" s="14"/>
-      <c r="B205" s="15"/>
-      <c r="C205" s="16"/>
-      <c r="D205" s="17"/>
-      <c r="E205" s="18"/>
-      <c r="F205" s="18"/>
-      <c r="G205" s="19"/>
-      <c r="H205" s="20"/>
-    </row>
-    <row r="206" spans="1:8">
-      <c r="A206" s="14"/>
-      <c r="B206" s="15"/>
-      <c r="C206" s="16"/>
-      <c r="D206" s="17"/>
-      <c r="E206" s="18"/>
-      <c r="F206" s="18"/>
-      <c r="G206" s="19"/>
-      <c r="H206" s="20"/>
-    </row>
-    <row r="207" spans="1:8">
-      <c r="A207" s="14"/>
-      <c r="B207" s="15"/>
-      <c r="C207" s="16"/>
-      <c r="D207" s="17"/>
-      <c r="E207" s="18"/>
-      <c r="F207" s="18"/>
-      <c r="G207" s="19"/>
-      <c r="H207" s="20"/>
-    </row>
-    <row r="208" spans="1:8">
-      <c r="A208" s="14"/>
-      <c r="B208" s="15"/>
-      <c r="C208" s="16"/>
-      <c r="D208" s="17"/>
-      <c r="E208" s="18"/>
-      <c r="F208" s="21"/>
-      <c r="G208" s="19"/>
-      <c r="H208" s="20"/>
+      <c r="H204" s="6"/>
+      <c r="L204" s="40"/>
+      <c r="M204" s="38"/>
+    </row>
+    <row r="205" spans="1:13">
+      <c r="A205" s="13"/>
+      <c r="B205" s="14"/>
+      <c r="C205" s="15"/>
+      <c r="D205" s="16"/>
+      <c r="E205" s="17"/>
+      <c r="F205" s="17"/>
+      <c r="G205" s="18"/>
+      <c r="H205" s="19"/>
+      <c r="L205" s="39"/>
+      <c r="M205" s="38"/>
+    </row>
+    <row r="206" spans="1:13">
+      <c r="A206" s="13"/>
+      <c r="B206" s="14"/>
+      <c r="C206" s="15"/>
+      <c r="D206" s="16"/>
+      <c r="E206" s="17"/>
+      <c r="F206" s="17"/>
+      <c r="G206" s="18"/>
+      <c r="H206" s="19"/>
+    </row>
+    <row r="207" spans="1:13">
+      <c r="A207" s="13"/>
+      <c r="B207" s="14"/>
+      <c r="C207" s="15"/>
+      <c r="D207" s="16"/>
+      <c r="E207" s="17"/>
+      <c r="F207" s="17"/>
+      <c r="G207" s="18"/>
+      <c r="H207" s="19"/>
+    </row>
+    <row r="208" spans="1:13">
+      <c r="A208" s="13"/>
+      <c r="B208" s="14"/>
+      <c r="C208" s="15"/>
+      <c r="D208" s="16"/>
+      <c r="E208" s="17"/>
+      <c r="F208" s="17"/>
+      <c r="G208" s="18"/>
+      <c r="H208" s="19"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="14"/>
-      <c r="B209" s="15"/>
-      <c r="C209" s="16"/>
-      <c r="D209" s="17"/>
-      <c r="E209" s="18"/>
-      <c r="F209" s="18"/>
-      <c r="G209" s="19"/>
-      <c r="H209" s="20"/>
+      <c r="A209" s="13"/>
+      <c r="B209" s="14"/>
+      <c r="C209" s="15"/>
+      <c r="D209" s="16"/>
+      <c r="E209" s="17"/>
+      <c r="F209" s="20"/>
+      <c r="G209" s="18"/>
+      <c r="H209" s="19"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="14"/>
-      <c r="B210" s="15"/>
-      <c r="C210" s="16"/>
-      <c r="D210" s="17"/>
-      <c r="E210" s="18"/>
-      <c r="F210" s="18"/>
-      <c r="G210" s="19"/>
-      <c r="H210" s="20"/>
+      <c r="A210" s="13"/>
+      <c r="B210" s="14"/>
+      <c r="C210" s="15"/>
+      <c r="D210" s="16"/>
+      <c r="E210" s="17"/>
+      <c r="F210" s="17"/>
+      <c r="G210" s="18"/>
+      <c r="H210" s="19"/>
     </row>
     <row r="211" spans="1:8">
-      <c r="A211" s="14"/>
-      <c r="B211" s="15"/>
-      <c r="C211" s="16"/>
-      <c r="D211" s="17"/>
-      <c r="E211" s="18"/>
-      <c r="F211" s="18"/>
-      <c r="G211" s="19"/>
-      <c r="H211" s="20"/>
+      <c r="A211" s="13"/>
+      <c r="B211" s="14"/>
+      <c r="C211" s="15"/>
+      <c r="D211" s="16"/>
+      <c r="E211" s="17"/>
+      <c r="F211" s="17"/>
+      <c r="G211" s="18"/>
+      <c r="H211" s="19"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="14"/>
-      <c r="B212" s="15"/>
-      <c r="C212" s="16"/>
-      <c r="D212" s="17"/>
-      <c r="E212" s="18"/>
-      <c r="F212" s="18"/>
-      <c r="G212" s="19"/>
-      <c r="H212" s="20"/>
+      <c r="A212" s="13"/>
+      <c r="B212" s="14"/>
+      <c r="C212" s="15"/>
+      <c r="D212" s="16"/>
+      <c r="E212" s="17"/>
+      <c r="F212" s="17"/>
+      <c r="G212" s="18"/>
+      <c r="H212" s="19"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="14"/>
-      <c r="B213" s="15"/>
-      <c r="C213" s="16"/>
-      <c r="D213" s="17"/>
-      <c r="E213" s="18"/>
-      <c r="F213" s="18"/>
-      <c r="G213" s="19"/>
-      <c r="H213" s="20"/>
+      <c r="A213" s="13"/>
+      <c r="B213" s="14"/>
+      <c r="C213" s="15"/>
+      <c r="D213" s="16"/>
+      <c r="E213" s="17"/>
+      <c r="F213" s="17"/>
+      <c r="G213" s="18"/>
+      <c r="H213" s="19"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="14"/>
-      <c r="B214" s="15"/>
-      <c r="C214" s="16"/>
-      <c r="D214" s="17"/>
-      <c r="E214" s="18"/>
-      <c r="F214" s="18"/>
-      <c r="G214" s="19"/>
-      <c r="H214" s="20"/>
+      <c r="A214" s="13"/>
+      <c r="B214" s="14"/>
+      <c r="C214" s="15"/>
+      <c r="D214" s="16"/>
+      <c r="E214" s="17"/>
+      <c r="F214" s="17"/>
+      <c r="G214" s="18"/>
+      <c r="H214" s="19"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="14"/>
-      <c r="B215" s="15"/>
-      <c r="C215" s="16"/>
-      <c r="D215" s="17"/>
-      <c r="E215" s="18"/>
-      <c r="F215" s="18"/>
-      <c r="G215" s="19"/>
-      <c r="H215" s="20"/>
+      <c r="A215" s="13"/>
+      <c r="B215" s="14"/>
+      <c r="C215" s="15"/>
+      <c r="D215" s="16"/>
+      <c r="E215" s="17"/>
+      <c r="F215" s="17"/>
+      <c r="G215" s="18"/>
+      <c r="H215" s="19"/>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="14"/>
-      <c r="B216" s="15"/>
-      <c r="C216" s="16"/>
-      <c r="D216" s="17"/>
-      <c r="E216" s="18"/>
-      <c r="F216" s="18"/>
-      <c r="G216" s="19"/>
-      <c r="H216" s="20"/>
+      <c r="A216" s="13"/>
+      <c r="B216" s="14"/>
+      <c r="C216" s="15"/>
+      <c r="D216" s="16"/>
+      <c r="E216" s="17"/>
+      <c r="F216" s="17"/>
+      <c r="G216" s="18"/>
+      <c r="H216" s="19"/>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="14"/>
-      <c r="B217" s="15"/>
-      <c r="C217" s="16"/>
-      <c r="D217" s="17"/>
-      <c r="E217" s="18"/>
-      <c r="F217" s="18"/>
-      <c r="G217" s="19"/>
-      <c r="H217" s="20"/>
+      <c r="A217" s="13"/>
+      <c r="B217" s="14"/>
+      <c r="C217" s="15"/>
+      <c r="D217" s="16"/>
+      <c r="E217" s="17"/>
+      <c r="F217" s="17"/>
+      <c r="G217" s="18"/>
+      <c r="H217" s="19"/>
     </row>
     <row r="218" spans="1:8">
-      <c r="A218" s="14"/>
-      <c r="B218" s="15"/>
-      <c r="C218" s="16"/>
-      <c r="D218" s="17"/>
-      <c r="E218" s="22"/>
-      <c r="F218" s="18"/>
-      <c r="G218" s="19"/>
-      <c r="H218" s="20"/>
+      <c r="A218" s="13"/>
+      <c r="B218" s="14"/>
+      <c r="C218" s="15"/>
+      <c r="D218" s="16"/>
+      <c r="E218" s="17"/>
+      <c r="F218" s="17"/>
+      <c r="G218" s="18"/>
+      <c r="H218" s="19"/>
     </row>
     <row r="219" spans="1:8">
-      <c r="A219" s="14"/>
-      <c r="B219" s="15"/>
-      <c r="C219" s="16"/>
-      <c r="D219" s="17"/>
-      <c r="E219" s="18"/>
-      <c r="F219" s="18"/>
-      <c r="G219" s="19"/>
-      <c r="H219" s="20"/>
+      <c r="A219" s="13"/>
+      <c r="B219" s="14"/>
+      <c r="C219" s="15"/>
+      <c r="D219" s="16"/>
+      <c r="E219" s="21"/>
+      <c r="F219" s="17"/>
+      <c r="G219" s="18"/>
+      <c r="H219" s="19"/>
     </row>
     <row r="220" spans="1:8">
-      <c r="A220" s="14"/>
-      <c r="B220" s="15"/>
-      <c r="C220" s="16"/>
-      <c r="D220" s="17"/>
-      <c r="E220" s="18"/>
-      <c r="F220" s="18"/>
-      <c r="G220" s="19"/>
-      <c r="H220" s="20"/>
+      <c r="A220" s="13"/>
+      <c r="B220" s="14"/>
+      <c r="C220" s="15"/>
+      <c r="D220" s="16"/>
+      <c r="E220" s="17"/>
+      <c r="F220" s="17"/>
+      <c r="G220" s="18"/>
+      <c r="H220" s="19"/>
     </row>
     <row r="221" spans="1:8">
-      <c r="A221" s="14"/>
-      <c r="B221" s="15"/>
-      <c r="C221" s="16"/>
-      <c r="D221" s="17"/>
-      <c r="E221" s="18"/>
-      <c r="F221" s="18"/>
-      <c r="G221" s="19"/>
-      <c r="H221" s="20"/>
+      <c r="A221" s="13"/>
+      <c r="B221" s="14"/>
+      <c r="C221" s="15"/>
+      <c r="D221" s="16"/>
+      <c r="E221" s="17"/>
+      <c r="F221" s="17"/>
+      <c r="G221" s="18"/>
+      <c r="H221" s="19"/>
     </row>
     <row r="222" spans="1:8">
-      <c r="A222" s="14"/>
-      <c r="B222" s="15"/>
-      <c r="C222" s="16"/>
-      <c r="D222" s="17"/>
-      <c r="E222" s="18"/>
-      <c r="F222" s="18"/>
-      <c r="G222" s="19"/>
-      <c r="H222" s="20"/>
+      <c r="A222" s="13"/>
+      <c r="B222" s="14"/>
+      <c r="C222" s="15"/>
+      <c r="D222" s="16"/>
+      <c r="E222" s="17"/>
+      <c r="F222" s="17"/>
+      <c r="G222" s="18"/>
+      <c r="H222" s="19"/>
     </row>
     <row r="223" spans="1:8">
-      <c r="A223" s="14"/>
-      <c r="B223" s="15"/>
-      <c r="C223" s="16"/>
-      <c r="D223" s="17"/>
-      <c r="E223" s="18"/>
-      <c r="F223" s="18"/>
-      <c r="G223" s="19"/>
-      <c r="H223" s="20"/>
+      <c r="A223" s="13"/>
+      <c r="B223" s="14"/>
+      <c r="C223" s="15"/>
+      <c r="D223" s="16"/>
+      <c r="E223" s="17"/>
+      <c r="F223" s="17"/>
+      <c r="G223" s="18"/>
+      <c r="H223" s="19"/>
     </row>
     <row r="224" spans="1:8">
-      <c r="A224" s="14"/>
-      <c r="B224" s="15"/>
-      <c r="C224" s="16"/>
-      <c r="D224" s="17"/>
-      <c r="E224" s="18"/>
-      <c r="F224" s="18"/>
-      <c r="G224" s="19"/>
-      <c r="H224" s="20"/>
+      <c r="A224" s="13"/>
+      <c r="B224" s="14"/>
+      <c r="C224" s="15"/>
+      <c r="D224" s="16"/>
+      <c r="E224" s="17"/>
+      <c r="F224" s="17"/>
+      <c r="G224" s="18"/>
+      <c r="H224" s="19"/>
     </row>
     <row r="225" spans="1:8">
-      <c r="A225" s="14"/>
-      <c r="B225" s="15"/>
-      <c r="C225" s="16"/>
-      <c r="D225" s="17"/>
-      <c r="E225" s="18"/>
-      <c r="F225" s="18"/>
-      <c r="G225" s="19"/>
-      <c r="H225" s="20"/>
+      <c r="A225" s="13"/>
+      <c r="B225" s="14"/>
+      <c r="C225" s="15"/>
+      <c r="D225" s="16"/>
+      <c r="E225" s="17"/>
+      <c r="F225" s="17"/>
+      <c r="G225" s="18"/>
+      <c r="H225" s="19"/>
     </row>
     <row r="226" spans="1:8">
-      <c r="A226" s="14"/>
-      <c r="B226" s="15"/>
-      <c r="C226" s="16"/>
-      <c r="D226" s="17"/>
-      <c r="E226" s="18"/>
-      <c r="F226" s="18"/>
-      <c r="G226" s="19"/>
-      <c r="H226" s="20"/>
+      <c r="A226" s="13"/>
+      <c r="B226" s="14"/>
+      <c r="C226" s="15"/>
+      <c r="D226" s="16"/>
+      <c r="E226" s="17"/>
+      <c r="F226" s="17"/>
+      <c r="G226" s="18"/>
+      <c r="H226" s="19"/>
     </row>
     <row r="227" spans="1:8">
-      <c r="A227" s="14"/>
-      <c r="B227" s="15"/>
-      <c r="C227" s="16"/>
-      <c r="D227" s="17"/>
-      <c r="E227" s="18"/>
-      <c r="F227" s="18"/>
-      <c r="G227" s="19"/>
-      <c r="H227" s="20"/>
+      <c r="A227" s="13"/>
+      <c r="B227" s="14"/>
+      <c r="C227" s="15"/>
+      <c r="D227" s="16"/>
+      <c r="E227" s="17"/>
+      <c r="F227" s="17"/>
+      <c r="G227" s="18"/>
+      <c r="H227" s="19"/>
     </row>
     <row r="228" spans="1:8">
-      <c r="A228" s="14"/>
-      <c r="B228" s="15"/>
-      <c r="C228" s="16"/>
-      <c r="D228" s="17"/>
-      <c r="E228" s="18"/>
-      <c r="F228" s="18"/>
-      <c r="G228" s="19"/>
-      <c r="H228" s="20"/>
+      <c r="A228" s="13"/>
+      <c r="B228" s="14"/>
+      <c r="C228" s="15"/>
+      <c r="D228" s="16"/>
+      <c r="E228" s="17"/>
+      <c r="F228" s="17"/>
+      <c r="G228" s="18"/>
+      <c r="H228" s="19"/>
     </row>
     <row r="229" spans="1:8">
-      <c r="A229" s="14"/>
-      <c r="B229" s="15"/>
-      <c r="C229" s="16"/>
-      <c r="D229" s="17"/>
-      <c r="E229" s="18"/>
-      <c r="F229" s="18"/>
-      <c r="G229" s="19"/>
-      <c r="H229" s="20"/>
+      <c r="A229" s="13"/>
+      <c r="B229" s="14"/>
+      <c r="C229" s="15"/>
+      <c r="D229" s="16"/>
+      <c r="E229" s="17"/>
+      <c r="F229" s="17"/>
+      <c r="G229" s="18"/>
+      <c r="H229" s="19"/>
     </row>
     <row r="230" spans="1:8">
-      <c r="A230" s="14"/>
-      <c r="B230" s="15"/>
-      <c r="C230" s="16"/>
-      <c r="D230" s="17"/>
-      <c r="E230" s="18"/>
-      <c r="F230" s="18"/>
-      <c r="G230" s="19"/>
-      <c r="H230" s="20"/>
+      <c r="A230" s="13"/>
+      <c r="B230" s="14"/>
+      <c r="C230" s="15"/>
+      <c r="D230" s="16"/>
+      <c r="E230" s="17"/>
+      <c r="F230" s="17"/>
+      <c r="G230" s="18"/>
+      <c r="H230" s="19"/>
     </row>
     <row r="231" spans="1:8">
-      <c r="A231" s="14"/>
-      <c r="B231" s="15"/>
-      <c r="C231" s="16"/>
-      <c r="D231" s="17"/>
-      <c r="E231" s="18"/>
-      <c r="F231" s="18"/>
-      <c r="G231" s="19"/>
-      <c r="H231" s="20"/>
+      <c r="A231" s="13"/>
+      <c r="B231" s="14"/>
+      <c r="C231" s="15"/>
+      <c r="D231" s="16"/>
+      <c r="E231" s="17"/>
+      <c r="F231" s="17"/>
+      <c r="G231" s="18"/>
+      <c r="H231" s="19"/>
     </row>
     <row r="232" spans="1:8">
-      <c r="A232" s="14"/>
-      <c r="B232" s="15"/>
-      <c r="C232" s="16"/>
-      <c r="D232" s="17"/>
-      <c r="E232" s="18"/>
-      <c r="F232" s="18"/>
-      <c r="G232" s="19"/>
-      <c r="H232" s="20"/>
+      <c r="A232" s="13"/>
+      <c r="B232" s="14"/>
+      <c r="C232" s="15"/>
+      <c r="D232" s="16"/>
+      <c r="E232" s="17"/>
+      <c r="F232" s="17"/>
+      <c r="G232" s="18"/>
+      <c r="H232" s="19"/>
     </row>
     <row r="233" spans="1:8">
-      <c r="A233" s="14"/>
-      <c r="B233" s="15"/>
-      <c r="C233" s="16"/>
-      <c r="D233" s="17"/>
-      <c r="E233" s="18"/>
-      <c r="F233" s="18"/>
-      <c r="G233" s="19"/>
-      <c r="H233" s="20"/>
+      <c r="A233" s="13"/>
+      <c r="B233" s="14"/>
+      <c r="C233" s="15"/>
+      <c r="D233" s="16"/>
+      <c r="E233" s="17"/>
+      <c r="F233" s="17"/>
+      <c r="G233" s="18"/>
+      <c r="H233" s="19"/>
     </row>
     <row r="234" spans="1:8">
-      <c r="A234" s="14"/>
-      <c r="B234" s="15"/>
-      <c r="C234" s="16"/>
-      <c r="D234" s="17"/>
-      <c r="E234" s="22"/>
-      <c r="F234" s="18"/>
-      <c r="G234" s="19"/>
-      <c r="H234" s="20"/>
+      <c r="A234" s="13"/>
+      <c r="B234" s="14"/>
+      <c r="C234" s="15"/>
+      <c r="D234" s="16"/>
+      <c r="E234" s="17"/>
+      <c r="F234" s="17"/>
+      <c r="G234" s="18"/>
+      <c r="H234" s="19"/>
     </row>
     <row r="235" spans="1:8">
-      <c r="A235" s="23"/>
-      <c r="B235" s="24"/>
-      <c r="C235" s="16"/>
-      <c r="D235" s="17"/>
-      <c r="E235" s="18"/>
-      <c r="F235" s="18"/>
-      <c r="G235" s="19"/>
-      <c r="H235" s="20"/>
+      <c r="A235" s="13"/>
+      <c r="B235" s="14"/>
+      <c r="C235" s="15"/>
+      <c r="D235" s="16"/>
+      <c r="E235" s="21"/>
+      <c r="F235" s="17"/>
+      <c r="G235" s="18"/>
+      <c r="H235" s="19"/>
     </row>
     <row r="236" spans="1:8">
-      <c r="A236" s="23"/>
-      <c r="B236" s="24"/>
-      <c r="C236" s="16"/>
-      <c r="D236" s="17"/>
-      <c r="E236" s="18"/>
-      <c r="F236" s="18"/>
-      <c r="G236" s="19"/>
-      <c r="H236" s="20"/>
+      <c r="A236" s="22"/>
+      <c r="B236" s="23"/>
+      <c r="C236" s="15"/>
+      <c r="D236" s="16"/>
+      <c r="E236" s="17"/>
+      <c r="F236" s="17"/>
+      <c r="G236" s="18"/>
+      <c r="H236" s="19"/>
     </row>
     <row r="237" spans="1:8">
-      <c r="A237" s="23"/>
-      <c r="B237" s="24"/>
-      <c r="C237" s="16"/>
-      <c r="D237" s="17"/>
-      <c r="E237" s="18"/>
-      <c r="F237" s="18"/>
-      <c r="G237" s="19"/>
-      <c r="H237" s="20"/>
+      <c r="A237" s="22"/>
+      <c r="B237" s="23"/>
+      <c r="C237" s="15"/>
+      <c r="D237" s="16"/>
+      <c r="E237" s="17"/>
+      <c r="F237" s="17"/>
+      <c r="G237" s="18"/>
+      <c r="H237" s="19"/>
     </row>
     <row r="238" spans="1:8">
-      <c r="A238" s="23"/>
-      <c r="B238" s="24"/>
-      <c r="C238" s="16"/>
-      <c r="D238" s="17"/>
-      <c r="E238" s="16"/>
-      <c r="F238" s="18"/>
-      <c r="G238" s="19"/>
-      <c r="H238" s="20"/>
+      <c r="A238" s="22"/>
+      <c r="B238" s="23"/>
+      <c r="C238" s="15"/>
+      <c r="D238" s="16"/>
+      <c r="E238" s="17"/>
+      <c r="F238" s="17"/>
+      <c r="G238" s="18"/>
+      <c r="H238" s="19"/>
     </row>
     <row r="239" spans="1:8">
-      <c r="A239" s="25"/>
-      <c r="B239" s="26"/>
-      <c r="C239" s="16"/>
-      <c r="D239" s="17"/>
-      <c r="E239" s="16"/>
-      <c r="F239" s="18"/>
-      <c r="G239" s="19"/>
-      <c r="H239" s="20"/>
+      <c r="A239" s="22"/>
+      <c r="B239" s="23"/>
+      <c r="C239" s="15"/>
+      <c r="D239" s="16"/>
+      <c r="E239" s="15"/>
+      <c r="F239" s="17"/>
+      <c r="G239" s="18"/>
+      <c r="H239" s="19"/>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="24"/>
+      <c r="B240" s="25"/>
+      <c r="C240" s="15"/>
+      <c r="D240" s="16"/>
+      <c r="E240" s="15"/>
+      <c r="F240" s="17"/>
+      <c r="G240" s="18"/>
+      <c r="H240" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6670,6 +7511,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6813,12 +7660,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6829,12 +7670,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6850,6 +7685,12 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>

--- a/MC2020_E25.xlsx
+++ b/MC2020_E25.xlsx
@@ -5,33 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\ID7010\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7997429F-F3ED-4E28-B3BB-BE164E4E8F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A986684C-9033-406C-BE3D-B4D62580F664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="410">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -399,6 +393,9 @@
     <t>JAYAMAHA J.M.S.D.</t>
   </si>
   <si>
+    <t>AB</t>
+  </si>
+  <si>
     <t>2025/E/060</t>
   </si>
   <si>
@@ -1140,6 +1137,9 @@
     <t>2025/E/184</t>
   </si>
   <si>
+    <t>PUJATHMANAN V.</t>
+  </si>
+  <si>
     <t>2025/E/185</t>
   </si>
   <si>
@@ -1149,75 +1149,69 @@
     <t>2025/E/186</t>
   </si>
   <si>
+    <t>DANANJAYA D.T.T.</t>
+  </si>
+  <si>
     <t>2025/E/187</t>
   </si>
   <si>
+    <t>UDHA J.G.M.R.F.</t>
+  </si>
+  <si>
     <t>2025/E/188</t>
   </si>
   <si>
+    <t>KULATHUNGA K.A.L.J.</t>
+  </si>
+  <si>
     <t>2025/E/189</t>
   </si>
   <si>
+    <t>JEBARATHNA K.J.D.</t>
+  </si>
+  <si>
     <t>2025/E/190</t>
   </si>
   <si>
+    <t>RATHNAYAKA R.M.A.S.</t>
+  </si>
+  <si>
     <t>2025/E/191</t>
   </si>
   <si>
+    <t>RATHNAYAKE R.M.D.D.B.</t>
+  </si>
+  <si>
     <t>2025/E/192</t>
   </si>
   <si>
+    <t>NIMALARATHNE S.M.M.N.</t>
+  </si>
+  <si>
     <t>2025/E/193</t>
   </si>
   <si>
+    <t>WIJENANDANA U.M.C.R.</t>
+  </si>
+  <si>
     <t>2025/E/194</t>
   </si>
   <si>
+    <t>DE SILVA W.P.G.K.</t>
+  </si>
+  <si>
     <t>2025/E/195</t>
   </si>
   <si>
+    <t>HEWAGE H.E.S.R</t>
+  </si>
+  <si>
     <t>2024/E/187</t>
   </si>
   <si>
     <t>SANDARUWAN D.S.M.M.Y</t>
   </si>
   <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>PUJATHMANAN V.</t>
-  </si>
-  <si>
-    <t>DANANJAYA D.T.T.</t>
-  </si>
-  <si>
-    <t>UDHA J.G.M.R.F.</t>
-  </si>
-  <si>
-    <t>KULATHUNGA K.A.L.J.</t>
-  </si>
-  <si>
-    <t>JEBARATHNA K.J.D.</t>
-  </si>
-  <si>
-    <t>RATHNAYAKA R.M.A.S.</t>
-  </si>
-  <si>
-    <t>RATHNAYAKE R.M.D.D.B.</t>
-  </si>
-  <si>
-    <t>NIMALARATHNE S.M.M.N.</t>
-  </si>
-  <si>
-    <t>WIJENANDANA U.M.C.R.</t>
-  </si>
-  <si>
-    <t>DE SILVA W.P.G.K.</t>
-  </si>
-  <si>
-    <t>HEWAGE H.E.S.R</t>
-  </si>
-  <si>
     <t>2024/E/010</t>
   </si>
   <si>
@@ -1239,6 +1233,9 @@
     <t>NILANJANA S.M.I.M.</t>
   </si>
   <si>
+    <t>2024/E/183</t>
+  </si>
+  <si>
     <t>2024/E/184</t>
   </si>
   <si>
@@ -1254,13 +1251,10 @@
     <t>PETERSON N.S.</t>
   </si>
   <si>
-    <t>2024/E/183</t>
+    <t>2023/E/090</t>
   </si>
   <si>
     <t>2021/E/184</t>
-  </si>
-  <si>
-    <t>2023/E/090</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1262,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1276,14 +1270,42 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1291,71 +1313,47 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1367,50 +1365,50 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.39988402966399123"/>
+        <bgColor rgb="FF9DC3E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.39988402966399123"/>
+        <bgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.39988402966399123"/>
+        <bgColor rgb="FF9DC3E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.39988402966399123"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.39988402966399123"/>
+        <bgColor rgb="FF8FAADC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.39988402966399123"/>
+        <bgColor rgb="FFC9C9C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1440,155 +1438,231 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
-    <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="60% - Accent2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="60% - Accent3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="60% - Accent4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="60% - Accent5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="60% - Accent6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Comma" xfId="10" builtinId="3"/>
-    <cellStyle name="Neutral 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Neutral 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Title 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 3" xfId="10" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Title 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF9C6500"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC9C9C9"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF8FAADC"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFA9D18E"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFEB9C"/>
+      <rgbColor rgb="FF9DC3E6"/>
+      <rgbColor rgb="FFF4B183"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFD966"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFBF00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF44546A"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFBE480A"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF242424"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1605,10 +1679,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1713,49 +1787,45 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -1763,33 +1833,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -1802,13 +1863,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1818,15 +1873,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -1834,7 +1887,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -1842,11 +1894,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1858,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M240"/>
+  <dimension ref="A1:L240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -1868,7 +1920,7 @@
     <col min="8" max="8" width="15.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1">
+    <row r="1" spans="1:12" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1893,5620 +1945,5820 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="10" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="33" t="s">
-        <v>383</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="C2" s="39">
+        <v>60</v>
+      </c>
+      <c r="D2" s="7">
         <v>82</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="8">
         <v>72</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="8">
+        <v>71</v>
+      </c>
       <c r="G2" s="9">
         <v>35</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L2" s="39"/>
-      <c r="M2" s="38"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="10" t="s">
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="9">
         <v>70</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>82</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="8">
         <v>72</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="8">
+        <v>71</v>
+      </c>
       <c r="G3" s="9">
         <v>51</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L3" s="39"/>
-      <c r="M3" s="38"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="10" t="s">
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="9">
         <v>60</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>75</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="8">
         <v>59</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="8">
+        <v>63</v>
+      </c>
       <c r="G4" s="9">
         <v>53</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="38"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="10" t="s">
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="9">
         <v>42</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>86</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="8">
         <v>65</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="8">
+        <v>77</v>
+      </c>
       <c r="G5" s="9">
         <v>63</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="38"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="11" t="s">
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="9">
         <v>36</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>99</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="8">
         <v>64</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="8">
+        <v>81</v>
+      </c>
       <c r="G6" s="9">
         <v>46</v>
       </c>
-      <c r="H6" s="7">
-        <v>28.571428599999997</v>
-      </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="38"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="11" t="s">
+      <c r="H6" s="10">
+        <v>28.571428600000001</v>
+      </c>
+      <c r="L6" s="11"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="9">
         <v>70</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>68.5</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="8">
         <v>64</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="8">
+        <v>70</v>
+      </c>
       <c r="G7" s="9">
         <v>60</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L7" s="39"/>
-      <c r="M7" s="38"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="11" t="s">
+      <c r="L7" s="11"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="9">
         <v>70</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>53</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="8">
         <v>80</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="40">
+        <v>71</v>
+      </c>
       <c r="G8" s="9">
         <v>59</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="38"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="11" t="s">
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="9">
         <v>54</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>82.5</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="8">
         <v>71</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="8">
+        <v>77</v>
+      </c>
       <c r="G9" s="9">
         <v>64</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L9" s="39"/>
-      <c r="M9" s="38"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="11" t="s">
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="9">
         <v>54</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>82.5</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="8">
         <v>68</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="8">
+        <v>77</v>
+      </c>
       <c r="G10" s="9">
         <v>42</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L10" s="39"/>
-      <c r="M10" s="38"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="11" t="s">
+      <c r="L10" s="11"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="9">
         <v>66</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>91</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="8">
         <v>82</v>
       </c>
-      <c r="F11" s="5"/>
+      <c r="F11" s="8">
+        <v>49</v>
+      </c>
       <c r="G11" s="9">
         <v>49</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L11" s="39"/>
-      <c r="M11" s="38"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="11" t="s">
+      <c r="L11" s="11"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="9">
         <v>52</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>95</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="8">
         <v>71</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="F12" s="8">
+        <v>80</v>
+      </c>
       <c r="G12" s="9">
         <v>57</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L12" s="39"/>
-      <c r="M12" s="38"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="11" t="s">
+      <c r="L12" s="11"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="9">
         <v>12</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>71</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="8">
         <v>64</v>
       </c>
-      <c r="F13" s="5"/>
+      <c r="F13" s="8">
+        <v>94</v>
+      </c>
       <c r="G13" s="9">
         <v>42</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L13" s="39"/>
-      <c r="M13" s="38"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="11" t="s">
+      <c r="L13" s="11"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="9">
         <v>52</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>95</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="8">
         <v>64</v>
       </c>
-      <c r="F14" s="5"/>
+      <c r="F14" s="8">
+        <v>80</v>
+      </c>
       <c r="G14" s="9">
         <v>46</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="10">
         <v>100</v>
       </c>
-      <c r="L14" s="39"/>
-      <c r="M14" s="38"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="11" t="s">
+      <c r="L14" s="11"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="13" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="9">
         <v>54</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>91</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="8">
         <v>88</v>
       </c>
-      <c r="F15" s="5"/>
+      <c r="F15" s="8">
+        <v>87</v>
+      </c>
       <c r="G15" s="9">
         <v>55</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="10">
         <v>100</v>
       </c>
-      <c r="L15" s="39"/>
-      <c r="M15" s="38"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="11" t="s">
+      <c r="L15" s="11"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C16" s="9">
         <v>58</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>80.5</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="8">
         <v>97</v>
       </c>
-      <c r="F16" s="5"/>
+      <c r="F16" s="8">
+        <v>81</v>
+      </c>
       <c r="G16" s="9">
         <v>62</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L16" s="39"/>
-      <c r="M16" s="38"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="11" t="s">
+      <c r="L16" s="11"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C17" s="9">
         <v>50</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>76</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="8">
         <v>73</v>
       </c>
-      <c r="F17" s="5"/>
+      <c r="F17" s="8">
+        <v>78</v>
+      </c>
       <c r="G17" s="9">
         <v>70</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L17" s="39"/>
-      <c r="M17" s="38"/>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="11" t="s">
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="13" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="9">
         <v>64</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>92.5</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="8">
         <v>75</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="8">
+        <v>88</v>
+      </c>
       <c r="G18" s="9">
         <v>57</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L18" s="39"/>
-      <c r="M18" s="38"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="11" t="s">
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="13" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="9">
         <v>54</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>91</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="8">
         <v>73</v>
       </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="8">
+        <v>87</v>
+      </c>
       <c r="G19" s="9">
         <v>77</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L19" s="39"/>
-      <c r="M19" s="38"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="11" t="s">
+      <c r="L19" s="11"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
       <c r="C20" s="9">
         <v>66</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>91</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="8">
         <v>83</v>
       </c>
-      <c r="F20" s="5"/>
+      <c r="F20" s="8">
+        <v>49</v>
+      </c>
       <c r="G20" s="9">
         <v>53</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L20" s="39"/>
-      <c r="M20" s="38"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="11" t="s">
+      <c r="L20" s="11"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="9">
         <v>54</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>79</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="8">
         <v>73</v>
       </c>
-      <c r="F21" s="5"/>
+      <c r="F21" s="8">
+        <v>72</v>
+      </c>
       <c r="G21" s="9">
         <v>58</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L21" s="39"/>
-      <c r="M21" s="38"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="11" t="s">
+      <c r="L21" s="11"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="13" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="9">
         <v>30</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>92</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="8">
         <v>62</v>
       </c>
-      <c r="F22" s="5"/>
+      <c r="F22" s="8">
+        <v>94</v>
+      </c>
       <c r="G22" s="9">
         <v>51</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L22" s="39"/>
-      <c r="M22" s="38"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="11" t="s">
+      <c r="L22" s="11"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="13" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="9">
         <v>32</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>89</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="8">
         <v>68</v>
       </c>
-      <c r="F23" s="5"/>
+      <c r="F23" s="8">
+        <v>77</v>
+      </c>
       <c r="G23" s="9">
         <v>40</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L23" s="39"/>
-      <c r="M23" s="38"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="11" t="s">
+      <c r="L23" s="11"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="13" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="9">
         <v>26</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>84</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="8">
         <v>90</v>
       </c>
-      <c r="F24" s="5"/>
+      <c r="F24" s="8">
+        <v>69</v>
+      </c>
       <c r="G24" s="9">
         <v>64</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L24" s="39"/>
-      <c r="M24" s="38"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="11" t="s">
+      <c r="L24" s="11"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="13" t="s">
         <v>55</v>
       </c>
       <c r="C25" s="9">
         <v>26</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>84</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="8">
         <v>67</v>
       </c>
-      <c r="F25" s="5"/>
+      <c r="F25" s="8">
+        <v>69</v>
+      </c>
       <c r="G25" s="9">
         <v>41</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L25" s="39"/>
-      <c r="M25" s="38"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="11" t="s">
+      <c r="L25" s="11"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="13" t="s">
         <v>57</v>
       </c>
       <c r="C26" s="9">
         <v>50</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>76</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="8">
         <v>55</v>
       </c>
-      <c r="F26" s="5"/>
+      <c r="F26" s="8">
+        <v>78</v>
+      </c>
       <c r="G26" s="9">
         <v>42</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L26" s="39"/>
-      <c r="M26" s="38"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="11" t="s">
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="13" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="9">
         <v>44</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>85</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="8">
         <v>96</v>
       </c>
-      <c r="F27" s="5"/>
+      <c r="F27" s="8">
+        <v>69</v>
+      </c>
       <c r="G27" s="9">
         <v>61</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L27" s="39"/>
-      <c r="M27" s="38"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="11" t="s">
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="13" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="9">
         <v>26</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>84</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="8">
         <v>71</v>
       </c>
-      <c r="F28" s="5"/>
+      <c r="F28" s="8">
+        <v>69</v>
+      </c>
       <c r="G28" s="9">
         <v>51</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L28" s="39"/>
-      <c r="M28" s="38"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="11" t="s">
+      <c r="L28" s="11"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="9">
         <v>50</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>79</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="8">
         <v>78</v>
       </c>
-      <c r="F29" s="5"/>
+      <c r="F29" s="8">
+        <v>74</v>
+      </c>
       <c r="G29" s="9">
         <v>51</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L29" s="39"/>
-      <c r="M29" s="38"/>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="11" t="s">
+      <c r="L29" s="11"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C30" s="9">
         <v>52</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>95</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="8">
         <v>69</v>
       </c>
-      <c r="F30" s="5"/>
+      <c r="F30" s="8">
+        <v>80</v>
+      </c>
       <c r="G30" s="9">
         <v>41</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L30" s="39"/>
-      <c r="M30" s="38"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="11" t="s">
+      <c r="L30" s="11"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="9">
         <v>18</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>98</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="8">
         <v>76</v>
       </c>
-      <c r="F31" s="5"/>
+      <c r="F31" s="8">
+        <v>90</v>
+      </c>
       <c r="G31" s="9">
         <v>68</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="10">
         <v>100</v>
       </c>
-      <c r="L31" s="39"/>
-      <c r="M31" s="38"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="11" t="s">
+      <c r="L31" s="11"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="13" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="9">
         <v>52</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>80</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="8">
         <v>72</v>
       </c>
-      <c r="F32" s="5"/>
+      <c r="F32" s="8">
+        <v>70</v>
+      </c>
       <c r="G32" s="9">
         <v>61</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="10">
         <v>100</v>
       </c>
-      <c r="L32" s="39"/>
-      <c r="M32" s="38"/>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="11" t="s">
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C33" s="9">
         <v>50</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>79</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="8">
         <v>70</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="F33" s="8">
+        <v>74</v>
+      </c>
       <c r="G33" s="9">
         <v>62</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L33" s="39"/>
-      <c r="M33" s="38"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="11" t="s">
+      <c r="L33" s="11"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C34" s="9">
         <v>30</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <v>82</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="8">
         <v>64</v>
       </c>
-      <c r="F34" s="5"/>
+      <c r="F34" s="8">
+        <v>80</v>
+      </c>
       <c r="G34" s="9">
         <v>55</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L34" s="39"/>
-      <c r="M34" s="38"/>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="11" t="s">
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="9">
         <v>30</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>82</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="8">
         <v>57</v>
       </c>
-      <c r="F35" s="5"/>
+      <c r="F35" s="8">
+        <v>66</v>
+      </c>
       <c r="G35" s="9">
         <v>45</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="10">
         <v>100</v>
       </c>
-      <c r="L35" s="39"/>
-      <c r="M35" s="38"/>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="11" t="s">
+      <c r="L35" s="11"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="13" t="s">
         <v>77</v>
       </c>
       <c r="C36" s="9">
         <v>70</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="7">
         <v>75</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="8">
         <v>57</v>
       </c>
-      <c r="F36" s="5"/>
+      <c r="F36" s="8">
+        <v>42</v>
+      </c>
       <c r="G36" s="9">
         <v>42</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L36" s="39"/>
-      <c r="M36" s="38"/>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="11" t="s">
+      <c r="L36" s="11"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="13" t="s">
         <v>79</v>
       </c>
       <c r="C37" s="9">
         <v>36</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="7">
         <v>99</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="8">
         <v>70</v>
       </c>
-      <c r="F37" s="5"/>
+      <c r="F37" s="8">
+        <v>81</v>
+      </c>
       <c r="G37" s="9">
         <v>52</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L37" s="39"/>
-      <c r="M37" s="38"/>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="11" t="s">
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="13" t="s">
         <v>81</v>
       </c>
       <c r="C38" s="9">
         <v>70</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="7">
         <v>75</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="8">
         <v>62</v>
       </c>
-      <c r="F38" s="5"/>
+      <c r="F38" s="8">
+        <v>83</v>
+      </c>
       <c r="G38" s="9">
         <v>42</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L38" s="39"/>
-      <c r="M38" s="38"/>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="11" t="s">
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="13" t="s">
         <v>83</v>
       </c>
       <c r="C39" s="9">
         <v>42</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="7">
         <v>86</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="8">
         <v>62</v>
       </c>
-      <c r="F39" s="5"/>
+      <c r="F39" s="8">
+        <v>77</v>
+      </c>
       <c r="G39" s="9">
         <v>67</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="10">
         <v>100</v>
       </c>
-      <c r="L39" s="39"/>
-      <c r="M39" s="38"/>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="11" t="s">
+      <c r="L39" s="11"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="13" t="s">
         <v>85</v>
       </c>
       <c r="C40" s="9">
         <v>44</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <v>92</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="8">
         <v>91</v>
       </c>
-      <c r="F40" s="5"/>
+      <c r="F40" s="8">
+        <v>95</v>
+      </c>
       <c r="G40" s="9">
         <v>69</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L40" s="39"/>
-      <c r="M40" s="38"/>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="11" t="s">
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="13" t="s">
         <v>87</v>
       </c>
       <c r="C41" s="9">
         <v>64</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <v>89</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="8">
         <v>91</v>
       </c>
-      <c r="F41" s="5"/>
+      <c r="F41" s="8">
+        <v>87</v>
+      </c>
       <c r="G41" s="9">
         <v>64</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="10">
         <v>100</v>
       </c>
-      <c r="L41" s="39"/>
-      <c r="M41" s="38"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="11" t="s">
+      <c r="L41" s="11"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="13" t="s">
         <v>89</v>
       </c>
       <c r="C42" s="9">
         <v>40</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>75.5</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="8">
         <v>80</v>
       </c>
-      <c r="F42" s="5"/>
+      <c r="F42" s="8">
+        <v>83</v>
+      </c>
       <c r="G42" s="9">
         <v>67</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L42" s="39"/>
-      <c r="M42" s="38"/>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="11" t="s">
+      <c r="L42" s="11"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="13" t="s">
         <v>91</v>
       </c>
       <c r="C43" s="9">
         <v>64</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="7">
         <v>88</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="8">
         <v>47</v>
       </c>
-      <c r="F43" s="5"/>
+      <c r="F43" s="8">
+        <v>93</v>
+      </c>
       <c r="G43" s="9">
         <v>54</v>
       </c>
-      <c r="H43" s="7">
+      <c r="H43" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L43" s="39"/>
-      <c r="M43" s="38"/>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="11" t="s">
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="13" t="s">
         <v>93</v>
       </c>
       <c r="C44" s="9">
         <v>46</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="7">
         <v>86</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="8">
         <v>73</v>
       </c>
-      <c r="F44" s="5"/>
+      <c r="F44" s="8">
+        <v>83</v>
+      </c>
       <c r="G44" s="9">
         <v>46</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="10">
         <v>100</v>
       </c>
-      <c r="L44" s="39"/>
-      <c r="M44" s="38"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="11" t="s">
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="13" t="s">
         <v>95</v>
       </c>
       <c r="C45" s="9">
         <v>34</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="7">
         <v>90</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="8">
         <v>70</v>
       </c>
-      <c r="F45" s="5"/>
+      <c r="F45" s="8">
+        <v>99</v>
+      </c>
       <c r="G45" s="9">
         <v>44</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L45" s="39"/>
-      <c r="M45" s="38"/>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="11" t="s">
+      <c r="L45" s="11"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="13" t="s">
         <v>97</v>
       </c>
       <c r="C46" s="9">
         <v>40</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="7">
         <v>75.5</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="8">
         <v>74</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="F46" s="8">
+        <v>83</v>
+      </c>
       <c r="G46" s="9">
         <v>50</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L46" s="39"/>
-      <c r="M46" s="38"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="11" t="s">
+      <c r="L46" s="11"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="13" t="s">
         <v>99</v>
       </c>
       <c r="C47" s="9">
         <v>46</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="7">
         <v>86</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="8">
         <v>65</v>
       </c>
-      <c r="F47" s="5"/>
+      <c r="F47" s="8">
+        <v>83</v>
+      </c>
       <c r="G47" s="9">
         <v>68</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L47" s="39"/>
-      <c r="M47" s="38"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="11" t="s">
+      <c r="L47" s="11"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="13" t="s">
         <v>101</v>
       </c>
       <c r="C48" s="9">
         <v>18</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="7">
         <v>98</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="8">
         <v>74</v>
       </c>
-      <c r="F48" s="5"/>
+      <c r="F48" s="8">
+        <v>90</v>
+      </c>
       <c r="G48" s="9">
         <v>55</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L48" s="39"/>
-      <c r="M48" s="38"/>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="11" t="s">
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="13" t="s">
         <v>103</v>
       </c>
       <c r="C49" s="9">
         <v>52</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="7">
         <v>80</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="8">
         <v>67</v>
       </c>
-      <c r="F49" s="5"/>
+      <c r="F49" s="8">
+        <v>70</v>
+      </c>
       <c r="G49" s="9">
         <v>54</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L49" s="39"/>
-      <c r="M49" s="38"/>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="11" t="s">
+      <c r="L49" s="11"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="13" t="s">
         <v>105</v>
       </c>
       <c r="C50" s="9">
         <v>40</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="7">
         <v>86.5</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="8">
         <v>63</v>
       </c>
-      <c r="F50" s="5"/>
+      <c r="F50" s="8">
+        <v>66</v>
+      </c>
       <c r="G50" s="9">
         <v>68</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="10">
         <v>100</v>
       </c>
-      <c r="L50" s="39"/>
-      <c r="M50" s="38"/>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="11" t="s">
+      <c r="L50" s="11"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="13" t="s">
         <v>107</v>
       </c>
       <c r="C51" s="9">
         <v>52</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="7">
         <v>99</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="8">
         <v>61</v>
       </c>
-      <c r="F51" s="5"/>
+      <c r="F51" s="8">
+        <v>90</v>
+      </c>
       <c r="G51" s="9">
         <v>52</v>
       </c>
-      <c r="H51" s="7">
+      <c r="H51" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L51" s="39"/>
-      <c r="M51" s="38"/>
-    </row>
-    <row r="52" spans="1:13">
-      <c r="A52" s="11" t="s">
+      <c r="L51" s="11"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="13" t="s">
         <v>109</v>
       </c>
       <c r="C52" s="9">
         <v>52</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="7">
         <v>80</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="8">
         <v>72</v>
       </c>
-      <c r="F52" s="5"/>
+      <c r="F52" s="8">
+        <v>70</v>
+      </c>
       <c r="G52" s="9">
         <v>46</v>
       </c>
-      <c r="H52" s="7">
+      <c r="H52" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L52" s="39"/>
-      <c r="M52" s="38"/>
-    </row>
-    <row r="53" spans="1:13">
-      <c r="A53" s="11" t="s">
+      <c r="L52" s="11"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="13" t="s">
         <v>111</v>
       </c>
       <c r="C53" s="9">
         <v>26</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="7">
         <v>79</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="8">
         <v>72</v>
       </c>
-      <c r="F53" s="5"/>
+      <c r="F53" s="8">
+        <v>72</v>
+      </c>
       <c r="G53" s="9">
         <v>48</v>
       </c>
-      <c r="H53" s="7">
+      <c r="H53" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L53" s="39"/>
-      <c r="M53" s="38"/>
-    </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="11" t="s">
+      <c r="L53" s="11"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="13" t="s">
         <v>113</v>
       </c>
       <c r="C54" s="9">
         <v>64</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="7">
         <v>89</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="8">
         <v>57</v>
       </c>
-      <c r="F54" s="5"/>
+      <c r="F54" s="8">
+        <v>88</v>
+      </c>
       <c r="G54" s="9">
         <v>51</v>
       </c>
-      <c r="H54" s="7">
+      <c r="H54" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L54" s="39"/>
-      <c r="M54" s="38"/>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="11" t="s">
+      <c r="L54" s="11"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="13" t="s">
         <v>115</v>
       </c>
       <c r="C55" s="9">
         <v>44</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="7">
         <v>92</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="8">
         <v>78</v>
       </c>
-      <c r="F55" s="5"/>
+      <c r="F55" s="8">
+        <v>95</v>
+      </c>
       <c r="G55" s="9">
         <v>46</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55" s="10">
         <v>100</v>
       </c>
-      <c r="L55" s="39"/>
-      <c r="M55" s="38"/>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="11" t="s">
+      <c r="L55" s="11"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="13" t="s">
         <v>117</v>
       </c>
       <c r="C56" s="9">
         <v>60</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="7">
         <v>75</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="8">
         <v>51</v>
       </c>
-      <c r="F56" s="5"/>
+      <c r="F56" s="8">
+        <v>63</v>
+      </c>
       <c r="G56" s="9">
         <v>71</v>
       </c>
-      <c r="H56" s="7">
+      <c r="H56" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L56" s="39"/>
-      <c r="M56" s="38"/>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" s="11" t="s">
+      <c r="L56" s="11"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="13" t="s">
         <v>119</v>
       </c>
       <c r="C57" s="9">
         <v>32</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="7">
         <v>94</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="8">
         <v>68</v>
       </c>
-      <c r="F57" s="5"/>
+      <c r="F57" s="8">
+        <v>83</v>
+      </c>
       <c r="G57" s="9">
         <v>42</v>
       </c>
-      <c r="H57" s="7">
+      <c r="H57" s="10">
         <v>100</v>
       </c>
-      <c r="L57" s="39"/>
-      <c r="M57" s="38"/>
-    </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="11" t="s">
+      <c r="L57" s="11"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="13" t="s">
         <v>121</v>
       </c>
       <c r="C58" s="9">
         <v>66</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="7">
         <v>68.5</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F58" s="5"/>
+      <c r="E58" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F58" s="8">
+        <v>55</v>
+      </c>
       <c r="G58" s="9">
         <v>45</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58" s="10">
         <v>50</v>
       </c>
-      <c r="L58" s="39"/>
-      <c r="M58" s="38"/>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B59" s="27" t="s">
+      <c r="L58" s="11"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="12" t="s">
         <v>123</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="C59" s="9">
         <v>54</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="7">
         <v>91</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="8">
         <v>78</v>
       </c>
-      <c r="F59" s="5"/>
+      <c r="F59" s="8">
+        <v>87</v>
+      </c>
       <c r="G59" s="9">
         <v>64</v>
       </c>
-      <c r="H59" s="7">
+      <c r="H59" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L59" s="39"/>
-      <c r="M59" s="38"/>
-    </row>
-    <row r="60" spans="1:13">
-      <c r="A60" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B60" s="27" t="s">
+      <c r="L59" s="11"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="12" t="s">
         <v>125</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="C60" s="9">
         <v>48</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="7">
         <v>91.5</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="8">
         <v>83</v>
       </c>
-      <c r="F60" s="5"/>
+      <c r="F60" s="8">
+        <v>81</v>
+      </c>
       <c r="G60" s="9">
         <v>53</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H60" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L60" s="39"/>
-      <c r="M60" s="38"/>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="27" t="s">
+      <c r="L60" s="11"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="12" t="s">
         <v>127</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="C61" s="9">
         <v>48</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="7">
         <v>84.5</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="8">
         <v>69</v>
       </c>
-      <c r="F61" s="5"/>
+      <c r="F61" s="8">
+        <v>81</v>
+      </c>
       <c r="G61" s="9">
         <v>48</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H61" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L61" s="39"/>
-      <c r="M61" s="38"/>
-    </row>
-    <row r="62" spans="1:13">
-      <c r="A62" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="B62" s="27" t="s">
+      <c r="L61" s="11"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="12" t="s">
         <v>129</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C62" s="9">
         <v>54</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="7">
         <v>82.5</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="8">
         <v>82</v>
       </c>
-      <c r="F62" s="5"/>
+      <c r="F62" s="8">
+        <v>77</v>
+      </c>
       <c r="G62" s="9">
         <v>54</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L62" s="39"/>
-      <c r="M62" s="38"/>
-    </row>
-    <row r="63" spans="1:13">
-      <c r="A63" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="27" t="s">
+      <c r="L62" s="11"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="12" t="s">
         <v>131</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="C63" s="9">
         <v>60</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="7">
         <v>90</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="8">
         <v>78</v>
       </c>
-      <c r="F63" s="5"/>
+      <c r="F63" s="8">
+        <v>83</v>
+      </c>
       <c r="G63" s="9">
         <v>66</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L63" s="39"/>
-      <c r="M63" s="38"/>
-    </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B64" s="27" t="s">
+      <c r="L63" s="11"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="12" t="s">
         <v>133</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="C64" s="9">
         <v>32</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="7">
         <v>89</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="8">
         <v>65</v>
       </c>
-      <c r="F64" s="5"/>
+      <c r="F64" s="8">
+        <v>70</v>
+      </c>
       <c r="G64" s="9">
         <v>58</v>
       </c>
-      <c r="H64" s="7">
+      <c r="H64" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L64" s="39"/>
-      <c r="M64" s="38"/>
-    </row>
-    <row r="65" spans="1:13">
-      <c r="A65" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B65" s="27" t="s">
+      <c r="L64" s="11"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="12" t="s">
         <v>135</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="C65" s="9">
         <v>56</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="7">
         <v>89</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="8">
         <v>77</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="8">
+        <v>87</v>
+      </c>
       <c r="G65" s="9">
         <v>51</v>
       </c>
-      <c r="H65" s="7">
+      <c r="H65" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L65" s="39"/>
-      <c r="M65" s="38"/>
-    </row>
-    <row r="66" spans="1:13">
-      <c r="A66" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B66" s="27" t="s">
+      <c r="L65" s="11"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="12" t="s">
         <v>137</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="C66" s="9">
         <v>48</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="7">
         <v>57</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="8">
         <v>74</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="8">
+        <v>84</v>
+      </c>
       <c r="G66" s="9">
         <v>51</v>
       </c>
-      <c r="H66" s="7">
+      <c r="H66" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L66" s="39"/>
-      <c r="M66" s="38"/>
-    </row>
-    <row r="67" spans="1:13">
-      <c r="A67" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="27" t="s">
+      <c r="L66" s="11"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="12" t="s">
         <v>139</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="C67" s="9">
         <v>56</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="7">
         <v>92</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="8">
         <v>79</v>
       </c>
-      <c r="F67" s="5"/>
+      <c r="F67" s="8">
+        <v>87</v>
+      </c>
       <c r="G67" s="9">
         <v>55</v>
       </c>
-      <c r="H67" s="7">
+      <c r="H67" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L67" s="39"/>
-      <c r="M67" s="38"/>
-    </row>
-    <row r="68" spans="1:13">
-      <c r="A68" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B68" s="27" t="s">
+      <c r="L67" s="11"/>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="12" t="s">
         <v>141</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="C68" s="9">
         <v>70</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="7">
         <v>75</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="8">
         <v>39</v>
       </c>
-      <c r="F68" s="5"/>
+      <c r="F68" s="8">
+        <v>42</v>
+      </c>
       <c r="G68" s="9">
         <v>44</v>
       </c>
-      <c r="H68" s="7">
-        <v>53.846153799999996</v>
-      </c>
-      <c r="L68" s="39"/>
-      <c r="M68" s="38"/>
-    </row>
-    <row r="69" spans="1:13">
-      <c r="A69" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B69" s="27" t="s">
+      <c r="H68" s="10">
+        <v>53.846153800000003</v>
+      </c>
+      <c r="L68" s="11"/>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="12" t="s">
         <v>143</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="C69" s="9">
         <v>44</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="7">
         <v>91</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="8">
         <v>58</v>
       </c>
-      <c r="F69" s="5"/>
+      <c r="F69" s="8">
+        <v>66</v>
+      </c>
       <c r="G69" s="9">
         <v>64</v>
       </c>
-      <c r="H69" s="7">
+      <c r="H69" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L69" s="39"/>
-      <c r="M69" s="38"/>
-    </row>
-    <row r="70" spans="1:13">
-      <c r="A70" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" s="27" t="s">
+      <c r="L69" s="11"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="12" t="s">
         <v>145</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="C70" s="9">
         <v>48</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="7">
         <v>89.5</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="8">
         <v>76</v>
       </c>
-      <c r="F70" s="5"/>
+      <c r="F70" s="8">
+        <v>99</v>
+      </c>
       <c r="G70" s="9">
         <v>68</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H70" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L70" s="39"/>
-      <c r="M70" s="38"/>
-    </row>
-    <row r="71" spans="1:13">
-      <c r="A71" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B71" s="27" t="s">
+      <c r="L70" s="11"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="12" t="s">
         <v>147</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>148</v>
       </c>
       <c r="C71" s="9">
         <v>34</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="7">
         <v>90</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E71" s="8">
         <v>80</v>
       </c>
-      <c r="F71" s="5"/>
+      <c r="F71" s="8">
+        <v>83</v>
+      </c>
       <c r="G71" s="9">
         <v>59</v>
       </c>
-      <c r="H71" s="7">
+      <c r="H71" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L71" s="39"/>
-      <c r="M71" s="38"/>
-    </row>
-    <row r="72" spans="1:13">
-      <c r="A72" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B72" s="27" t="s">
+      <c r="L71" s="11"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="12" t="s">
         <v>149</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>150</v>
       </c>
       <c r="C72" s="9">
         <v>44</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="7">
         <v>91.5</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="8">
         <v>78</v>
       </c>
-      <c r="F72" s="5"/>
+      <c r="F72" s="8">
+        <v>71</v>
+      </c>
       <c r="G72" s="9">
         <v>51</v>
       </c>
-      <c r="H72" s="7">
+      <c r="H72" s="10">
         <v>76.923076899999998</v>
       </c>
-      <c r="L72" s="39"/>
-      <c r="M72" s="38"/>
-    </row>
-    <row r="73" spans="1:13">
-      <c r="A73" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B73" s="27" t="s">
+      <c r="L72" s="11"/>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="12" t="s">
         <v>151</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="C73" s="9">
         <v>70</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="7">
         <v>75</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="8">
         <v>72</v>
       </c>
-      <c r="F73" s="5"/>
+      <c r="F73" s="8">
+        <v>42</v>
+      </c>
       <c r="G73" s="9">
         <v>46</v>
       </c>
-      <c r="H73" s="7">
+      <c r="H73" s="10">
         <v>57.142857100000001</v>
       </c>
-      <c r="L73" s="39"/>
-      <c r="M73" s="38"/>
-    </row>
-    <row r="74" spans="1:13">
-      <c r="A74" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B74" s="27" t="s">
+      <c r="L73" s="11"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="12" t="s">
         <v>153</v>
       </c>
+      <c r="B74" s="13" t="s">
+        <v>154</v>
+      </c>
       <c r="C74" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F74" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G74" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H74" s="7">
+        <v>122</v>
+      </c>
+      <c r="H74" s="10">
         <v>7.1428570999999996</v>
       </c>
-      <c r="L74" s="39"/>
-      <c r="M74" s="38"/>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="A75" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B75" s="27" t="s">
+      <c r="L74" s="11"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="12" t="s">
         <v>155</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="C75" s="9">
         <v>52</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E75" s="5">
+      <c r="D75" s="41">
+        <v>57</v>
+      </c>
+      <c r="E75" s="8">
         <v>73</v>
       </c>
-      <c r="F75" s="5"/>
+      <c r="F75" s="8">
+        <v>93</v>
+      </c>
       <c r="G75" s="9">
         <v>64</v>
       </c>
-      <c r="H75" s="7">
+      <c r="H75" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L75" s="39"/>
-      <c r="M75" s="38"/>
-    </row>
-    <row r="76" spans="1:13">
-      <c r="A76" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B76" s="27" t="s">
+      <c r="L75" s="11"/>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="12" t="s">
         <v>157</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="C76" s="9">
         <v>48</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="7">
         <v>89.5</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="8">
         <v>80</v>
       </c>
-      <c r="F76" s="5"/>
+      <c r="F76" s="8">
+        <v>99</v>
+      </c>
       <c r="G76" s="9">
         <v>74</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H76" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L76" s="39"/>
-      <c r="M76" s="38"/>
-    </row>
-    <row r="77" spans="1:13">
-      <c r="A77" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B77" s="27" t="s">
+      <c r="L76" s="11"/>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="12" t="s">
         <v>159</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="C77" s="9">
         <v>58</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="7">
         <v>68.5</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E77" s="8">
         <v>85</v>
       </c>
-      <c r="F77" s="5"/>
+      <c r="F77" s="8">
+        <v>70</v>
+      </c>
       <c r="G77" s="9">
         <v>48</v>
       </c>
-      <c r="H77" s="7">
+      <c r="H77" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L77" s="39"/>
-      <c r="M77" s="38"/>
-    </row>
-    <row r="78" spans="1:13">
-      <c r="A78" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B78" s="27" t="s">
+      <c r="L77" s="11"/>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="12" t="s">
         <v>161</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="C78" s="9">
         <v>52</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="7">
         <v>99</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E78" s="8">
         <v>52</v>
       </c>
-      <c r="F78" s="5"/>
+      <c r="F78" s="8">
+        <v>90</v>
+      </c>
       <c r="G78" s="9">
         <v>64</v>
       </c>
-      <c r="H78" s="7">
+      <c r="H78" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L78" s="39"/>
-      <c r="M78" s="38"/>
-    </row>
-    <row r="79" spans="1:13">
-      <c r="A79" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" s="27" t="s">
+      <c r="L78" s="11"/>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="12" t="s">
         <v>163</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="C79" s="9">
         <v>52</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="7">
         <v>68</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="8">
         <v>86</v>
       </c>
-      <c r="F79" s="5"/>
+      <c r="F79" s="8">
+        <v>55</v>
+      </c>
       <c r="G79" s="9">
         <v>62</v>
       </c>
-      <c r="H79" s="7">
+      <c r="H79" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L79" s="39"/>
-      <c r="M79" s="38"/>
-    </row>
-    <row r="80" spans="1:13">
-      <c r="A80" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B80" s="27" t="s">
+      <c r="L79" s="11"/>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="12" t="s">
         <v>165</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>166</v>
       </c>
       <c r="C80" s="9">
         <v>26</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="7">
         <v>91</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="8">
         <v>75</v>
       </c>
-      <c r="F80" s="5"/>
+      <c r="F80" s="8">
+        <v>72</v>
+      </c>
       <c r="G80" s="9">
         <v>64</v>
       </c>
-      <c r="H80" s="7">
+      <c r="H80" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L80" s="39"/>
-      <c r="M80" s="38"/>
-    </row>
-    <row r="81" spans="1:13">
-      <c r="A81" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B81" s="27" t="s">
+      <c r="L80" s="11"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="12" t="s">
         <v>167</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>168</v>
       </c>
       <c r="C81" s="9">
         <v>56</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="7">
         <v>92</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="8">
         <v>85</v>
       </c>
-      <c r="F81" s="5"/>
+      <c r="F81" s="8">
+        <v>87</v>
+      </c>
       <c r="G81" s="9">
         <v>67</v>
       </c>
-      <c r="H81" s="7">
+      <c r="H81" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L81" s="39"/>
-      <c r="M81" s="38"/>
-    </row>
-    <row r="82" spans="1:13">
-      <c r="A82" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B82" s="27" t="s">
+      <c r="L81" s="11"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="12" t="s">
         <v>169</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="C82" s="9">
         <v>34</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="7">
         <v>90</v>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="8">
         <v>60</v>
       </c>
-      <c r="F82" s="5"/>
+      <c r="F82" s="8">
+        <v>83</v>
+      </c>
       <c r="G82" s="9">
         <v>46</v>
       </c>
-      <c r="H82" s="7">
+      <c r="H82" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L82" s="39"/>
-      <c r="M82" s="38"/>
-    </row>
-    <row r="83" spans="1:13">
-      <c r="A83" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B83" s="27" t="s">
+      <c r="L82" s="11"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="12" t="s">
         <v>171</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="C83" s="9">
         <v>44</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="7">
         <v>91</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="8">
         <v>62</v>
       </c>
-      <c r="F83" s="5"/>
+      <c r="F83" s="8">
+        <v>66</v>
+      </c>
       <c r="G83" s="9">
         <v>61</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L83" s="39"/>
-      <c r="M83" s="38"/>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="A84" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B84" s="27" t="s">
+      <c r="L83" s="11"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="12" t="s">
         <v>173</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="C84" s="9">
         <v>34</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="7">
         <v>90</v>
       </c>
-      <c r="E84" s="5">
+      <c r="E84" s="8">
         <v>79</v>
       </c>
-      <c r="F84" s="5"/>
+      <c r="F84" s="8">
+        <v>83</v>
+      </c>
       <c r="G84" s="9">
         <v>50</v>
       </c>
-      <c r="H84" s="7">
+      <c r="H84" s="10">
         <v>100</v>
       </c>
-      <c r="L84" s="39"/>
-      <c r="M84" s="38"/>
-    </row>
-    <row r="85" spans="1:13">
-      <c r="A85" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B85" s="27" t="s">
+      <c r="L84" s="11"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="12" t="s">
         <v>175</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="C85" s="9">
         <v>48</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="7">
         <v>89.5</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="8">
         <v>85</v>
       </c>
-      <c r="F85" s="5"/>
+      <c r="F85" s="8">
+        <v>99</v>
+      </c>
       <c r="G85" s="9">
         <v>71</v>
       </c>
-      <c r="H85" s="7">
+      <c r="H85" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L85" s="39"/>
-      <c r="M85" s="38"/>
-    </row>
-    <row r="86" spans="1:13">
-      <c r="A86" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B86" s="27" t="s">
+      <c r="L85" s="11"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="12" t="s">
         <v>177</v>
       </c>
+      <c r="B86" s="13" t="s">
+        <v>178</v>
+      </c>
       <c r="C86" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F86" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G86" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H86" s="7">
+        <v>122</v>
+      </c>
+      <c r="H86" s="10">
         <v>0</v>
       </c>
-      <c r="L86" s="39"/>
-      <c r="M86" s="38"/>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B87" s="27" t="s">
+      <c r="L86" s="11"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="12" t="s">
         <v>179</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>180</v>
       </c>
       <c r="C87" s="9">
         <v>40</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="7">
         <v>75.5</v>
       </c>
-      <c r="E87" s="5">
+      <c r="E87" s="8">
         <v>71</v>
       </c>
-      <c r="F87" s="5"/>
+      <c r="F87" s="8">
+        <v>69</v>
+      </c>
       <c r="G87" s="9">
         <v>46</v>
       </c>
-      <c r="H87" s="7">
+      <c r="H87" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L87" s="39"/>
-      <c r="M87" s="38"/>
-    </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B88" s="27" t="s">
+      <c r="L87" s="11"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="12" t="s">
         <v>181</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="C88" s="9">
         <v>52</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="7">
         <v>88</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F88" s="5"/>
+      <c r="E88" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F88" s="8">
+        <v>93</v>
+      </c>
       <c r="G88" s="9">
         <v>58</v>
       </c>
-      <c r="H88" s="7">
+      <c r="H88" s="10">
         <v>35.714285699999998</v>
       </c>
-      <c r="L88" s="39"/>
-      <c r="M88" s="38"/>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B89" s="27" t="s">
+      <c r="L88" s="11"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="12" t="s">
         <v>183</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="C89" s="9">
         <v>58</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="7">
         <v>80.5</v>
       </c>
-      <c r="E89" s="5">
+      <c r="E89" s="8">
         <v>55</v>
       </c>
-      <c r="F89" s="5"/>
+      <c r="F89" s="8">
+        <v>81</v>
+      </c>
       <c r="G89" s="9">
         <v>51</v>
       </c>
-      <c r="H89" s="7">
+      <c r="H89" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L89" s="39"/>
-      <c r="M89" s="38"/>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B90" s="27" t="s">
+      <c r="L89" s="11"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" s="12" t="s">
         <v>185</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>186</v>
       </c>
       <c r="C90" s="9">
         <v>46</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="7">
         <v>86</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="8">
         <v>59</v>
       </c>
-      <c r="F90" s="5"/>
+      <c r="F90" s="8">
+        <v>83</v>
+      </c>
       <c r="G90" s="9">
         <v>52</v>
       </c>
-      <c r="H90" s="7">
+      <c r="H90" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L90" s="39"/>
-      <c r="M90" s="38"/>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B91" s="27" t="s">
+      <c r="L90" s="11"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" s="12" t="s">
         <v>187</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>188</v>
       </c>
       <c r="C91" s="9">
         <v>44</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="7">
         <v>82</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E91" s="8">
         <v>67</v>
       </c>
-      <c r="F91" s="5"/>
+      <c r="F91" s="8">
+        <v>71</v>
+      </c>
       <c r="G91" s="9">
         <v>62</v>
       </c>
-      <c r="H91" s="7">
+      <c r="H91" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L91" s="39"/>
-      <c r="M91" s="38"/>
-    </row>
-    <row r="92" spans="1:13">
-      <c r="A92" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="B92" s="27" t="s">
+      <c r="L91" s="11"/>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" s="12" t="s">
         <v>189</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>190</v>
       </c>
       <c r="C92" s="9">
         <v>38</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="7">
         <v>90</v>
       </c>
-      <c r="E92" s="5">
+      <c r="E92" s="8">
         <v>85</v>
       </c>
-      <c r="F92" s="5"/>
+      <c r="F92" s="40">
+        <v>71</v>
+      </c>
       <c r="G92" s="9">
         <v>56</v>
       </c>
-      <c r="H92" s="7">
+      <c r="H92" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L92" s="39"/>
-      <c r="M92" s="38"/>
-    </row>
-    <row r="93" spans="1:13">
-      <c r="A93" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B93" s="27" t="s">
+      <c r="L92" s="11"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="12" t="s">
         <v>191</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="C93" s="9">
         <v>44</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="7">
         <v>53</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E93" s="8">
         <v>69</v>
       </c>
-      <c r="F93" s="5"/>
+      <c r="F93" s="8">
+        <v>88</v>
+      </c>
       <c r="G93" s="9">
         <v>48</v>
       </c>
-      <c r="H93" s="7">
+      <c r="H93" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L93" s="39"/>
-      <c r="M93" s="38"/>
-    </row>
-    <row r="94" spans="1:13">
-      <c r="A94" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B94" s="27" t="s">
+      <c r="L93" s="11"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="12" t="s">
         <v>193</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="C94" s="9">
         <v>44</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="7">
         <v>53</v>
       </c>
-      <c r="E94" s="5">
+      <c r="E94" s="8">
         <v>80</v>
       </c>
-      <c r="F94" s="5"/>
+      <c r="F94" s="8">
+        <v>63</v>
+      </c>
       <c r="G94" s="9">
         <v>49</v>
       </c>
-      <c r="H94" s="7">
+      <c r="H94" s="10">
         <v>50</v>
       </c>
-      <c r="L94" s="39"/>
-      <c r="M94" s="38"/>
-    </row>
-    <row r="95" spans="1:13">
-      <c r="A95" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B95" s="27" t="s">
+      <c r="L94" s="11"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" s="12" t="s">
         <v>195</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>196</v>
       </c>
       <c r="C95" s="9">
         <v>70</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="7">
         <v>82</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E95" s="8">
         <v>67</v>
       </c>
-      <c r="F95" s="5"/>
+      <c r="F95" s="8">
+        <v>71</v>
+      </c>
       <c r="G95" s="9">
         <v>55</v>
       </c>
-      <c r="H95" s="7">
+      <c r="H95" s="10">
         <v>35.714285699999998</v>
       </c>
-      <c r="L95" s="39"/>
-      <c r="M95" s="38"/>
-    </row>
-    <row r="96" spans="1:13">
-      <c r="A96" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B96" s="27" t="s">
+      <c r="L95" s="11"/>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" s="12" t="s">
         <v>197</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>198</v>
       </c>
       <c r="C96" s="9">
         <v>60</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="7">
         <v>75</v>
       </c>
-      <c r="E96" s="5">
+      <c r="E96" s="8">
         <v>68</v>
       </c>
-      <c r="F96" s="5"/>
+      <c r="F96" s="8">
+        <v>63</v>
+      </c>
       <c r="G96" s="9">
         <v>46</v>
       </c>
-      <c r="H96" s="7">
+      <c r="H96" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L96" s="39"/>
-      <c r="M96" s="38"/>
-    </row>
-    <row r="97" spans="1:13">
-      <c r="A97" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B97" s="27" t="s">
+      <c r="L96" s="11"/>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" s="12" t="s">
         <v>199</v>
       </c>
+      <c r="B97" s="13" t="s">
+        <v>200</v>
+      </c>
       <c r="C97" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F97" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G97" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H97" s="7">
+        <v>122</v>
+      </c>
+      <c r="H97" s="10">
         <v>0</v>
       </c>
-      <c r="L97" s="39"/>
-      <c r="M97" s="38"/>
-    </row>
-    <row r="98" spans="1:13">
-      <c r="A98" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B98" s="27" t="s">
+      <c r="L97" s="11"/>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" s="12" t="s">
         <v>201</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="C98" s="9">
         <v>60</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="7">
         <v>75</v>
       </c>
-      <c r="E98" s="5">
+      <c r="E98" s="8">
         <v>75</v>
       </c>
-      <c r="F98" s="5"/>
+      <c r="F98" s="8">
+        <v>63</v>
+      </c>
       <c r="G98" s="9">
         <v>65</v>
       </c>
-      <c r="H98" s="7">
+      <c r="H98" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L98" s="39"/>
-      <c r="M98" s="38"/>
-    </row>
-    <row r="99" spans="1:13">
-      <c r="A99" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="B99" s="27" t="s">
+      <c r="L98" s="11"/>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" s="12" t="s">
         <v>203</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>204</v>
       </c>
       <c r="C99" s="9">
         <v>38</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="7">
         <v>90</v>
       </c>
-      <c r="E99" s="5">
+      <c r="E99" s="8">
         <v>64</v>
       </c>
-      <c r="F99" s="5"/>
+      <c r="F99" s="40">
+        <v>71</v>
+      </c>
       <c r="G99" s="9">
         <v>61</v>
       </c>
-      <c r="H99" s="7">
+      <c r="H99" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L99" s="39"/>
-      <c r="M99" s="38"/>
-    </row>
-    <row r="100" spans="1:13">
-      <c r="A100" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B100" s="26" t="s">
+      <c r="L99" s="11"/>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="5" t="s">
         <v>205</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="C100" s="9">
         <v>60</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="7">
         <v>82</v>
       </c>
-      <c r="E100" s="5">
+      <c r="E100" s="8">
         <v>74</v>
       </c>
-      <c r="F100" s="5"/>
+      <c r="F100" s="8">
+        <v>83</v>
+      </c>
       <c r="G100" s="9">
         <v>36</v>
       </c>
-      <c r="H100" s="7">
+      <c r="H100" s="10">
         <v>100</v>
       </c>
-      <c r="L100" s="39"/>
-      <c r="M100" s="38"/>
-    </row>
-    <row r="101" spans="1:13">
-      <c r="A101" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="B101" s="26" t="s">
+      <c r="L100" s="11"/>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="5" t="s">
         <v>207</v>
       </c>
+      <c r="B101" s="6" t="s">
+        <v>208</v>
+      </c>
       <c r="C101" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D101" s="8">
+        <v>122</v>
+      </c>
+      <c r="D101" s="7">
         <v>80.5</v>
       </c>
-      <c r="E101" s="5">
+      <c r="E101" s="8">
         <v>58</v>
       </c>
-      <c r="F101" s="5"/>
+      <c r="F101" s="8">
+        <v>81</v>
+      </c>
       <c r="G101" s="9">
         <v>64</v>
       </c>
-      <c r="H101" s="7">
+      <c r="H101" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L101" s="39"/>
-      <c r="M101" s="38"/>
-    </row>
-    <row r="102" spans="1:13">
-      <c r="A102" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="B102" s="26" t="s">
+      <c r="L101" s="11"/>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="5" t="s">
         <v>209</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="C102" s="9">
         <v>42</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="7">
         <v>86</v>
       </c>
-      <c r="E102" s="5">
+      <c r="E102" s="8">
         <v>53</v>
       </c>
-      <c r="F102" s="5"/>
+      <c r="F102" s="8">
+        <v>77</v>
+      </c>
       <c r="G102" s="9">
         <v>45</v>
       </c>
-      <c r="H102" s="7">
+      <c r="H102" s="10">
         <v>42.857142899999999</v>
       </c>
-      <c r="L102" s="39"/>
-      <c r="M102" s="38"/>
-    </row>
-    <row r="103" spans="1:13">
-      <c r="A103" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="B103" s="26" t="s">
+      <c r="L102" s="11"/>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" s="5" t="s">
         <v>211</v>
       </c>
+      <c r="B103" s="6" t="s">
+        <v>212</v>
+      </c>
       <c r="C103" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D103" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F103" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G103" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H103" s="7">
+        <v>122</v>
+      </c>
+      <c r="H103" s="10">
         <v>0</v>
       </c>
-      <c r="L103" s="39"/>
-      <c r="M103" s="38"/>
-    </row>
-    <row r="104" spans="1:13">
-      <c r="A104" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="B104" s="26" t="s">
+      <c r="L103" s="11"/>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" s="5" t="s">
         <v>213</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="C104" s="9">
         <v>64</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D104" s="7">
         <v>88</v>
       </c>
-      <c r="E104" s="5">
+      <c r="E104" s="8">
         <v>91</v>
       </c>
-      <c r="F104" s="5"/>
+      <c r="F104" s="8">
+        <v>93</v>
+      </c>
       <c r="G104" s="9">
         <v>69</v>
       </c>
-      <c r="H104" s="7">
+      <c r="H104" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L104" s="39"/>
-      <c r="M104" s="38"/>
-    </row>
-    <row r="105" spans="1:13">
-      <c r="A105" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B105" s="26" t="s">
+      <c r="L104" s="11"/>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" s="5" t="s">
         <v>215</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="C105" s="9">
         <v>28</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="7">
         <v>88</v>
       </c>
-      <c r="E105" s="5">
+      <c r="E105" s="8">
         <v>83</v>
       </c>
-      <c r="F105" s="5"/>
+      <c r="F105" s="8">
+        <v>100</v>
+      </c>
       <c r="G105" s="9">
         <v>35</v>
       </c>
-      <c r="H105" s="7">
+      <c r="H105" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L105" s="39"/>
-      <c r="M105" s="38"/>
-    </row>
-    <row r="106" spans="1:13">
-      <c r="A106" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="B106" s="26" t="s">
+      <c r="L105" s="11"/>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" s="5" t="s">
         <v>217</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="C106" s="9">
         <v>46</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="7">
         <v>86</v>
       </c>
-      <c r="E106" s="5">
+      <c r="E106" s="8">
         <v>48</v>
       </c>
-      <c r="F106" s="5"/>
+      <c r="F106" s="8">
+        <v>81</v>
+      </c>
       <c r="G106" s="9">
         <v>57</v>
       </c>
-      <c r="H106" s="7">
+      <c r="H106" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L106" s="39"/>
-      <c r="M106" s="38"/>
-    </row>
-    <row r="107" spans="1:13">
-      <c r="A107" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="B107" s="26" t="s">
+      <c r="L106" s="11"/>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" s="5" t="s">
         <v>219</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>220</v>
       </c>
       <c r="C107" s="9">
         <v>46</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="7">
         <v>91.5</v>
       </c>
-      <c r="E107" s="5">
+      <c r="E107" s="8">
         <v>71</v>
       </c>
-      <c r="F107" s="5"/>
+      <c r="F107" s="8">
+        <v>81</v>
+      </c>
       <c r="G107" s="9">
         <v>55</v>
       </c>
-      <c r="H107" s="7">
+      <c r="H107" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L107" s="39"/>
-      <c r="M107" s="38"/>
-    </row>
-    <row r="108" spans="1:13">
-      <c r="A108" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="B108" s="26" t="s">
+      <c r="L107" s="11"/>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" s="5" t="s">
         <v>221</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="C108" s="9">
         <v>18</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="7">
         <v>98</v>
       </c>
-      <c r="E108" s="5">
+      <c r="E108" s="8">
         <v>86</v>
       </c>
-      <c r="F108" s="5"/>
+      <c r="F108" s="8">
+        <v>94</v>
+      </c>
       <c r="G108" s="9">
         <v>63</v>
       </c>
-      <c r="H108" s="7">
+      <c r="H108" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L108" s="39"/>
-      <c r="M108" s="38"/>
-    </row>
-    <row r="109" spans="1:13">
-      <c r="A109" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="B109" s="26" t="s">
+      <c r="L108" s="11"/>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" s="5" t="s">
         <v>223</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="C109" s="9">
         <v>12</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="7">
         <v>71</v>
       </c>
-      <c r="E109" s="5">
+      <c r="E109" s="8">
         <v>69</v>
       </c>
-      <c r="F109" s="5"/>
+      <c r="F109" s="8">
+        <v>94</v>
+      </c>
       <c r="G109" s="9">
         <v>47</v>
       </c>
-      <c r="H109" s="7">
+      <c r="H109" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L109" s="39"/>
-      <c r="M109" s="38"/>
-    </row>
-    <row r="110" spans="1:13">
-      <c r="A110" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B110" s="26" t="s">
+      <c r="L109" s="11"/>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" s="5" t="s">
         <v>225</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="C110" s="9">
         <v>56</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="7">
         <v>92</v>
       </c>
-      <c r="E110" s="5">
+      <c r="E110" s="8">
         <v>81</v>
       </c>
-      <c r="F110" s="5"/>
+      <c r="F110" s="8">
+        <v>87</v>
+      </c>
       <c r="G110" s="9">
         <v>70</v>
       </c>
-      <c r="H110" s="7">
+      <c r="H110" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L110" s="39"/>
-      <c r="M110" s="38"/>
-    </row>
-    <row r="111" spans="1:13">
-      <c r="A111" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="B111" s="26" t="s">
+      <c r="L110" s="11"/>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" s="5" t="s">
         <v>227</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="C111" s="9">
         <v>52</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="7">
         <v>99</v>
       </c>
-      <c r="E111" s="5">
+      <c r="E111" s="8">
         <v>52</v>
       </c>
-      <c r="F111" s="5"/>
+      <c r="F111" s="8">
+        <v>42</v>
+      </c>
       <c r="G111" s="9">
         <v>44</v>
       </c>
-      <c r="H111" s="7">
+      <c r="H111" s="10">
         <v>57.142857100000001</v>
       </c>
-      <c r="L111" s="39"/>
-      <c r="M111" s="38"/>
-    </row>
-    <row r="112" spans="1:13">
-      <c r="A112" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B112" s="26" t="s">
+      <c r="L111" s="11"/>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" s="5" t="s">
         <v>229</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>230</v>
       </c>
       <c r="C112" s="9">
         <v>50</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="7">
         <v>79</v>
       </c>
-      <c r="E112" s="5">
+      <c r="E112" s="8">
         <v>72</v>
       </c>
-      <c r="F112" s="5"/>
+      <c r="F112" s="8">
+        <v>74</v>
+      </c>
       <c r="G112" s="9">
         <v>49</v>
       </c>
-      <c r="H112" s="7">
+      <c r="H112" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L112" s="39"/>
-      <c r="M112" s="38"/>
-    </row>
-    <row r="113" spans="1:13">
-      <c r="A113" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B113" s="26" t="s">
+      <c r="L112" s="11"/>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" s="5" t="s">
         <v>231</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="C113" s="9">
         <v>34</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="7">
         <v>68</v>
       </c>
-      <c r="E113" s="5">
+      <c r="E113" s="8">
         <v>62</v>
       </c>
-      <c r="F113" s="5"/>
+      <c r="F113" s="8">
+        <v>55</v>
+      </c>
       <c r="G113" s="9">
         <v>58</v>
       </c>
-      <c r="H113" s="7">
+      <c r="H113" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L113" s="39"/>
-      <c r="M113" s="38"/>
-    </row>
-    <row r="114" spans="1:13">
-      <c r="A114" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B114" s="26" t="s">
+      <c r="L113" s="11"/>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" s="5" t="s">
         <v>233</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="C114" s="9">
         <v>48</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="7">
         <v>96</v>
       </c>
-      <c r="E114" s="5">
+      <c r="E114" s="8">
         <v>79</v>
       </c>
-      <c r="F114" s="5"/>
+      <c r="F114" s="8">
+        <v>87</v>
+      </c>
       <c r="G114" s="9">
         <v>60</v>
       </c>
-      <c r="H114" s="7">
+      <c r="H114" s="10">
         <v>100</v>
       </c>
-      <c r="L114" s="39"/>
-      <c r="M114" s="38"/>
-    </row>
-    <row r="115" spans="1:13">
-      <c r="A115" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B115" s="26" t="s">
+      <c r="L114" s="11"/>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" s="5" t="s">
         <v>235</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>236</v>
       </c>
       <c r="C115" s="9">
         <v>40</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="7">
         <v>86.5</v>
       </c>
-      <c r="E115" s="5">
+      <c r="E115" s="8">
         <v>64</v>
       </c>
-      <c r="F115" s="5"/>
+      <c r="F115" s="8">
+        <v>66</v>
+      </c>
       <c r="G115" s="9">
         <v>58</v>
       </c>
-      <c r="H115" s="7">
+      <c r="H115" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L115" s="39"/>
-      <c r="M115" s="38"/>
-    </row>
-    <row r="116" spans="1:13">
-      <c r="A116" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="B116" s="26" t="s">
+      <c r="L115" s="11"/>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" s="5" t="s">
         <v>237</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="C116" s="9">
         <v>48</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D116" s="7">
         <v>96</v>
       </c>
-      <c r="E116" s="5">
+      <c r="E116" s="8">
         <v>62</v>
       </c>
-      <c r="F116" s="5"/>
+      <c r="F116" s="8">
+        <v>87</v>
+      </c>
       <c r="G116" s="9">
         <v>51</v>
       </c>
-      <c r="H116" s="7">
+      <c r="H116" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L116" s="39"/>
-      <c r="M116" s="38"/>
-    </row>
-    <row r="117" spans="1:13">
-      <c r="A117" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="B117" s="26" t="s">
+      <c r="L116" s="11"/>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" s="5" t="s">
         <v>239</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="C117" s="9">
         <v>32</v>
       </c>
-      <c r="D117" s="8">
+      <c r="D117" s="7">
         <v>94</v>
       </c>
-      <c r="E117" s="5">
+      <c r="E117" s="8">
         <v>86</v>
       </c>
-      <c r="F117" s="5"/>
+      <c r="F117" s="8">
+        <v>78</v>
+      </c>
       <c r="G117" s="9">
         <v>58</v>
       </c>
-      <c r="H117" s="7">
+      <c r="H117" s="10">
         <v>100</v>
       </c>
-      <c r="L117" s="39"/>
-      <c r="M117" s="38"/>
-    </row>
-    <row r="118" spans="1:13">
-      <c r="A118" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B118" s="26" t="s">
+      <c r="L117" s="11"/>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" s="5" t="s">
         <v>241</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="C118" s="9">
         <v>38</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D118" s="7">
         <v>90</v>
       </c>
-      <c r="E118" s="5">
+      <c r="E118" s="8">
         <v>64</v>
       </c>
-      <c r="F118" s="5"/>
+      <c r="F118" s="40">
+        <v>71</v>
+      </c>
       <c r="G118" s="9">
         <v>58</v>
       </c>
-      <c r="H118" s="7">
+      <c r="H118" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L118" s="39"/>
-      <c r="M118" s="38"/>
-    </row>
-    <row r="119" spans="1:13">
-      <c r="A119" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="B119" s="26" t="s">
+      <c r="L118" s="11"/>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" s="5" t="s">
         <v>243</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="C119" s="9">
         <v>28</v>
       </c>
-      <c r="D119" s="8">
+      <c r="D119" s="7">
         <v>88</v>
       </c>
-      <c r="E119" s="5">
+      <c r="E119" s="8">
         <v>75</v>
       </c>
-      <c r="F119" s="5"/>
+      <c r="F119" s="8">
+        <v>100</v>
+      </c>
       <c r="G119" s="9">
         <v>38</v>
       </c>
-      <c r="H119" s="7">
+      <c r="H119" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L119" s="39"/>
-      <c r="M119" s="38"/>
-    </row>
-    <row r="120" spans="1:13">
-      <c r="A120" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B120" s="26" t="s">
+      <c r="L119" s="11"/>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" s="5" t="s">
         <v>245</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="C120" s="9">
         <v>48</v>
       </c>
-      <c r="D120" s="8">
+      <c r="D120" s="7">
         <v>96</v>
       </c>
-      <c r="E120" s="5">
+      <c r="E120" s="8">
         <v>69</v>
       </c>
-      <c r="F120" s="5"/>
+      <c r="F120" s="8">
+        <v>87</v>
+      </c>
       <c r="G120" s="9">
         <v>60</v>
       </c>
-      <c r="H120" s="7">
+      <c r="H120" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L120" s="39"/>
-      <c r="M120" s="38"/>
-    </row>
-    <row r="121" spans="1:13">
-      <c r="A121" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B121" s="26" t="s">
+      <c r="L120" s="11"/>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" s="5" t="s">
         <v>247</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="C121" s="9">
         <v>50</v>
       </c>
-      <c r="D121" s="8">
+      <c r="D121" s="7">
         <v>76</v>
       </c>
-      <c r="E121" s="5">
+      <c r="E121" s="8">
         <v>66</v>
       </c>
-      <c r="F121" s="5"/>
+      <c r="F121" s="8">
+        <v>78</v>
+      </c>
       <c r="G121" s="9">
         <v>43</v>
       </c>
-      <c r="H121" s="7">
+      <c r="H121" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L121" s="39"/>
-      <c r="M121" s="38"/>
-    </row>
-    <row r="122" spans="1:13">
-      <c r="A122" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B122" s="26" t="s">
+      <c r="L121" s="11"/>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122" s="5" t="s">
         <v>249</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="C122" s="9">
         <v>58</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D122" s="7">
         <v>80.5</v>
       </c>
-      <c r="E122" s="5">
+      <c r="E122" s="8">
         <v>54</v>
       </c>
-      <c r="F122" s="5"/>
+      <c r="F122" s="8">
+        <v>81</v>
+      </c>
       <c r="G122" s="9">
         <v>44</v>
       </c>
-      <c r="H122" s="7">
+      <c r="H122" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L122" s="39"/>
-      <c r="M122" s="38"/>
-    </row>
-    <row r="123" spans="1:13">
-      <c r="A123" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="B123" s="26" t="s">
+      <c r="L122" s="11"/>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123" s="5" t="s">
         <v>251</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="C123" s="9">
         <v>40</v>
       </c>
-      <c r="D123" s="8">
+      <c r="D123" s="7">
         <v>86.5</v>
       </c>
-      <c r="E123" s="5">
+      <c r="E123" s="8">
         <v>65</v>
       </c>
-      <c r="F123" s="5"/>
+      <c r="F123" s="8">
+        <v>66</v>
+      </c>
       <c r="G123" s="9">
         <v>61</v>
       </c>
-      <c r="H123" s="7">
+      <c r="H123" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L123" s="39"/>
-      <c r="M123" s="38"/>
-    </row>
-    <row r="124" spans="1:13">
-      <c r="A124" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="B124" s="26" t="s">
+      <c r="L123" s="11"/>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" s="5" t="s">
         <v>253</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C124" s="9">
         <v>40</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D124" s="7">
         <v>89</v>
       </c>
-      <c r="E124" s="5">
+      <c r="E124" s="8">
         <v>60</v>
       </c>
-      <c r="F124" s="5"/>
+      <c r="F124" s="8">
+        <v>69</v>
+      </c>
       <c r="G124" s="9">
         <v>43</v>
       </c>
-      <c r="H124" s="7">
+      <c r="H124" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L124" s="39"/>
-      <c r="M124" s="38"/>
-    </row>
-    <row r="125" spans="1:13">
-      <c r="A125" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B125" s="26" t="s">
+      <c r="L124" s="11"/>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" s="5" t="s">
         <v>255</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="C125" s="9">
         <v>46</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="7">
         <v>86</v>
       </c>
-      <c r="E125" s="5">
+      <c r="E125" s="8">
         <v>88</v>
       </c>
-      <c r="F125" s="5"/>
+      <c r="F125" s="8">
+        <v>81</v>
+      </c>
       <c r="G125" s="9">
         <v>42</v>
       </c>
-      <c r="H125" s="7">
+      <c r="H125" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L125" s="39"/>
-      <c r="M125" s="38"/>
-    </row>
-    <row r="126" spans="1:13">
-      <c r="A126" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="B126" s="26" t="s">
+      <c r="L125" s="11"/>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" s="5" t="s">
         <v>257</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>258</v>
       </c>
       <c r="C126" s="9">
         <v>54</v>
       </c>
-      <c r="D126" s="8">
+      <c r="D126" s="7">
         <v>91</v>
       </c>
-      <c r="E126" s="5">
+      <c r="E126" s="8">
         <v>67</v>
       </c>
-      <c r="F126" s="5"/>
+      <c r="F126" s="8">
+        <v>87</v>
+      </c>
       <c r="G126" s="9">
         <v>47</v>
       </c>
-      <c r="H126" s="7">
+      <c r="H126" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L126" s="39"/>
-      <c r="M126" s="38"/>
-    </row>
-    <row r="127" spans="1:13">
-      <c r="A127" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="B127" s="26" t="s">
+      <c r="L126" s="11"/>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" s="5" t="s">
         <v>259</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="C127" s="9">
         <v>38</v>
       </c>
-      <c r="D127" s="8">
+      <c r="D127" s="7">
         <v>90</v>
       </c>
-      <c r="E127" s="5">
+      <c r="E127" s="8">
         <v>90</v>
       </c>
-      <c r="F127" s="5"/>
+      <c r="F127" s="40">
+        <v>71</v>
+      </c>
       <c r="G127" s="9">
         <v>57</v>
       </c>
-      <c r="H127" s="7">
+      <c r="H127" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L127" s="39"/>
-      <c r="M127" s="38"/>
-    </row>
-    <row r="128" spans="1:13">
-      <c r="A128" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="B128" s="26" t="s">
+      <c r="L127" s="11"/>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" s="5" t="s">
         <v>261</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>262</v>
       </c>
       <c r="C128" s="9">
         <v>70</v>
       </c>
-      <c r="D128" s="8">
+      <c r="D128" s="7">
         <v>86</v>
       </c>
-      <c r="E128" s="5">
+      <c r="E128" s="8">
         <v>69</v>
       </c>
-      <c r="F128" s="5"/>
+      <c r="F128" s="8">
+        <v>69</v>
+      </c>
       <c r="G128" s="9">
         <v>63</v>
       </c>
-      <c r="H128" s="7">
+      <c r="H128" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L128" s="39"/>
-      <c r="M128" s="38"/>
-    </row>
-    <row r="129" spans="1:13">
-      <c r="A129" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="B129" s="26" t="s">
+      <c r="L128" s="11"/>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" s="5" t="s">
         <v>263</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>264</v>
       </c>
       <c r="C129" s="9">
         <v>30</v>
       </c>
-      <c r="D129" s="8">
+      <c r="D129" s="7">
         <v>94</v>
       </c>
-      <c r="E129" s="5">
+      <c r="E129" s="8">
         <v>78</v>
       </c>
-      <c r="F129" s="5"/>
+      <c r="F129" s="8">
+        <v>66</v>
+      </c>
       <c r="G129" s="9">
         <v>35</v>
       </c>
-      <c r="H129" s="7">
+      <c r="H129" s="10">
         <v>100</v>
       </c>
-      <c r="L129" s="39"/>
-      <c r="M129" s="38"/>
-    </row>
-    <row r="130" spans="1:13">
-      <c r="A130" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B130" s="26" t="s">
+      <c r="L129" s="11"/>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" s="5" t="s">
         <v>265</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>266</v>
       </c>
       <c r="C130" s="9">
         <v>50</v>
       </c>
-      <c r="D130" s="8">
+      <c r="D130" s="7">
         <v>94</v>
       </c>
-      <c r="E130" s="5">
+      <c r="E130" s="8">
         <v>67</v>
       </c>
-      <c r="F130" s="5"/>
+      <c r="F130" s="8">
+        <v>74</v>
+      </c>
       <c r="G130" s="9">
         <v>38</v>
       </c>
-      <c r="H130" s="7">
+      <c r="H130" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L130" s="39"/>
-      <c r="M130" s="38"/>
-    </row>
-    <row r="131" spans="1:13">
-      <c r="A131" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B131" s="26" t="s">
+      <c r="L130" s="11"/>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" s="5" t="s">
         <v>267</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="C131" s="9">
         <v>42</v>
       </c>
-      <c r="D131" s="8">
+      <c r="D131" s="7">
         <v>86</v>
       </c>
-      <c r="E131" s="5">
+      <c r="E131" s="8">
         <v>58</v>
       </c>
-      <c r="F131" s="5"/>
+      <c r="F131" s="8">
+        <v>77</v>
+      </c>
       <c r="G131" s="9">
         <v>58</v>
       </c>
-      <c r="H131" s="7">
+      <c r="H131" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L131" s="39"/>
-      <c r="M131" s="38"/>
-    </row>
-    <row r="132" spans="1:13">
-      <c r="A132" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="B132" s="26" t="s">
+      <c r="L131" s="11"/>
+    </row>
+    <row r="132" spans="1:12">
+      <c r="A132" s="5" t="s">
         <v>269</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="C132" s="9">
         <v>70</v>
       </c>
-      <c r="D132" s="8">
+      <c r="D132" s="7">
         <v>86</v>
       </c>
-      <c r="E132" s="5">
+      <c r="E132" s="8">
         <v>71</v>
       </c>
-      <c r="F132" s="5"/>
+      <c r="F132" s="8">
+        <v>69</v>
+      </c>
       <c r="G132" s="9">
         <v>60</v>
       </c>
-      <c r="H132" s="7">
+      <c r="H132" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L132" s="39"/>
-      <c r="M132" s="38"/>
-    </row>
-    <row r="133" spans="1:13">
-      <c r="A133" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="B133" s="26" t="s">
+      <c r="L132" s="11"/>
+    </row>
+    <row r="133" spans="1:12">
+      <c r="A133" s="5" t="s">
         <v>271</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="C133" s="9">
         <v>48</v>
       </c>
-      <c r="D133" s="8">
+      <c r="D133" s="7">
         <v>57</v>
       </c>
-      <c r="E133" s="5">
+      <c r="E133" s="8">
         <v>80</v>
       </c>
-      <c r="F133" s="5"/>
+      <c r="F133" s="8">
+        <v>84</v>
+      </c>
       <c r="G133" s="9">
         <v>61</v>
       </c>
-      <c r="H133" s="7">
+      <c r="H133" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L133" s="39"/>
-      <c r="M133" s="38"/>
-    </row>
-    <row r="134" spans="1:13">
-      <c r="A134" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="B134" s="26" t="s">
+      <c r="L133" s="11"/>
+    </row>
+    <row r="134" spans="1:12">
+      <c r="A134" s="5" t="s">
         <v>273</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="C134" s="9">
         <v>44</v>
       </c>
-      <c r="D134" s="8">
+      <c r="D134" s="7">
         <v>85</v>
       </c>
-      <c r="E134" s="5">
+      <c r="E134" s="8">
         <v>54</v>
       </c>
-      <c r="F134" s="5"/>
+      <c r="F134" s="8">
+        <v>69</v>
+      </c>
       <c r="G134" s="9">
         <v>58</v>
       </c>
-      <c r="H134" s="7">
+      <c r="H134" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L134" s="39"/>
-      <c r="M134" s="38"/>
-    </row>
-    <row r="135" spans="1:13">
-      <c r="A135" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="B135" s="26" t="s">
+      <c r="L134" s="11"/>
+    </row>
+    <row r="135" spans="1:12">
+      <c r="A135" s="5" t="s">
         <v>275</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>276</v>
       </c>
       <c r="C135" s="9">
         <v>48</v>
       </c>
-      <c r="D135" s="8">
+      <c r="D135" s="7">
         <v>84.5</v>
       </c>
-      <c r="E135" s="5">
+      <c r="E135" s="8">
         <v>86</v>
       </c>
-      <c r="F135" s="5"/>
+      <c r="F135" s="8">
+        <v>87</v>
+      </c>
       <c r="G135" s="9">
         <v>62</v>
       </c>
-      <c r="H135" s="7">
+      <c r="H135" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L135" s="39"/>
-      <c r="M135" s="38"/>
-    </row>
-    <row r="136" spans="1:13">
-      <c r="A136" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="B136" s="26" t="s">
+      <c r="L135" s="11"/>
+    </row>
+    <row r="136" spans="1:12">
+      <c r="A136" s="5" t="s">
         <v>277</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="C136" s="9">
         <v>40</v>
       </c>
-      <c r="D136" s="8">
+      <c r="D136" s="7">
         <v>66.5</v>
       </c>
-      <c r="E136" s="5">
+      <c r="E136" s="8">
         <v>78</v>
       </c>
-      <c r="F136" s="5"/>
+      <c r="F136" s="8">
+        <v>69</v>
+      </c>
       <c r="G136" s="9">
         <v>53</v>
       </c>
-      <c r="H136" s="7">
+      <c r="H136" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L136" s="39"/>
-      <c r="M136" s="38"/>
-    </row>
-    <row r="137" spans="1:13">
-      <c r="A137" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="B137" s="26" t="s">
+      <c r="L136" s="11"/>
+    </row>
+    <row r="137" spans="1:12">
+      <c r="A137" s="5" t="s">
         <v>279</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>280</v>
       </c>
       <c r="C137" s="9">
         <v>66</v>
       </c>
-      <c r="D137" s="8">
+      <c r="D137" s="7">
         <v>91</v>
       </c>
-      <c r="E137" s="5">
+      <c r="E137" s="8">
         <v>89</v>
       </c>
-      <c r="F137" s="5"/>
+      <c r="F137" s="8">
+        <v>49</v>
+      </c>
       <c r="G137" s="9">
         <v>30</v>
       </c>
-      <c r="H137" s="7">
+      <c r="H137" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L137" s="39"/>
-      <c r="M137" s="38"/>
-    </row>
-    <row r="138" spans="1:13">
-      <c r="A138" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="B138" s="26" t="s">
+      <c r="L137" s="11"/>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" s="5" t="s">
         <v>281</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>282</v>
       </c>
       <c r="C138" s="9">
         <v>44</v>
       </c>
-      <c r="D138" s="8">
+      <c r="D138" s="7">
         <v>92</v>
       </c>
-      <c r="E138" s="5">
+      <c r="E138" s="8">
         <v>87</v>
       </c>
-      <c r="F138" s="5"/>
+      <c r="F138" s="8">
+        <v>95</v>
+      </c>
       <c r="G138" s="9">
         <v>59</v>
       </c>
-      <c r="H138" s="7">
+      <c r="H138" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L138" s="39"/>
-      <c r="M138" s="38"/>
-    </row>
-    <row r="139" spans="1:13">
-      <c r="A139" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="B139" s="26" t="s">
+      <c r="L138" s="11"/>
+    </row>
+    <row r="139" spans="1:12">
+      <c r="A139" s="5" t="s">
         <v>283</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>284</v>
       </c>
       <c r="C139" s="9">
         <v>40</v>
       </c>
-      <c r="D139" s="8">
+      <c r="D139" s="7">
         <v>66.5</v>
       </c>
-      <c r="E139" s="5">
+      <c r="E139" s="8">
         <v>76</v>
       </c>
-      <c r="F139" s="5"/>
+      <c r="F139" s="8">
+        <v>69</v>
+      </c>
       <c r="G139" s="9">
         <v>51</v>
       </c>
-      <c r="H139" s="7">
+      <c r="H139" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L139" s="39"/>
-      <c r="M139" s="38"/>
-    </row>
-    <row r="140" spans="1:13">
-      <c r="A140" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="B140" s="26" t="s">
+      <c r="L139" s="11"/>
+    </row>
+    <row r="140" spans="1:12">
+      <c r="A140" s="5" t="s">
         <v>285</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>286</v>
       </c>
       <c r="C140" s="9">
         <v>18</v>
       </c>
-      <c r="D140" s="8">
+      <c r="D140" s="7">
         <v>98</v>
       </c>
-      <c r="E140" s="5">
+      <c r="E140" s="8">
         <v>89</v>
       </c>
-      <c r="F140" s="5"/>
+      <c r="F140" s="8">
+        <v>81</v>
+      </c>
       <c r="G140" s="9">
         <v>61</v>
       </c>
-      <c r="H140" s="7">
+      <c r="H140" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L140" s="39"/>
-      <c r="M140" s="38"/>
-    </row>
-    <row r="141" spans="1:13">
-      <c r="A141" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="B141" s="26" t="s">
+      <c r="L140" s="11"/>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141" s="5" t="s">
         <v>287</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="C141" s="9">
         <v>46</v>
       </c>
-      <c r="D141" s="8">
+      <c r="D141" s="7">
         <v>86</v>
       </c>
-      <c r="E141" s="5">
+      <c r="E141" s="8">
         <v>66</v>
       </c>
-      <c r="F141" s="5"/>
+      <c r="F141" s="8">
+        <v>81</v>
+      </c>
       <c r="G141" s="9">
         <v>54</v>
       </c>
-      <c r="H141" s="7">
+      <c r="H141" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L141" s="39"/>
-      <c r="M141" s="38"/>
-    </row>
-    <row r="142" spans="1:13">
-      <c r="A142" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="B142" s="26" t="s">
+      <c r="L141" s="11"/>
+    </row>
+    <row r="142" spans="1:12">
+      <c r="A142" s="5" t="s">
         <v>289</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>290</v>
       </c>
       <c r="C142" s="9">
         <v>46</v>
       </c>
-      <c r="D142" s="8">
+      <c r="D142" s="7">
         <v>86</v>
       </c>
-      <c r="E142" s="5">
+      <c r="E142" s="8">
         <v>62</v>
       </c>
-      <c r="F142" s="5"/>
+      <c r="F142" s="8">
+        <v>81</v>
+      </c>
       <c r="G142" s="9">
         <v>45</v>
       </c>
-      <c r="H142" s="7">
+      <c r="H142" s="10">
         <v>100</v>
       </c>
-      <c r="L142" s="39"/>
-      <c r="M142" s="38"/>
-    </row>
-    <row r="143" spans="1:13">
-      <c r="A143" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="B143" s="26" t="s">
+      <c r="L142" s="11"/>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="A143" s="5" t="s">
         <v>291</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="C143" s="9">
         <v>44</v>
       </c>
-      <c r="D143" s="8">
+      <c r="D143" s="7">
         <v>91</v>
       </c>
-      <c r="E143" s="5">
+      <c r="E143" s="8">
         <v>85</v>
       </c>
-      <c r="F143" s="5"/>
+      <c r="F143" s="8">
+        <v>66</v>
+      </c>
       <c r="G143" s="9">
         <v>47</v>
       </c>
-      <c r="H143" s="7">
+      <c r="H143" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L143" s="39"/>
-      <c r="M143" s="38"/>
-    </row>
-    <row r="144" spans="1:13">
-      <c r="A144" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="B144" s="26" t="s">
+      <c r="L143" s="11"/>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="A144" s="5" t="s">
         <v>293</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>294</v>
       </c>
       <c r="C144" s="9">
         <v>44</v>
       </c>
-      <c r="D144" s="8">
+      <c r="D144" s="7">
         <v>91</v>
       </c>
-      <c r="E144" s="5">
+      <c r="E144" s="8">
         <v>72</v>
       </c>
-      <c r="F144" s="5"/>
+      <c r="F144" s="8">
+        <v>66</v>
+      </c>
       <c r="G144" s="9">
         <v>61</v>
       </c>
-      <c r="H144" s="7">
+      <c r="H144" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L144" s="39"/>
-      <c r="M144" s="38"/>
-    </row>
-    <row r="145" spans="1:13">
-      <c r="A145" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="B145" s="26" t="s">
+      <c r="L144" s="11"/>
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145" s="5" t="s">
         <v>295</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="C145" s="9">
         <v>34</v>
       </c>
-      <c r="D145" s="8">
+      <c r="D145" s="7">
         <v>68</v>
       </c>
-      <c r="E145" s="5">
+      <c r="E145" s="8">
         <v>69</v>
       </c>
-      <c r="F145" s="5"/>
+      <c r="F145" s="8">
+        <v>55</v>
+      </c>
       <c r="G145" s="9">
         <v>73</v>
       </c>
-      <c r="H145" s="7">
+      <c r="H145" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L145" s="39"/>
-      <c r="M145" s="38"/>
-    </row>
-    <row r="146" spans="1:13">
-      <c r="A146" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="B146" s="26" t="s">
+      <c r="L145" s="11"/>
+    </row>
+    <row r="146" spans="1:12">
+      <c r="A146" s="5" t="s">
         <v>297</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="C146" s="9">
         <v>72</v>
       </c>
-      <c r="D146" s="8">
+      <c r="D146" s="7">
         <v>82</v>
       </c>
-      <c r="E146" s="5">
+      <c r="E146" s="8">
         <v>73</v>
       </c>
-      <c r="F146" s="5"/>
+      <c r="F146" s="8">
+        <v>77</v>
+      </c>
       <c r="G146" s="9">
         <v>53</v>
       </c>
-      <c r="H146" s="7">
+      <c r="H146" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L146" s="39"/>
-      <c r="M146" s="38"/>
-    </row>
-    <row r="147" spans="1:13">
-      <c r="A147" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="B147" s="26" t="s">
+      <c r="L146" s="11"/>
+    </row>
+    <row r="147" spans="1:12">
+      <c r="A147" s="5" t="s">
         <v>299</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>300</v>
       </c>
       <c r="C147" s="9">
         <v>48</v>
       </c>
-      <c r="D147" s="8">
+      <c r="D147" s="7">
         <v>99</v>
       </c>
-      <c r="E147" s="5">
+      <c r="E147" s="8">
         <v>81</v>
       </c>
-      <c r="F147" s="5"/>
+      <c r="F147" s="8">
+        <v>81</v>
+      </c>
       <c r="G147" s="9">
         <v>54</v>
       </c>
-      <c r="H147" s="7">
+      <c r="H147" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L147" s="39"/>
-      <c r="M147" s="38"/>
-    </row>
-    <row r="148" spans="1:13">
-      <c r="A148" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="B148" s="26" t="s">
+      <c r="L147" s="11"/>
+    </row>
+    <row r="148" spans="1:12">
+      <c r="A148" s="5" t="s">
         <v>301</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>302</v>
       </c>
       <c r="C148" s="9">
         <v>48</v>
       </c>
-      <c r="D148" s="8">
+      <c r="D148" s="7">
         <v>96</v>
       </c>
-      <c r="E148" s="5">
+      <c r="E148" s="8">
         <v>74</v>
       </c>
-      <c r="F148" s="5"/>
+      <c r="F148" s="8">
+        <v>87</v>
+      </c>
       <c r="G148" s="9">
         <v>51</v>
       </c>
-      <c r="H148" s="7">
+      <c r="H148" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L148" s="39"/>
-      <c r="M148" s="38"/>
-    </row>
-    <row r="149" spans="1:13">
-      <c r="A149" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="B149" s="26" t="s">
+      <c r="L148" s="11"/>
+    </row>
+    <row r="149" spans="1:12">
+      <c r="A149" s="5" t="s">
         <v>303</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>304</v>
       </c>
       <c r="C149" s="9">
         <v>28</v>
       </c>
-      <c r="D149" s="8">
+      <c r="D149" s="7">
         <v>88</v>
       </c>
-      <c r="E149" s="5">
+      <c r="E149" s="8">
         <v>76</v>
       </c>
-      <c r="F149" s="5"/>
+      <c r="F149" s="8">
+        <v>100</v>
+      </c>
       <c r="G149" s="9">
         <v>56</v>
       </c>
-      <c r="H149" s="7">
+      <c r="H149" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L149" s="39"/>
-      <c r="M149" s="38"/>
-    </row>
-    <row r="150" spans="1:13">
-      <c r="A150" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="B150" s="26" t="s">
+      <c r="L149" s="11"/>
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150" s="5" t="s">
         <v>305</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>306</v>
       </c>
       <c r="C150" s="9">
         <v>52</v>
       </c>
-      <c r="D150" s="8">
+      <c r="D150" s="7">
         <v>80</v>
       </c>
-      <c r="E150" s="5">
+      <c r="E150" s="8">
         <v>56</v>
       </c>
-      <c r="F150" s="5"/>
+      <c r="F150" s="8">
+        <v>70</v>
+      </c>
       <c r="G150" s="9">
         <v>51</v>
       </c>
-      <c r="H150" s="7">
+      <c r="H150" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L150" s="39"/>
-      <c r="M150" s="38"/>
-    </row>
-    <row r="151" spans="1:13">
-      <c r="A151" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="B151" s="26" t="s">
+      <c r="L150" s="11"/>
+    </row>
+    <row r="151" spans="1:12">
+      <c r="A151" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C151" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D151" s="8">
+      <c r="B151" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C151" s="42">
+        <v>48</v>
+      </c>
+      <c r="D151" s="7">
         <v>68.5</v>
       </c>
-      <c r="E151" s="5">
+      <c r="E151" s="8">
         <v>82</v>
       </c>
-      <c r="F151" s="5"/>
+      <c r="F151" s="8">
+        <v>70</v>
+      </c>
       <c r="G151" s="9">
         <v>67</v>
       </c>
-      <c r="H151" s="7">
+      <c r="H151" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L151" s="39"/>
-      <c r="M151" s="38"/>
-    </row>
-    <row r="152" spans="1:13">
-      <c r="A152" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B152" s="26" t="s">
+      <c r="L151" s="11"/>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152" s="5" t="s">
         <v>309</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>310</v>
       </c>
       <c r="C152" s="9">
         <v>40</v>
       </c>
-      <c r="D152" s="8">
+      <c r="D152" s="7">
         <v>66.5</v>
       </c>
-      <c r="E152" s="5">
+      <c r="E152" s="8">
         <v>59</v>
       </c>
-      <c r="F152" s="5"/>
+      <c r="F152" s="8">
+        <v>70</v>
+      </c>
       <c r="G152" s="9">
         <v>45</v>
       </c>
-      <c r="H152" s="7">
+      <c r="H152" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L152" s="39"/>
-      <c r="M152" s="38"/>
-    </row>
-    <row r="153" spans="1:13">
-      <c r="A153" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="B153" s="26" t="s">
+      <c r="L152" s="11"/>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153" s="5" t="s">
         <v>311</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>312</v>
       </c>
       <c r="C153" s="9">
         <v>46</v>
       </c>
-      <c r="D153" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F153" s="5"/>
+      <c r="D153" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G153" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H153" s="7">
+        <v>122</v>
+      </c>
+      <c r="H153" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L153" s="39"/>
-      <c r="M153" s="38"/>
-    </row>
-    <row r="154" spans="1:13">
-      <c r="A154" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="B154" s="26" t="s">
+      <c r="L153" s="11"/>
+    </row>
+    <row r="154" spans="1:12">
+      <c r="A154" s="5" t="s">
         <v>313</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>314</v>
       </c>
       <c r="C154" s="9">
         <v>28</v>
       </c>
-      <c r="D154" s="8">
+      <c r="D154" s="7">
         <v>88</v>
       </c>
-      <c r="E154" s="5">
+      <c r="E154" s="8">
         <v>73</v>
       </c>
-      <c r="F154" s="5"/>
+      <c r="F154" s="8">
+        <v>100</v>
+      </c>
       <c r="G154" s="9">
         <v>73</v>
       </c>
-      <c r="H154" s="7">
+      <c r="H154" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L154" s="39"/>
-      <c r="M154" s="38"/>
-    </row>
-    <row r="155" spans="1:13">
-      <c r="A155" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="B155" s="26" t="s">
+      <c r="L154" s="11"/>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155" s="5" t="s">
         <v>315</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="C155" s="9">
         <v>44</v>
       </c>
-      <c r="D155" s="8">
+      <c r="D155" s="7">
         <v>85</v>
       </c>
-      <c r="E155" s="5">
+      <c r="E155" s="8">
         <v>41</v>
       </c>
-      <c r="F155" s="5"/>
+      <c r="F155" s="8">
+        <v>69</v>
+      </c>
       <c r="G155" s="9">
         <v>62</v>
       </c>
-      <c r="H155" s="7">
+      <c r="H155" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L155" s="39"/>
-      <c r="M155" s="38"/>
-    </row>
-    <row r="156" spans="1:13">
-      <c r="A156" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B156" s="26" t="s">
+      <c r="L155" s="11"/>
+    </row>
+    <row r="156" spans="1:12">
+      <c r="A156" s="5" t="s">
         <v>317</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>318</v>
       </c>
       <c r="C156" s="9">
         <v>44</v>
       </c>
-      <c r="D156" s="8">
+      <c r="D156" s="7">
         <v>85</v>
       </c>
-      <c r="E156" s="5">
+      <c r="E156" s="8">
         <v>69</v>
       </c>
-      <c r="F156" s="5"/>
+      <c r="F156" s="8">
+        <v>69</v>
+      </c>
       <c r="G156" s="9">
         <v>49</v>
       </c>
-      <c r="H156" s="7">
+      <c r="H156" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L156" s="39"/>
-      <c r="M156" s="38"/>
-    </row>
-    <row r="157" spans="1:13">
-      <c r="A157" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="B157" s="26" t="s">
+      <c r="L156" s="11"/>
+    </row>
+    <row r="157" spans="1:12">
+      <c r="A157" s="5" t="s">
         <v>319</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="C157" s="9">
         <v>26</v>
       </c>
-      <c r="D157" s="8">
+      <c r="D157" s="7">
         <v>84</v>
       </c>
-      <c r="E157" s="5">
+      <c r="E157" s="8">
         <v>59</v>
       </c>
-      <c r="F157" s="5"/>
-      <c r="G157" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H157" s="7">
+      <c r="F157" s="8">
+        <v>69</v>
+      </c>
+      <c r="G157" s="42">
+        <v>50</v>
+      </c>
+      <c r="H157" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L157" s="39"/>
-      <c r="M157" s="38"/>
-    </row>
-    <row r="158" spans="1:13">
-      <c r="A158" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B158" s="26" t="s">
+      <c r="L157" s="11"/>
+    </row>
+    <row r="158" spans="1:12">
+      <c r="A158" s="5" t="s">
         <v>321</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>322</v>
       </c>
       <c r="C158" s="9">
         <v>48</v>
       </c>
-      <c r="D158" s="8">
+      <c r="D158" s="7">
         <v>89.5</v>
       </c>
-      <c r="E158" s="5">
+      <c r="E158" s="8">
         <v>77</v>
       </c>
-      <c r="F158" s="5"/>
+      <c r="F158" s="8">
+        <v>99</v>
+      </c>
       <c r="G158" s="9">
         <v>50</v>
       </c>
-      <c r="H158" s="7">
+      <c r="H158" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L158" s="39"/>
-      <c r="M158" s="38"/>
-    </row>
-    <row r="159" spans="1:13">
-      <c r="A159" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="B159" s="26" t="s">
+      <c r="L158" s="11"/>
+    </row>
+    <row r="159" spans="1:12">
+      <c r="A159" s="5" t="s">
         <v>323</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>324</v>
       </c>
       <c r="C159" s="9">
         <v>64</v>
       </c>
-      <c r="D159" s="8">
+      <c r="D159" s="7">
         <v>92.5</v>
       </c>
-      <c r="E159" s="5">
+      <c r="E159" s="8">
         <v>80</v>
       </c>
-      <c r="F159" s="5"/>
+      <c r="F159" s="8">
+        <v>88</v>
+      </c>
       <c r="G159" s="9">
         <v>62</v>
       </c>
-      <c r="H159" s="7">
+      <c r="H159" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L159" s="39"/>
-      <c r="M159" s="38"/>
-    </row>
-    <row r="160" spans="1:13">
-      <c r="A160" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="B160" s="26" t="s">
+      <c r="L159" s="11"/>
+    </row>
+    <row r="160" spans="1:12">
+      <c r="A160" s="5" t="s">
         <v>325</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>326</v>
       </c>
       <c r="C160" s="9">
         <v>52</v>
       </c>
-      <c r="D160" s="8">
+      <c r="D160" s="7">
         <v>89</v>
       </c>
-      <c r="E160" s="5">
+      <c r="E160" s="8">
         <v>69</v>
       </c>
-      <c r="F160" s="5"/>
+      <c r="F160" s="8">
+        <v>69</v>
+      </c>
       <c r="G160" s="9">
         <v>51</v>
       </c>
-      <c r="H160" s="7">
+      <c r="H160" s="10">
         <v>100</v>
       </c>
-      <c r="L160" s="39"/>
-      <c r="M160" s="38"/>
-    </row>
-    <row r="161" spans="1:13">
-      <c r="A161" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="B161" s="26" t="s">
+      <c r="L160" s="11"/>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="A161" s="5" t="s">
         <v>327</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>328</v>
       </c>
       <c r="C161" s="9">
         <v>54</v>
       </c>
-      <c r="D161" s="8">
+      <c r="D161" s="7">
         <v>91</v>
       </c>
-      <c r="E161" s="5">
+      <c r="E161" s="8">
         <v>69</v>
       </c>
-      <c r="F161" s="5"/>
+      <c r="F161" s="8">
+        <v>42</v>
+      </c>
       <c r="G161" s="9">
         <v>47</v>
       </c>
-      <c r="H161" s="7">
+      <c r="H161" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L161" s="39"/>
-      <c r="M161" s="38"/>
-    </row>
-    <row r="162" spans="1:13">
-      <c r="A162" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="B162" s="26" t="s">
+      <c r="L161" s="11"/>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" s="5" t="s">
         <v>329</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>330</v>
       </c>
       <c r="C162" s="9">
         <v>52</v>
       </c>
-      <c r="D162" s="8">
+      <c r="D162" s="7">
         <v>99</v>
       </c>
-      <c r="E162" s="5">
+      <c r="E162" s="8">
         <v>68</v>
       </c>
-      <c r="F162" s="5"/>
+      <c r="F162" s="8">
+        <v>90</v>
+      </c>
       <c r="G162" s="9">
         <v>50</v>
       </c>
-      <c r="H162" s="7">
+      <c r="H162" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L162" s="39"/>
-      <c r="M162" s="38"/>
-    </row>
-    <row r="163" spans="1:13">
-      <c r="A163" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="B163" s="26" t="s">
+      <c r="L162" s="11"/>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163" s="5" t="s">
         <v>331</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>332</v>
       </c>
       <c r="C163" s="9">
         <v>12</v>
       </c>
-      <c r="D163" s="8">
+      <c r="D163" s="7">
         <v>71</v>
       </c>
-      <c r="E163" s="5">
+      <c r="E163" s="8">
         <v>64</v>
       </c>
-      <c r="F163" s="5"/>
+      <c r="F163" s="8">
+        <v>94</v>
+      </c>
       <c r="G163" s="9">
         <v>45</v>
       </c>
-      <c r="H163" s="7">
+      <c r="H163" s="10">
         <v>100</v>
       </c>
-      <c r="L163" s="39"/>
-      <c r="M163" s="38"/>
-    </row>
-    <row r="164" spans="1:13">
-      <c r="A164" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="B164" s="26" t="s">
+      <c r="L163" s="11"/>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="A164" s="5" t="s">
         <v>333</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="C164" s="9">
         <v>26</v>
       </c>
-      <c r="D164" s="8">
+      <c r="D164" s="7">
         <v>91</v>
       </c>
-      <c r="E164" s="5">
+      <c r="E164" s="8">
         <v>62</v>
       </c>
-      <c r="F164" s="5"/>
+      <c r="F164" s="8">
+        <v>72</v>
+      </c>
       <c r="G164" s="9">
         <v>49</v>
       </c>
-      <c r="H164" s="7">
+      <c r="H164" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L164" s="39"/>
-      <c r="M164" s="38"/>
-    </row>
-    <row r="165" spans="1:13">
-      <c r="A165" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="B165" s="26" t="s">
+      <c r="L164" s="11"/>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165" s="5" t="s">
         <v>335</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>336</v>
       </c>
       <c r="C165" s="9">
         <v>70</v>
       </c>
-      <c r="D165" s="8">
+      <c r="D165" s="7">
         <v>86</v>
       </c>
-      <c r="E165" s="5">
+      <c r="E165" s="8">
         <v>58</v>
       </c>
-      <c r="F165" s="5"/>
+      <c r="F165" s="8">
+        <v>69</v>
+      </c>
       <c r="G165" s="9">
         <v>51</v>
       </c>
-      <c r="H165" s="7">
+      <c r="H165" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L165" s="39"/>
-      <c r="M165" s="38"/>
-    </row>
-    <row r="166" spans="1:13">
-      <c r="A166" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="B166" s="26" t="s">
+      <c r="L165" s="11"/>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166" s="5" t="s">
         <v>337</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="C166" s="9">
         <v>67</v>
       </c>
-      <c r="D166" s="8">
+      <c r="D166" s="7">
         <v>76</v>
       </c>
-      <c r="E166" s="5">
+      <c r="E166" s="8">
         <v>69</v>
       </c>
-      <c r="F166" s="5"/>
+      <c r="F166" s="8">
+        <v>78</v>
+      </c>
       <c r="G166" s="9">
         <v>56</v>
       </c>
-      <c r="H166" s="7">
+      <c r="H166" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L166" s="39"/>
-      <c r="M166" s="38"/>
-    </row>
-    <row r="167" spans="1:13">
-      <c r="A167" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="B167" s="26" t="s">
+      <c r="L166" s="11"/>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167" s="5" t="s">
         <v>339</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>340</v>
       </c>
       <c r="C167" s="9">
         <v>48</v>
       </c>
-      <c r="D167" s="8">
+      <c r="D167" s="7">
         <v>57</v>
       </c>
-      <c r="E167" s="5">
+      <c r="E167" s="8">
         <v>78</v>
       </c>
-      <c r="F167" s="5"/>
+      <c r="F167" s="8">
+        <v>84</v>
+      </c>
       <c r="G167" s="9">
         <v>61</v>
       </c>
-      <c r="H167" s="7">
+      <c r="H167" s="10">
         <v>100</v>
       </c>
-      <c r="L167" s="39"/>
-      <c r="M167" s="38"/>
-    </row>
-    <row r="168" spans="1:13">
-      <c r="A168" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="B168" s="26" t="s">
+      <c r="L167" s="11"/>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="A168" s="5" t="s">
         <v>341</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>342</v>
       </c>
       <c r="C168" s="9">
         <v>40</v>
       </c>
-      <c r="D168" s="8">
+      <c r="D168" s="7">
         <v>86.5</v>
       </c>
-      <c r="E168" s="5">
+      <c r="E168" s="8">
         <v>74</v>
       </c>
-      <c r="F168" s="5"/>
+      <c r="F168" s="8">
+        <v>66</v>
+      </c>
       <c r="G168" s="9">
         <v>58</v>
       </c>
-      <c r="H168" s="7">
+      <c r="H168" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L168" s="39"/>
-      <c r="M168" s="38"/>
-    </row>
-    <row r="169" spans="1:13">
-      <c r="A169" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="B169" s="26" t="s">
+      <c r="L168" s="11"/>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169" s="5" t="s">
         <v>343</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="C169" s="9">
         <v>54</v>
       </c>
-      <c r="D169" s="8">
+      <c r="D169" s="7">
         <v>82.5</v>
       </c>
-      <c r="E169" s="5">
+      <c r="E169" s="8">
         <v>70</v>
       </c>
-      <c r="F169" s="5"/>
+      <c r="F169" s="8">
+        <v>77</v>
+      </c>
       <c r="G169" s="9">
         <v>43</v>
       </c>
-      <c r="H169" s="7">
+      <c r="H169" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L169" s="39"/>
-      <c r="M169" s="38"/>
-    </row>
-    <row r="170" spans="1:13">
-      <c r="A170" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="B170" s="26" t="s">
+      <c r="L169" s="11"/>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170" s="5" t="s">
         <v>345</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>346</v>
       </c>
       <c r="C170" s="9">
         <v>44</v>
       </c>
-      <c r="D170" s="8">
+      <c r="D170" s="7">
         <v>92</v>
       </c>
-      <c r="E170" s="5">
+      <c r="E170" s="8">
         <v>56</v>
       </c>
-      <c r="F170" s="5"/>
+      <c r="F170" s="8">
+        <v>95</v>
+      </c>
       <c r="G170" s="9">
         <v>57</v>
       </c>
-      <c r="H170" s="7">
+      <c r="H170" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L170" s="39"/>
-      <c r="M170" s="38"/>
-    </row>
-    <row r="171" spans="1:13">
-      <c r="A171" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="B171" s="26" t="s">
+      <c r="L170" s="11"/>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="A171" s="5" t="s">
         <v>347</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>348</v>
       </c>
       <c r="C171" s="9">
         <v>54</v>
       </c>
-      <c r="D171" s="8">
+      <c r="D171" s="7">
         <v>79</v>
       </c>
-      <c r="E171" s="5">
+      <c r="E171" s="8">
         <v>70</v>
       </c>
-      <c r="F171" s="5"/>
+      <c r="F171" s="8">
+        <v>72</v>
+      </c>
       <c r="G171" s="9">
         <v>77</v>
       </c>
-      <c r="H171" s="7">
+      <c r="H171" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L171" s="39"/>
-      <c r="M171" s="38"/>
-    </row>
-    <row r="172" spans="1:13">
-      <c r="A172" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="B172" s="26" t="s">
+      <c r="L171" s="11"/>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="A172" s="5" t="s">
         <v>349</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="C172" s="9">
         <v>46</v>
       </c>
-      <c r="D172" s="8">
+      <c r="D172" s="7">
         <v>86</v>
       </c>
-      <c r="E172" s="5">
+      <c r="E172" s="8">
         <v>72</v>
       </c>
-      <c r="F172" s="5"/>
+      <c r="F172" s="8">
+        <v>83</v>
+      </c>
       <c r="G172" s="9">
         <v>45</v>
       </c>
-      <c r="H172" s="7">
+      <c r="H172" s="10">
         <v>100</v>
       </c>
-      <c r="L172" s="39"/>
-      <c r="M172" s="38"/>
-    </row>
-    <row r="173" spans="1:13">
-      <c r="A173" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="B173" s="26" t="s">
+      <c r="L172" s="11"/>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="A173" s="5" t="s">
         <v>351</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>352</v>
       </c>
       <c r="C173" s="9">
         <v>40</v>
       </c>
-      <c r="D173" s="8">
+      <c r="D173" s="7">
         <v>75.5</v>
       </c>
-      <c r="E173" s="5">
+      <c r="E173" s="8">
         <v>80</v>
       </c>
-      <c r="F173" s="5"/>
+      <c r="F173" s="8">
+        <v>84</v>
+      </c>
       <c r="G173" s="9">
         <v>62</v>
       </c>
-      <c r="H173" s="7">
+      <c r="H173" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L173" s="39"/>
-      <c r="M173" s="38"/>
-    </row>
-    <row r="174" spans="1:13">
-      <c r="A174" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="B174" s="26" t="s">
+      <c r="L173" s="11"/>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="A174" s="5" t="s">
         <v>353</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>354</v>
       </c>
       <c r="C174" s="9">
         <v>36</v>
       </c>
-      <c r="D174" s="8">
+      <c r="D174" s="7">
         <v>99</v>
       </c>
-      <c r="E174" s="5">
+      <c r="E174" s="8">
         <v>80</v>
       </c>
-      <c r="F174" s="5"/>
+      <c r="F174" s="8">
+        <v>81</v>
+      </c>
       <c r="G174" s="9">
         <v>53</v>
       </c>
-      <c r="H174" s="7">
+      <c r="H174" s="10">
         <v>76.923076899999998</v>
       </c>
-      <c r="L174" s="39"/>
-      <c r="M174" s="38"/>
-    </row>
-    <row r="175" spans="1:13">
-      <c r="A175" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="B175" s="26" t="s">
+      <c r="L174" s="11"/>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="A175" s="5" t="s">
         <v>355</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="C175" s="9">
         <v>48</v>
       </c>
-      <c r="D175" s="8">
+      <c r="D175" s="7">
         <v>57</v>
       </c>
-      <c r="E175" s="5">
+      <c r="E175" s="8">
         <v>80</v>
       </c>
-      <c r="F175" s="5"/>
+      <c r="F175" s="8">
+        <v>84</v>
+      </c>
       <c r="G175" s="9">
         <v>43</v>
       </c>
-      <c r="H175" s="7">
+      <c r="H175" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L175" s="39"/>
-      <c r="M175" s="38"/>
-    </row>
-    <row r="176" spans="1:13">
-      <c r="A176" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="B176" s="26" t="s">
+      <c r="L175" s="11"/>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="A176" s="5" t="s">
         <v>357</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="C176" s="9">
         <v>70</v>
       </c>
-      <c r="D176" s="8">
+      <c r="D176" s="7">
         <v>86</v>
       </c>
-      <c r="E176" s="5">
+      <c r="E176" s="8">
         <v>53</v>
       </c>
-      <c r="F176" s="5"/>
+      <c r="F176" s="8">
+        <v>69</v>
+      </c>
       <c r="G176" s="9">
         <v>52</v>
       </c>
-      <c r="H176" s="7">
+      <c r="H176" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L176" s="39"/>
-      <c r="M176" s="38"/>
-    </row>
-    <row r="177" spans="1:13">
-      <c r="A177" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B177" s="26" t="s">
+      <c r="L176" s="11"/>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177" s="5" t="s">
         <v>359</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>360</v>
       </c>
       <c r="C177" s="9">
         <v>52</v>
       </c>
-      <c r="D177" s="8">
+      <c r="D177" s="7">
         <v>95</v>
       </c>
-      <c r="E177" s="5">
+      <c r="E177" s="8">
         <v>63</v>
       </c>
-      <c r="F177" s="5"/>
+      <c r="F177" s="8">
+        <v>80</v>
+      </c>
       <c r="G177" s="9">
         <v>50</v>
       </c>
-      <c r="H177" s="7">
+      <c r="H177" s="10">
         <v>71.428571399999996</v>
       </c>
-      <c r="L177" s="39"/>
-      <c r="M177" s="38"/>
-    </row>
-    <row r="178" spans="1:13">
-      <c r="A178" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="B178" s="26" t="s">
+      <c r="L177" s="11"/>
+    </row>
+    <row r="178" spans="1:12">
+      <c r="A178" s="5" t="s">
         <v>361</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>362</v>
       </c>
       <c r="C178" s="9">
         <v>60</v>
       </c>
-      <c r="D178" s="8">
+      <c r="D178" s="7">
         <v>90</v>
       </c>
-      <c r="E178" s="5">
+      <c r="E178" s="8">
         <v>64</v>
       </c>
-      <c r="F178" s="5"/>
+      <c r="F178" s="8">
+        <v>83</v>
+      </c>
       <c r="G178" s="9">
         <v>55</v>
       </c>
-      <c r="H178" s="7">
+      <c r="H178" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L178" s="39"/>
-      <c r="M178" s="38"/>
-    </row>
-    <row r="179" spans="1:13">
-      <c r="A179" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="B179" s="26" t="s">
+      <c r="L178" s="11"/>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179" s="5" t="s">
         <v>363</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>364</v>
       </c>
       <c r="C179" s="9">
         <v>26</v>
       </c>
-      <c r="D179" s="8">
+      <c r="D179" s="7">
         <v>100</v>
       </c>
-      <c r="E179" s="5">
+      <c r="E179" s="8">
         <v>61</v>
       </c>
-      <c r="F179" s="5"/>
+      <c r="F179" s="8">
+        <v>81</v>
+      </c>
       <c r="G179" s="9">
         <v>53</v>
       </c>
-      <c r="H179" s="7">
+      <c r="H179" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L179" s="39"/>
-      <c r="M179" s="38"/>
-    </row>
-    <row r="180" spans="1:13">
-      <c r="A180" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="B180" s="26" t="s">
+      <c r="L179" s="11"/>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180" s="5" t="s">
         <v>365</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="C180" s="9">
         <v>60</v>
       </c>
-      <c r="D180" s="8">
+      <c r="D180" s="7">
         <v>90</v>
       </c>
-      <c r="E180" s="5">
+      <c r="E180" s="8">
         <v>77</v>
       </c>
-      <c r="F180" s="5"/>
+      <c r="F180" s="8">
+        <v>83</v>
+      </c>
       <c r="G180" s="9">
         <v>61</v>
       </c>
-      <c r="H180" s="7">
+      <c r="H180" s="10">
         <v>78.571428600000004</v>
       </c>
-      <c r="L180" s="39"/>
-      <c r="M180" s="38"/>
-    </row>
-    <row r="181" spans="1:13">
-      <c r="A181" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="B181" s="26" t="s">
+      <c r="L180" s="11"/>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181" s="5" t="s">
         <v>367</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>368</v>
       </c>
       <c r="C181" s="9">
         <v>64</v>
       </c>
-      <c r="D181" s="8">
+      <c r="D181" s="7">
         <v>92.5</v>
       </c>
-      <c r="E181" s="5">
+      <c r="E181" s="8">
         <v>68</v>
       </c>
-      <c r="F181" s="5"/>
+      <c r="F181" s="8">
+        <v>88</v>
+      </c>
       <c r="G181" s="9">
         <v>48</v>
       </c>
-      <c r="H181" s="7">
+      <c r="H181" s="10">
         <v>100</v>
       </c>
-      <c r="L181" s="39"/>
-      <c r="M181" s="38"/>
-    </row>
-    <row r="182" spans="1:13">
-      <c r="A182" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="B182" s="28" t="s">
-        <v>384</v>
+      <c r="L181" s="11"/>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="A182" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B182" s="14" t="s">
+        <v>370</v>
       </c>
       <c r="C182" s="9">
         <v>46</v>
       </c>
-      <c r="D182" s="8">
+      <c r="D182" s="7">
         <v>84.5</v>
       </c>
-      <c r="E182" s="5">
+      <c r="E182" s="8">
         <v>50</v>
       </c>
-      <c r="F182" s="5"/>
+      <c r="F182" s="8">
+        <v>100</v>
+      </c>
       <c r="G182" s="9">
         <v>37</v>
       </c>
-      <c r="H182" s="7">
+      <c r="H182" s="10">
         <v>64.285714299999995</v>
       </c>
-      <c r="L182" s="39"/>
-      <c r="M182" s="38"/>
-    </row>
-    <row r="183" spans="1:13">
-      <c r="A183" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="B183" s="28" t="s">
-        <v>370</v>
+      <c r="L182" s="11"/>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="A183" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B183" s="14" t="s">
+        <v>372</v>
       </c>
       <c r="C183" s="9">
         <v>34</v>
       </c>
-      <c r="D183" s="8">
+      <c r="D183" s="7">
         <v>68</v>
       </c>
-      <c r="E183" s="5">
+      <c r="E183" s="8">
         <v>45</v>
       </c>
-      <c r="F183" s="5"/>
+      <c r="F183" s="8">
+        <v>55</v>
+      </c>
       <c r="G183" s="9">
         <v>44</v>
       </c>
-      <c r="H183" s="7">
+      <c r="H183" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L183" s="39"/>
-      <c r="M183" s="38"/>
-    </row>
-    <row r="184" spans="1:13">
-      <c r="A184" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="B184" s="29" t="s">
-        <v>385</v>
+      <c r="L183" s="11"/>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="A184" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B184" s="15" t="s">
+        <v>374</v>
       </c>
       <c r="C184" s="9">
         <v>54</v>
       </c>
-      <c r="D184" s="8">
+      <c r="D184" s="7">
         <v>91</v>
       </c>
-      <c r="E184" s="5">
+      <c r="E184" s="8">
         <v>72</v>
       </c>
-      <c r="F184" s="5"/>
+      <c r="F184" s="8">
+        <v>69</v>
+      </c>
       <c r="G184" s="9">
         <v>53</v>
       </c>
-      <c r="H184" s="7">
+      <c r="H184" s="10">
         <v>100</v>
       </c>
-      <c r="L184" s="39"/>
-      <c r="M184" s="38"/>
-    </row>
-    <row r="185" spans="1:13">
-      <c r="A185" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="B185" s="30" t="s">
-        <v>386</v>
+      <c r="L184" s="11"/>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="A185" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B185" s="16" t="s">
+        <v>376</v>
       </c>
       <c r="C185" s="9">
         <v>64</v>
       </c>
-      <c r="D185" s="8">
+      <c r="D185" s="7">
         <v>88</v>
       </c>
-      <c r="E185" s="5">
+      <c r="E185" s="8">
         <v>90</v>
       </c>
-      <c r="F185" s="5"/>
+      <c r="F185" s="8">
+        <v>93</v>
+      </c>
       <c r="G185" s="9">
         <v>74</v>
       </c>
-      <c r="H185" s="7">
+      <c r="H185" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L185" s="39"/>
-      <c r="M185" s="38"/>
-    </row>
-    <row r="186" spans="1:13">
-      <c r="A186" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="B186" s="28" t="s">
-        <v>387</v>
+      <c r="L185" s="11"/>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="A186" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B186" s="14" t="s">
+        <v>378</v>
       </c>
       <c r="C186" s="9">
         <v>72</v>
       </c>
-      <c r="D186" s="8">
+      <c r="D186" s="7">
         <v>100</v>
       </c>
-      <c r="E186" s="5">
+      <c r="E186" s="8">
         <v>52</v>
       </c>
-      <c r="F186" s="5"/>
+      <c r="F186" s="8">
+        <v>81</v>
+      </c>
       <c r="G186" s="9">
         <v>62</v>
       </c>
-      <c r="H186" s="7">
+      <c r="H186" s="10">
         <v>100</v>
       </c>
-      <c r="L186" s="39"/>
-      <c r="M186" s="38"/>
-    </row>
-    <row r="187" spans="1:13">
-      <c r="A187" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B187" s="28" t="s">
-        <v>388</v>
+      <c r="L186" s="11"/>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="A187" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B187" s="14" t="s">
+        <v>380</v>
       </c>
       <c r="C187" s="9">
         <v>46</v>
       </c>
-      <c r="D187" s="8">
+      <c r="D187" s="7">
         <v>84.5</v>
       </c>
-      <c r="E187" s="5">
+      <c r="E187" s="8">
         <v>69</v>
       </c>
-      <c r="F187" s="5"/>
+      <c r="F187" s="8">
+        <v>87</v>
+      </c>
       <c r="G187" s="9">
         <v>47</v>
       </c>
-      <c r="H187" s="7">
+      <c r="H187" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L187" s="39"/>
-      <c r="M187" s="38"/>
-    </row>
-    <row r="188" spans="1:13">
-      <c r="A188" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="B188" s="28" t="s">
-        <v>389</v>
+      <c r="L187" s="11"/>
+    </row>
+    <row r="188" spans="1:12">
+      <c r="A188" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B188" s="14" t="s">
+        <v>382</v>
       </c>
       <c r="C188" s="9">
         <v>54</v>
       </c>
-      <c r="D188" s="8">
+      <c r="D188" s="7">
         <v>87</v>
       </c>
-      <c r="E188" s="5">
+      <c r="E188" s="8">
         <v>75</v>
       </c>
-      <c r="F188" s="5"/>
+      <c r="F188" s="8">
+        <v>42</v>
+      </c>
       <c r="G188" s="9">
         <v>37</v>
       </c>
-      <c r="H188" s="7">
+      <c r="H188" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L188" s="39"/>
-      <c r="M188" s="38"/>
-    </row>
-    <row r="189" spans="1:13">
-      <c r="A189" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="B189" s="28" t="s">
-        <v>390</v>
+      <c r="L188" s="11"/>
+    </row>
+    <row r="189" spans="1:12">
+      <c r="A189" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B189" s="14" t="s">
+        <v>384</v>
       </c>
       <c r="C189" s="9">
         <v>54</v>
       </c>
-      <c r="D189" s="8">
+      <c r="D189" s="7">
         <v>87</v>
       </c>
-      <c r="E189" s="5">
+      <c r="E189" s="8">
         <v>54</v>
       </c>
-      <c r="F189" s="5"/>
+      <c r="F189" s="8">
+        <v>42</v>
+      </c>
       <c r="G189" s="9">
         <v>42</v>
       </c>
-      <c r="H189" s="7">
+      <c r="H189" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L189" s="39"/>
-      <c r="M189" s="38"/>
-    </row>
-    <row r="190" spans="1:13">
-      <c r="A190" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="B190" s="31" t="s">
-        <v>391</v>
+      <c r="L189" s="11"/>
+    </row>
+    <row r="190" spans="1:12">
+      <c r="A190" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B190" s="17" t="s">
+        <v>386</v>
       </c>
       <c r="C190" s="9">
         <v>72</v>
       </c>
-      <c r="D190" s="8">
+      <c r="D190" s="7">
         <v>100</v>
       </c>
-      <c r="E190" s="5">
+      <c r="E190" s="8">
         <v>73</v>
       </c>
-      <c r="F190" s="5"/>
+      <c r="F190" s="8">
+        <v>81</v>
+      </c>
       <c r="G190" s="9">
         <v>57</v>
       </c>
-      <c r="H190" s="7">
+      <c r="H190" s="10">
         <v>85.714285700000005</v>
       </c>
-      <c r="L190" s="39"/>
-      <c r="M190" s="38"/>
-    </row>
-    <row r="191" spans="1:13">
-      <c r="A191" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="B191" s="28" t="s">
-        <v>392</v>
+      <c r="L190" s="11"/>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B191" s="14" t="s">
+        <v>388</v>
       </c>
       <c r="C191" s="9">
         <v>72</v>
       </c>
-      <c r="D191" s="8">
+      <c r="D191" s="7">
         <v>100</v>
       </c>
-      <c r="E191" s="5">
+      <c r="E191" s="8">
         <v>69</v>
       </c>
-      <c r="F191" s="5"/>
+      <c r="F191" s="8">
+        <v>81</v>
+      </c>
       <c r="G191" s="9">
         <v>62</v>
       </c>
-      <c r="H191" s="7">
+      <c r="H191" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L191" s="39"/>
-      <c r="M191" s="38"/>
-    </row>
-    <row r="192" spans="1:13">
-      <c r="A192" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="B192" s="28" t="s">
-        <v>393</v>
+      <c r="L191" s="11"/>
+    </row>
+    <row r="192" spans="1:12">
+      <c r="A192" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B192" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="C192" s="9">
         <v>54</v>
       </c>
-      <c r="D192" s="8">
+      <c r="D192" s="7">
         <v>87</v>
       </c>
-      <c r="E192" s="5">
+      <c r="E192" s="8">
         <v>78</v>
       </c>
-      <c r="F192" s="5"/>
+      <c r="F192" s="8">
+        <v>42</v>
+      </c>
       <c r="G192" s="9">
         <v>45</v>
       </c>
-      <c r="H192" s="7">
+      <c r="H192" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L192" s="39"/>
-      <c r="M192" s="38"/>
-    </row>
-    <row r="193" spans="1:13">
-      <c r="A193" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="B193" s="28" t="s">
-        <v>394</v>
+      <c r="L192" s="11"/>
+    </row>
+    <row r="193" spans="1:12">
+      <c r="A193" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B193" s="14" t="s">
+        <v>392</v>
       </c>
       <c r="C193" s="9">
         <v>54</v>
       </c>
-      <c r="D193" s="8">
+      <c r="D193" s="7">
         <v>87</v>
       </c>
-      <c r="E193" s="5">
+      <c r="E193" s="8">
         <v>65</v>
       </c>
-      <c r="F193" s="5"/>
+      <c r="F193" s="8">
+        <v>42</v>
+      </c>
       <c r="G193" s="9">
         <v>39</v>
       </c>
-      <c r="H193" s="7">
+      <c r="H193" s="10">
         <v>92.857142899999999</v>
       </c>
-      <c r="L193" s="39"/>
-      <c r="M193" s="38"/>
-    </row>
-    <row r="194" spans="1:13">
-      <c r="A194" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="B194" s="32" t="s">
-        <v>382</v>
+      <c r="L193" s="11"/>
+    </row>
+    <row r="194" spans="1:12">
+      <c r="A194" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="B194" s="19" t="s">
+        <v>394</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D194" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F194" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G194" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H194" s="6"/>
-      <c r="L194" s="40"/>
-      <c r="M194" s="38"/>
-    </row>
-    <row r="195" spans="1:13">
-      <c r="A195" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H194" s="20"/>
+      <c r="L194" s="21"/>
+    </row>
+    <row r="195" spans="1:12">
+      <c r="A195" s="22" t="s">
         <v>395</v>
       </c>
-      <c r="B195" s="28" t="s">
+      <c r="B195" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="C195" s="9" t="s">
-        <v>383</v>
+      <c r="C195" s="42">
+        <v>51</v>
       </c>
       <c r="D195" s="9">
         <v>79</v>
       </c>
-      <c r="E195" s="5">
+      <c r="E195" s="8">
         <v>59</v>
       </c>
-      <c r="F195" s="5"/>
+      <c r="F195" s="8">
+        <v>49</v>
+      </c>
       <c r="G195" s="9">
         <v>50</v>
       </c>
-      <c r="H195" s="6"/>
-      <c r="L195" s="41"/>
-      <c r="M195" s="38"/>
-    </row>
-    <row r="196" spans="1:13">
-      <c r="A196" s="34" t="s">
+      <c r="H195" s="20"/>
+      <c r="L195" s="23"/>
+    </row>
+    <row r="196" spans="1:12">
+      <c r="A196" s="22" t="s">
         <v>397</v>
       </c>
-      <c r="B196" s="28"/>
-      <c r="C196" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D196" s="8">
+      <c r="B196" s="14"/>
+      <c r="C196" s="42">
+        <v>60</v>
+      </c>
+      <c r="D196" s="7">
         <v>86.5</v>
       </c>
-      <c r="E196" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F196" s="5"/>
+      <c r="E196" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F196" s="8">
+        <v>43</v>
+      </c>
       <c r="G196" s="9">
         <v>53</v>
       </c>
-      <c r="H196" s="6"/>
-      <c r="L196" s="41"/>
-      <c r="M196" s="38"/>
-    </row>
-    <row r="197" spans="1:13">
-      <c r="A197" s="34" t="s">
+      <c r="H196" s="20"/>
+      <c r="L196" s="23"/>
+    </row>
+    <row r="197" spans="1:12">
+      <c r="A197" s="22" t="s">
         <v>398</v>
       </c>
-      <c r="B197" s="28" t="s">
+      <c r="B197" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="C197" s="9" t="s">
-        <v>383</v>
+      <c r="C197" s="42">
+        <v>15</v>
       </c>
       <c r="D197" s="9">
         <v>91</v>
       </c>
-      <c r="E197" s="5">
+      <c r="E197" s="8">
         <v>54</v>
       </c>
-      <c r="F197" s="5"/>
+      <c r="F197" s="8">
+        <v>49</v>
+      </c>
       <c r="G197" s="9">
         <v>40</v>
       </c>
-      <c r="H197" s="6"/>
-      <c r="L197" s="41"/>
-      <c r="M197" s="38"/>
-    </row>
-    <row r="198" spans="1:13">
-      <c r="A198" s="34" t="s">
+      <c r="H197" s="20"/>
+      <c r="L197" s="23"/>
+    </row>
+    <row r="198" spans="1:12">
+      <c r="A198" s="22" t="s">
         <v>400</v>
       </c>
-      <c r="B198" s="28" t="s">
+      <c r="B198" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="C198" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D198" s="8">
+      <c r="C198" s="42">
+        <v>65</v>
+      </c>
+      <c r="D198" s="7">
         <v>86.5</v>
       </c>
-      <c r="E198" s="5">
+      <c r="E198" s="8">
         <v>59</v>
       </c>
-      <c r="F198" s="5"/>
+      <c r="F198" s="8">
+        <v>43</v>
+      </c>
       <c r="G198" s="9">
         <v>71</v>
       </c>
-      <c r="H198" s="6"/>
-      <c r="L198" s="41"/>
-      <c r="M198" s="38"/>
-    </row>
-    <row r="199" spans="1:13">
-      <c r="A199" s="34" t="s">
-        <v>407</v>
-      </c>
-      <c r="B199" s="28"/>
-      <c r="C199" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D199" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E199" s="5">
+      <c r="H198" s="20"/>
+      <c r="L198" s="23"/>
+    </row>
+    <row r="199" spans="1:12">
+      <c r="A199" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="B199" s="14"/>
+      <c r="C199" s="42">
+        <v>47</v>
+      </c>
+      <c r="D199" s="41">
+        <v>60</v>
+      </c>
+      <c r="E199" s="8">
         <v>54</v>
       </c>
-      <c r="F199" s="5"/>
+      <c r="F199" s="8">
+        <v>43</v>
+      </c>
       <c r="G199" s="9">
         <v>49</v>
       </c>
-      <c r="H199" s="6"/>
-      <c r="L199" s="41"/>
-      <c r="M199" s="38"/>
-    </row>
-    <row r="200" spans="1:13">
-      <c r="A200" s="34" t="s">
-        <v>402</v>
-      </c>
-      <c r="B200" s="28" t="s">
+      <c r="H199" s="20"/>
+      <c r="L199" s="23"/>
+    </row>
+    <row r="200" spans="1:12">
+      <c r="A200" s="22" t="s">
         <v>403</v>
       </c>
-      <c r="C200" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D200" s="8">
+      <c r="B200" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="C200" s="42">
+        <v>60</v>
+      </c>
+      <c r="D200" s="7">
         <v>86.5</v>
       </c>
-      <c r="E200" s="5">
+      <c r="E200" s="8">
         <v>59</v>
       </c>
-      <c r="F200" s="5"/>
+      <c r="F200" s="8">
+        <v>43</v>
+      </c>
       <c r="G200" s="9">
         <v>54</v>
       </c>
-      <c r="H200" s="6"/>
-      <c r="L200" s="41"/>
-      <c r="M200" s="38"/>
-    </row>
-    <row r="201" spans="1:13">
-      <c r="A201" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="B201" s="30"/>
-      <c r="C201" s="9">
+      <c r="H200" s="20"/>
+      <c r="L200" s="23"/>
+    </row>
+    <row r="201" spans="1:12">
+      <c r="A201" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B201" s="16"/>
+      <c r="C201" s="42">
         <v>36</v>
       </c>
-      <c r="D201" s="8">
+      <c r="D201" s="7">
         <v>92.5</v>
       </c>
-      <c r="E201" s="5">
+      <c r="E201" s="8">
         <v>60</v>
       </c>
-      <c r="F201" s="5"/>
+      <c r="F201" s="8">
+        <v>70</v>
+      </c>
       <c r="G201" s="9">
         <v>54</v>
       </c>
-      <c r="H201" s="6"/>
-      <c r="L201" s="41"/>
-      <c r="M201" s="38"/>
-    </row>
-    <row r="202" spans="1:13">
-      <c r="A202" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="B202" s="30" t="s">
+      <c r="H201" s="20"/>
+      <c r="L201" s="23"/>
+    </row>
+    <row r="202" spans="1:12">
+      <c r="A202" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="C202" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D202" s="8">
+      <c r="B202" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C202" s="42">
+        <v>45</v>
+      </c>
+      <c r="D202" s="7">
         <v>86.5</v>
       </c>
-      <c r="E202" s="5">
+      <c r="E202" s="8">
         <v>43</v>
       </c>
-      <c r="F202" s="5"/>
+      <c r="F202" s="8">
+        <v>43</v>
+      </c>
       <c r="G202" s="9">
         <v>45</v>
       </c>
-      <c r="H202" s="6"/>
-      <c r="L202" s="40"/>
-      <c r="M202" s="38"/>
-    </row>
-    <row r="203" spans="1:13">
-      <c r="A203" s="12" t="s">
+      <c r="H202" s="20"/>
+      <c r="L202" s="21"/>
+    </row>
+    <row r="203" spans="1:12">
+      <c r="A203" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="B203" s="16"/>
+      <c r="C203" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E203" s="8">
+        <v>43</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H203" s="20"/>
+      <c r="L203" s="21"/>
+    </row>
+    <row r="204" spans="1:12">
+      <c r="A204" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="B203" s="30"/>
-      <c r="C203" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D203" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E203" s="5">
-        <v>43</v>
-      </c>
-      <c r="F203" s="5"/>
-      <c r="G203" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="H203" s="6"/>
-      <c r="L203" s="40"/>
-      <c r="M203" s="38"/>
-    </row>
-    <row r="204" spans="1:13">
-      <c r="A204" s="35" t="s">
-        <v>408</v>
-      </c>
-      <c r="B204" s="36"/>
-      <c r="C204" s="37" t="s">
-        <v>383</v>
-      </c>
-      <c r="D204" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="E204" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F204" s="5"/>
+      <c r="B204" s="25"/>
+      <c r="C204" s="43">
+        <v>26</v>
+      </c>
+      <c r="D204" s="41">
+        <v>25</v>
+      </c>
+      <c r="E204" s="40">
+        <v>60</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="G204" s="9">
         <v>29</v>
       </c>
-      <c r="H204" s="6"/>
-      <c r="L204" s="40"/>
-      <c r="M204" s="38"/>
-    </row>
-    <row r="205" spans="1:13">
-      <c r="A205" s="13"/>
-      <c r="B205" s="14"/>
-      <c r="C205" s="15"/>
-      <c r="D205" s="16"/>
-      <c r="E205" s="17"/>
-      <c r="F205" s="17"/>
-      <c r="G205" s="18"/>
-      <c r="H205" s="19"/>
-      <c r="L205" s="39"/>
-      <c r="M205" s="38"/>
-    </row>
-    <row r="206" spans="1:13">
-      <c r="A206" s="13"/>
-      <c r="B206" s="14"/>
-      <c r="C206" s="15"/>
-      <c r="D206" s="16"/>
-      <c r="E206" s="17"/>
-      <c r="F206" s="17"/>
-      <c r="G206" s="18"/>
-      <c r="H206" s="19"/>
-    </row>
-    <row r="207" spans="1:13">
-      <c r="A207" s="13"/>
-      <c r="B207" s="14"/>
-      <c r="C207" s="15"/>
-      <c r="D207" s="16"/>
-      <c r="E207" s="17"/>
-      <c r="F207" s="17"/>
-      <c r="G207" s="18"/>
-      <c r="H207" s="19"/>
-    </row>
-    <row r="208" spans="1:13">
-      <c r="A208" s="13"/>
-      <c r="B208" s="14"/>
-      <c r="C208" s="15"/>
-      <c r="D208" s="16"/>
-      <c r="E208" s="17"/>
-      <c r="F208" s="17"/>
-      <c r="G208" s="18"/>
-      <c r="H208" s="19"/>
+      <c r="H204" s="20"/>
+      <c r="L204" s="21"/>
+    </row>
+    <row r="205" spans="1:12">
+      <c r="A205" s="26"/>
+      <c r="B205" s="27"/>
+      <c r="C205" s="28"/>
+      <c r="D205" s="29"/>
+      <c r="E205" s="30"/>
+      <c r="F205" s="30"/>
+      <c r="G205" s="31"/>
+      <c r="H205" s="32"/>
+      <c r="L205" s="11"/>
+    </row>
+    <row r="206" spans="1:12">
+      <c r="A206" s="26"/>
+      <c r="B206" s="27"/>
+      <c r="C206" s="28"/>
+      <c r="D206" s="29"/>
+      <c r="E206" s="30"/>
+      <c r="F206" s="30"/>
+      <c r="G206" s="31"/>
+      <c r="H206" s="32"/>
+    </row>
+    <row r="207" spans="1:12">
+      <c r="A207" s="26"/>
+      <c r="B207" s="27"/>
+      <c r="C207" s="28"/>
+      <c r="D207" s="29"/>
+      <c r="E207" s="30"/>
+      <c r="F207" s="30"/>
+      <c r="G207" s="31"/>
+      <c r="H207" s="32"/>
+    </row>
+    <row r="208" spans="1:12">
+      <c r="A208" s="26"/>
+      <c r="B208" s="27"/>
+      <c r="C208" s="28"/>
+      <c r="D208" s="29"/>
+      <c r="E208" s="30"/>
+      <c r="F208" s="30"/>
+      <c r="G208" s="31"/>
+      <c r="H208" s="32"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="13"/>
-      <c r="B209" s="14"/>
-      <c r="C209" s="15"/>
-      <c r="D209" s="16"/>
-      <c r="E209" s="17"/>
-      <c r="F209" s="20"/>
-      <c r="G209" s="18"/>
-      <c r="H209" s="19"/>
+      <c r="A209" s="26"/>
+      <c r="B209" s="27"/>
+      <c r="C209" s="28"/>
+      <c r="D209" s="29"/>
+      <c r="E209" s="30"/>
+      <c r="F209" s="33"/>
+      <c r="G209" s="31"/>
+      <c r="H209" s="32"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="13"/>
-      <c r="B210" s="14"/>
-      <c r="C210" s="15"/>
-      <c r="D210" s="16"/>
-      <c r="E210" s="17"/>
-      <c r="F210" s="17"/>
-      <c r="G210" s="18"/>
-      <c r="H210" s="19"/>
+      <c r="A210" s="26"/>
+      <c r="B210" s="27"/>
+      <c r="C210" s="28"/>
+      <c r="D210" s="29"/>
+      <c r="E210" s="30"/>
+      <c r="F210" s="30"/>
+      <c r="G210" s="31"/>
+      <c r="H210" s="32"/>
     </row>
     <row r="211" spans="1:8">
-      <c r="A211" s="13"/>
-      <c r="B211" s="14"/>
-      <c r="C211" s="15"/>
-      <c r="D211" s="16"/>
-      <c r="E211" s="17"/>
-      <c r="F211" s="17"/>
-      <c r="G211" s="18"/>
-      <c r="H211" s="19"/>
+      <c r="A211" s="26"/>
+      <c r="B211" s="27"/>
+      <c r="C211" s="28"/>
+      <c r="D211" s="29"/>
+      <c r="E211" s="30"/>
+      <c r="F211" s="30"/>
+      <c r="G211" s="31"/>
+      <c r="H211" s="32"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="13"/>
-      <c r="B212" s="14"/>
-      <c r="C212" s="15"/>
-      <c r="D212" s="16"/>
-      <c r="E212" s="17"/>
-      <c r="F212" s="17"/>
-      <c r="G212" s="18"/>
-      <c r="H212" s="19"/>
+      <c r="A212" s="26"/>
+      <c r="B212" s="27"/>
+      <c r="C212" s="28"/>
+      <c r="D212" s="29"/>
+      <c r="E212" s="30"/>
+      <c r="F212" s="30"/>
+      <c r="G212" s="31"/>
+      <c r="H212" s="32"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="13"/>
-      <c r="B213" s="14"/>
-      <c r="C213" s="15"/>
-      <c r="D213" s="16"/>
-      <c r="E213" s="17"/>
-      <c r="F213" s="17"/>
-      <c r="G213" s="18"/>
-      <c r="H213" s="19"/>
+      <c r="A213" s="26"/>
+      <c r="B213" s="27"/>
+      <c r="C213" s="28"/>
+      <c r="D213" s="29"/>
+      <c r="E213" s="30"/>
+      <c r="F213" s="30"/>
+      <c r="G213" s="31"/>
+      <c r="H213" s="32"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="13"/>
-      <c r="B214" s="14"/>
-      <c r="C214" s="15"/>
-      <c r="D214" s="16"/>
-      <c r="E214" s="17"/>
-      <c r="F214" s="17"/>
-      <c r="G214" s="18"/>
-      <c r="H214" s="19"/>
+      <c r="A214" s="26"/>
+      <c r="B214" s="27"/>
+      <c r="C214" s="28"/>
+      <c r="D214" s="29"/>
+      <c r="E214" s="30"/>
+      <c r="F214" s="30"/>
+      <c r="G214" s="31"/>
+      <c r="H214" s="32"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="13"/>
-      <c r="B215" s="14"/>
-      <c r="C215" s="15"/>
-      <c r="D215" s="16"/>
-      <c r="E215" s="17"/>
-      <c r="F215" s="17"/>
-      <c r="G215" s="18"/>
-      <c r="H215" s="19"/>
+      <c r="A215" s="26"/>
+      <c r="B215" s="27"/>
+      <c r="C215" s="28"/>
+      <c r="D215" s="29"/>
+      <c r="E215" s="30"/>
+      <c r="F215" s="30"/>
+      <c r="G215" s="31"/>
+      <c r="H215" s="32"/>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="13"/>
-      <c r="B216" s="14"/>
-      <c r="C216" s="15"/>
-      <c r="D216" s="16"/>
-      <c r="E216" s="17"/>
-      <c r="F216" s="17"/>
-      <c r="G216" s="18"/>
-      <c r="H216" s="19"/>
+      <c r="A216" s="26"/>
+      <c r="B216" s="27"/>
+      <c r="C216" s="28"/>
+      <c r="D216" s="29"/>
+      <c r="E216" s="30"/>
+      <c r="F216" s="30"/>
+      <c r="G216" s="31"/>
+      <c r="H216" s="32"/>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="13"/>
-      <c r="B217" s="14"/>
-      <c r="C217" s="15"/>
-      <c r="D217" s="16"/>
-      <c r="E217" s="17"/>
-      <c r="F217" s="17"/>
-      <c r="G217" s="18"/>
-      <c r="H217" s="19"/>
+      <c r="A217" s="26"/>
+      <c r="B217" s="27"/>
+      <c r="C217" s="28"/>
+      <c r="D217" s="29"/>
+      <c r="E217" s="30"/>
+      <c r="F217" s="30"/>
+      <c r="G217" s="31"/>
+      <c r="H217" s="32"/>
     </row>
     <row r="218" spans="1:8">
-      <c r="A218" s="13"/>
-      <c r="B218" s="14"/>
-      <c r="C218" s="15"/>
-      <c r="D218" s="16"/>
-      <c r="E218" s="17"/>
-      <c r="F218" s="17"/>
-      <c r="G218" s="18"/>
-      <c r="H218" s="19"/>
+      <c r="A218" s="26"/>
+      <c r="B218" s="27"/>
+      <c r="C218" s="28"/>
+      <c r="D218" s="29"/>
+      <c r="E218" s="30"/>
+      <c r="F218" s="30"/>
+      <c r="G218" s="31"/>
+      <c r="H218" s="32"/>
     </row>
     <row r="219" spans="1:8">
-      <c r="A219" s="13"/>
-      <c r="B219" s="14"/>
-      <c r="C219" s="15"/>
-      <c r="D219" s="16"/>
-      <c r="E219" s="21"/>
-      <c r="F219" s="17"/>
-      <c r="G219" s="18"/>
-      <c r="H219" s="19"/>
+      <c r="A219" s="26"/>
+      <c r="B219" s="27"/>
+      <c r="C219" s="28"/>
+      <c r="D219" s="29"/>
+      <c r="E219" s="34"/>
+      <c r="F219" s="30"/>
+      <c r="G219" s="31"/>
+      <c r="H219" s="32"/>
     </row>
     <row r="220" spans="1:8">
-      <c r="A220" s="13"/>
-      <c r="B220" s="14"/>
-      <c r="C220" s="15"/>
-      <c r="D220" s="16"/>
-      <c r="E220" s="17"/>
-      <c r="F220" s="17"/>
-      <c r="G220" s="18"/>
-      <c r="H220" s="19"/>
+      <c r="A220" s="26"/>
+      <c r="B220" s="27"/>
+      <c r="C220" s="28"/>
+      <c r="D220" s="29"/>
+      <c r="E220" s="30"/>
+      <c r="F220" s="30"/>
+      <c r="G220" s="31"/>
+      <c r="H220" s="32"/>
     </row>
     <row r="221" spans="1:8">
-      <c r="A221" s="13"/>
-      <c r="B221" s="14"/>
-      <c r="C221" s="15"/>
-      <c r="D221" s="16"/>
-      <c r="E221" s="17"/>
-      <c r="F221" s="17"/>
-      <c r="G221" s="18"/>
-      <c r="H221" s="19"/>
+      <c r="A221" s="26"/>
+      <c r="B221" s="27"/>
+      <c r="C221" s="28"/>
+      <c r="D221" s="29"/>
+      <c r="E221" s="30"/>
+      <c r="F221" s="30"/>
+      <c r="G221" s="31"/>
+      <c r="H221" s="32"/>
     </row>
     <row r="222" spans="1:8">
-      <c r="A222" s="13"/>
-      <c r="B222" s="14"/>
-      <c r="C222" s="15"/>
-      <c r="D222" s="16"/>
-      <c r="E222" s="17"/>
-      <c r="F222" s="17"/>
-      <c r="G222" s="18"/>
-      <c r="H222" s="19"/>
+      <c r="A222" s="26"/>
+      <c r="B222" s="27"/>
+      <c r="C222" s="28"/>
+      <c r="D222" s="29"/>
+      <c r="E222" s="30"/>
+      <c r="F222" s="30"/>
+      <c r="G222" s="31"/>
+      <c r="H222" s="32"/>
     </row>
     <row r="223" spans="1:8">
-      <c r="A223" s="13"/>
-      <c r="B223" s="14"/>
-      <c r="C223" s="15"/>
-      <c r="D223" s="16"/>
-      <c r="E223" s="17"/>
-      <c r="F223" s="17"/>
-      <c r="G223" s="18"/>
-      <c r="H223" s="19"/>
+      <c r="A223" s="26"/>
+      <c r="B223" s="27"/>
+      <c r="C223" s="28"/>
+      <c r="D223" s="29"/>
+      <c r="E223" s="30"/>
+      <c r="F223" s="30"/>
+      <c r="G223" s="31"/>
+      <c r="H223" s="32"/>
     </row>
     <row r="224" spans="1:8">
-      <c r="A224" s="13"/>
-      <c r="B224" s="14"/>
-      <c r="C224" s="15"/>
-      <c r="D224" s="16"/>
-      <c r="E224" s="17"/>
-      <c r="F224" s="17"/>
-      <c r="G224" s="18"/>
-      <c r="H224" s="19"/>
+      <c r="A224" s="26"/>
+      <c r="B224" s="27"/>
+      <c r="C224" s="28"/>
+      <c r="D224" s="29"/>
+      <c r="E224" s="30"/>
+      <c r="F224" s="30"/>
+      <c r="G224" s="31"/>
+      <c r="H224" s="32"/>
     </row>
     <row r="225" spans="1:8">
-      <c r="A225" s="13"/>
-      <c r="B225" s="14"/>
-      <c r="C225" s="15"/>
-      <c r="D225" s="16"/>
-      <c r="E225" s="17"/>
-      <c r="F225" s="17"/>
-      <c r="G225" s="18"/>
-      <c r="H225" s="19"/>
+      <c r="A225" s="26"/>
+      <c r="B225" s="27"/>
+      <c r="C225" s="28"/>
+      <c r="D225" s="29"/>
+      <c r="E225" s="30"/>
+      <c r="F225" s="30"/>
+      <c r="G225" s="31"/>
+      <c r="H225" s="32"/>
     </row>
     <row r="226" spans="1:8">
-      <c r="A226" s="13"/>
-      <c r="B226" s="14"/>
-      <c r="C226" s="15"/>
-      <c r="D226" s="16"/>
-      <c r="E226" s="17"/>
-      <c r="F226" s="17"/>
-      <c r="G226" s="18"/>
-      <c r="H226" s="19"/>
+      <c r="A226" s="26"/>
+      <c r="B226" s="27"/>
+      <c r="C226" s="28"/>
+      <c r="D226" s="29"/>
+      <c r="E226" s="30"/>
+      <c r="F226" s="30"/>
+      <c r="G226" s="31"/>
+      <c r="H226" s="32"/>
     </row>
     <row r="227" spans="1:8">
-      <c r="A227" s="13"/>
-      <c r="B227" s="14"/>
-      <c r="C227" s="15"/>
-      <c r="D227" s="16"/>
-      <c r="E227" s="17"/>
-      <c r="F227" s="17"/>
-      <c r="G227" s="18"/>
-      <c r="H227" s="19"/>
+      <c r="A227" s="26"/>
+      <c r="B227" s="27"/>
+      <c r="C227" s="28"/>
+      <c r="D227" s="29"/>
+      <c r="E227" s="30"/>
+      <c r="F227" s="30"/>
+      <c r="G227" s="31"/>
+      <c r="H227" s="32"/>
     </row>
     <row r="228" spans="1:8">
-      <c r="A228" s="13"/>
-      <c r="B228" s="14"/>
-      <c r="C228" s="15"/>
-      <c r="D228" s="16"/>
-      <c r="E228" s="17"/>
-      <c r="F228" s="17"/>
-      <c r="G228" s="18"/>
-      <c r="H228" s="19"/>
+      <c r="A228" s="26"/>
+      <c r="B228" s="27"/>
+      <c r="C228" s="28"/>
+      <c r="D228" s="29"/>
+      <c r="E228" s="30"/>
+      <c r="F228" s="30"/>
+      <c r="G228" s="31"/>
+      <c r="H228" s="32"/>
     </row>
     <row r="229" spans="1:8">
-      <c r="A229" s="13"/>
-      <c r="B229" s="14"/>
-      <c r="C229" s="15"/>
-      <c r="D229" s="16"/>
-      <c r="E229" s="17"/>
-      <c r="F229" s="17"/>
-      <c r="G229" s="18"/>
-      <c r="H229" s="19"/>
+      <c r="A229" s="26"/>
+      <c r="B229" s="27"/>
+      <c r="C229" s="28"/>
+      <c r="D229" s="29"/>
+      <c r="E229" s="30"/>
+      <c r="F229" s="30"/>
+      <c r="G229" s="31"/>
+      <c r="H229" s="32"/>
     </row>
     <row r="230" spans="1:8">
-      <c r="A230" s="13"/>
-      <c r="B230" s="14"/>
-      <c r="C230" s="15"/>
-      <c r="D230" s="16"/>
-      <c r="E230" s="17"/>
-      <c r="F230" s="17"/>
-      <c r="G230" s="18"/>
-      <c r="H230" s="19"/>
+      <c r="A230" s="26"/>
+      <c r="B230" s="27"/>
+      <c r="C230" s="28"/>
+      <c r="D230" s="29"/>
+      <c r="E230" s="30"/>
+      <c r="F230" s="30"/>
+      <c r="G230" s="31"/>
+      <c r="H230" s="32"/>
     </row>
     <row r="231" spans="1:8">
-      <c r="A231" s="13"/>
-      <c r="B231" s="14"/>
-      <c r="C231" s="15"/>
-      <c r="D231" s="16"/>
-      <c r="E231" s="17"/>
-      <c r="F231" s="17"/>
-      <c r="G231" s="18"/>
-      <c r="H231" s="19"/>
+      <c r="A231" s="26"/>
+      <c r="B231" s="27"/>
+      <c r="C231" s="28"/>
+      <c r="D231" s="29"/>
+      <c r="E231" s="30"/>
+      <c r="F231" s="30"/>
+      <c r="G231" s="31"/>
+      <c r="H231" s="32"/>
     </row>
     <row r="232" spans="1:8">
-      <c r="A232" s="13"/>
-      <c r="B232" s="14"/>
-      <c r="C232" s="15"/>
-      <c r="D232" s="16"/>
-      <c r="E232" s="17"/>
-      <c r="F232" s="17"/>
-      <c r="G232" s="18"/>
-      <c r="H232" s="19"/>
+      <c r="A232" s="26"/>
+      <c r="B232" s="27"/>
+      <c r="C232" s="28"/>
+      <c r="D232" s="29"/>
+      <c r="E232" s="30"/>
+      <c r="F232" s="30"/>
+      <c r="G232" s="31"/>
+      <c r="H232" s="32"/>
     </row>
     <row r="233" spans="1:8">
-      <c r="A233" s="13"/>
-      <c r="B233" s="14"/>
-      <c r="C233" s="15"/>
-      <c r="D233" s="16"/>
-      <c r="E233" s="17"/>
-      <c r="F233" s="17"/>
-      <c r="G233" s="18"/>
-      <c r="H233" s="19"/>
+      <c r="A233" s="26"/>
+      <c r="B233" s="27"/>
+      <c r="C233" s="28"/>
+      <c r="D233" s="29"/>
+      <c r="E233" s="30"/>
+      <c r="F233" s="30"/>
+      <c r="G233" s="31"/>
+      <c r="H233" s="32"/>
     </row>
     <row r="234" spans="1:8">
-      <c r="A234" s="13"/>
-      <c r="B234" s="14"/>
-      <c r="C234" s="15"/>
-      <c r="D234" s="16"/>
-      <c r="E234" s="17"/>
-      <c r="F234" s="17"/>
-      <c r="G234" s="18"/>
-      <c r="H234" s="19"/>
+      <c r="A234" s="26"/>
+      <c r="B234" s="27"/>
+      <c r="C234" s="28"/>
+      <c r="D234" s="29"/>
+      <c r="E234" s="30"/>
+      <c r="F234" s="30"/>
+      <c r="G234" s="31"/>
+      <c r="H234" s="32"/>
     </row>
     <row r="235" spans="1:8">
-      <c r="A235" s="13"/>
-      <c r="B235" s="14"/>
-      <c r="C235" s="15"/>
-      <c r="D235" s="16"/>
-      <c r="E235" s="21"/>
-      <c r="F235" s="17"/>
-      <c r="G235" s="18"/>
-      <c r="H235" s="19"/>
+      <c r="A235" s="26"/>
+      <c r="B235" s="27"/>
+      <c r="C235" s="28"/>
+      <c r="D235" s="29"/>
+      <c r="E235" s="34"/>
+      <c r="F235" s="30"/>
+      <c r="G235" s="31"/>
+      <c r="H235" s="32"/>
     </row>
     <row r="236" spans="1:8">
-      <c r="A236" s="22"/>
-      <c r="B236" s="23"/>
-      <c r="C236" s="15"/>
-      <c r="D236" s="16"/>
-      <c r="E236" s="17"/>
-      <c r="F236" s="17"/>
-      <c r="G236" s="18"/>
-      <c r="H236" s="19"/>
+      <c r="A236" s="35"/>
+      <c r="B236" s="36"/>
+      <c r="C236" s="28"/>
+      <c r="D236" s="29"/>
+      <c r="E236" s="30"/>
+      <c r="F236" s="30"/>
+      <c r="G236" s="31"/>
+      <c r="H236" s="32"/>
     </row>
     <row r="237" spans="1:8">
-      <c r="A237" s="22"/>
-      <c r="B237" s="23"/>
-      <c r="C237" s="15"/>
-      <c r="D237" s="16"/>
-      <c r="E237" s="17"/>
-      <c r="F237" s="17"/>
-      <c r="G237" s="18"/>
-      <c r="H237" s="19"/>
+      <c r="A237" s="35"/>
+      <c r="B237" s="36"/>
+      <c r="C237" s="28"/>
+      <c r="D237" s="29"/>
+      <c r="E237" s="30"/>
+      <c r="F237" s="30"/>
+      <c r="G237" s="31"/>
+      <c r="H237" s="32"/>
     </row>
     <row r="238" spans="1:8">
-      <c r="A238" s="22"/>
-      <c r="B238" s="23"/>
-      <c r="C238" s="15"/>
-      <c r="D238" s="16"/>
-      <c r="E238" s="17"/>
-      <c r="F238" s="17"/>
-      <c r="G238" s="18"/>
-      <c r="H238" s="19"/>
+      <c r="A238" s="35"/>
+      <c r="B238" s="36"/>
+      <c r="C238" s="28"/>
+      <c r="D238" s="29"/>
+      <c r="E238" s="30"/>
+      <c r="F238" s="30"/>
+      <c r="G238" s="31"/>
+      <c r="H238" s="32"/>
     </row>
     <row r="239" spans="1:8">
-      <c r="A239" s="22"/>
-      <c r="B239" s="23"/>
-      <c r="C239" s="15"/>
-      <c r="D239" s="16"/>
-      <c r="E239" s="15"/>
-      <c r="F239" s="17"/>
-      <c r="G239" s="18"/>
-      <c r="H239" s="19"/>
+      <c r="A239" s="35"/>
+      <c r="B239" s="36"/>
+      <c r="C239" s="28"/>
+      <c r="D239" s="29"/>
+      <c r="E239" s="28"/>
+      <c r="F239" s="30"/>
+      <c r="G239" s="31"/>
+      <c r="H239" s="32"/>
     </row>
     <row r="240" spans="1:8">
-      <c r="A240" s="24"/>
-      <c r="B240" s="25"/>
-      <c r="C240" s="15"/>
-      <c r="D240" s="16"/>
-      <c r="E240" s="15"/>
-      <c r="F240" s="17"/>
-      <c r="G240" s="18"/>
-      <c r="H240" s="19"/>
+      <c r="A240" s="37"/>
+      <c r="B240" s="38"/>
+      <c r="C240" s="28"/>
+      <c r="D240" s="29"/>
+      <c r="E240" s="28"/>
+      <c r="F240" s="30"/>
+      <c r="G240" s="31"/>
+      <c r="H240" s="32"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -7669,6 +7921,12 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
@@ -7695,4 +7953,20 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a5132194-61b6-4507-86ae-3af00c68c385"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>